--- a/templates/제품마스터_양식.xlsx
+++ b/templates/제품마스터_양식.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -117,6 +117,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E2000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -520,7 +522,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>TM-10001</t>
         </is>
@@ -543,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>TM-10001</t>
         </is>
@@ -566,7 +568,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>TM-10001</t>
         </is>
@@ -589,7 +591,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>TM-10001</t>
         </is>
@@ -612,7 +614,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>TM-20002</t>
         </is>
@@ -635,7 +637,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>TM-20002</t>
         </is>
@@ -658,7 +660,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>TM-20002</t>
         </is>
@@ -680,6 +682,5982 @@
         <v>228</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="9" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="9" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="9" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="9" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="9" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="9" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="9" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="9" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="9" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="9" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="9" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="9" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="9" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="9" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="9" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="9" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="9" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="9" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="9" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="9" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="9" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="9" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="9" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="9" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="9" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="9" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="9" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="9" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="9" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="9" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="9" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="9" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="9" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="9" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="9" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="9" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="9" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="9" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="9" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="9" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="9" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="9" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="9" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="9" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="9" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="9" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="9" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="9" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="9" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="9" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="9" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="9" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="9" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="9" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="9" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="9" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="9" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="9" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="9" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="9" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="9" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="9" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="9" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="9" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="9" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="9" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="9" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="9" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="9" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="9" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="9" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="9" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="9" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="9" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="9" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="9" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="9" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="9" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="9" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="9" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="9" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="9" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="9" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="9" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="9" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="9" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="9" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="9" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="9" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="9" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="9" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="9" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="9" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="9" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="9" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="9" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="9" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="9" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="9" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="9" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="9" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="9" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="9" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="9" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="9" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="9" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="9" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="9" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="9" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="9" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="9" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="9" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="9" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="9" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="9" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="9" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="9" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="9" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="9" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="9" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="9" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="9" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="9" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="9" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="9" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="9" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="9" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="9" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="9" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="9" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="9" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="9" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="9" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="9" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="9" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="9" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="9" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="9" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="9" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="9" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="9" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="9" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="9" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="9" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="9" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="9" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="9" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="9" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="9" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="9" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="9" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="9" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="9" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="9" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="9" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="9" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="9" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="9" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="9" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="9" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="9" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="9" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="9" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="9" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="9" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="9" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="9" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="9" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="9" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="9" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="9" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="9" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="9" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="9" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="9" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="9" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="9" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="9" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="9" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="9" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="9" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="9" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="9" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="9" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="9" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="9" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="9" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="9" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="9" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="9" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="9" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="9" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="9" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="9" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="9" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="9" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="9" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="9" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="9" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="9" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="9" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="9" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="9" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="9" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="9" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="9" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="9" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="9" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="9" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="9" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="9" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="9" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="9" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="9" t="n"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="9" t="n"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="9" t="n"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="9" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="9" t="n"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="9" t="n"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="9" t="n"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="9" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="9" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="9" t="n"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="9" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="9" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="9" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="9" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="9" t="n"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="9" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="9" t="n"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="9" t="n"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="9" t="n"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="9" t="n"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="9" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="9" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="9" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="9" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="9" t="n"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="9" t="n"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="9" t="n"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="9" t="n"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="9" t="n"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="9" t="n"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="9" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="9" t="n"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="9" t="n"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="9" t="n"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="9" t="n"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="9" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="9" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="9" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="9" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="9" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="9" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="9" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="9" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="9" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="9" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="9" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="9" t="n"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="9" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="9" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="9" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="9" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="9" t="n"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="9" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="9" t="n"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="9" t="n"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="9" t="n"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="9" t="n"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="9" t="n"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="9" t="n"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="9" t="n"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="9" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="9" t="n"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="9" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="9" t="n"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="9" t="n"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="9" t="n"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="9" t="n"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="9" t="n"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="9" t="n"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="9" t="n"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="9" t="n"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="9" t="n"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="9" t="n"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="9" t="n"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="9" t="n"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="9" t="n"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="9" t="n"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="9" t="n"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="9" t="n"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="9" t="n"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="9" t="n"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="9" t="n"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="9" t="n"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="9" t="n"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="9" t="n"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="9" t="n"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="9" t="n"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="9" t="n"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="9" t="n"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="9" t="n"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="9" t="n"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="9" t="n"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="9" t="n"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="9" t="n"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="9" t="n"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="9" t="n"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="9" t="n"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="9" t="n"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="9" t="n"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="9" t="n"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="9" t="n"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="9" t="n"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="9" t="n"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="9" t="n"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="9" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="9" t="n"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="9" t="n"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="9" t="n"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="9" t="n"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="9" t="n"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="9" t="n"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="9" t="n"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="9" t="n"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="9" t="n"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="9" t="n"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="9" t="n"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="9" t="n"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="9" t="n"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="9" t="n"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="9" t="n"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="9" t="n"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="9" t="n"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="9" t="n"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="9" t="n"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="9" t="n"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="9" t="n"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="9" t="n"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="9" t="n"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="9" t="n"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="9" t="n"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="9" t="n"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="9" t="n"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="9" t="n"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="9" t="n"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="9" t="n"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="9" t="n"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="9" t="n"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="9" t="n"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="9" t="n"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="9" t="n"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="9" t="n"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="9" t="n"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="9" t="n"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="9" t="n"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="9" t="n"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="9" t="n"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="9" t="n"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="9" t="n"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="9" t="n"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="9" t="n"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="9" t="n"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="9" t="n"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="9" t="n"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="9" t="n"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="9" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="9" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="9" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="9" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="9" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="9" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="9" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="9" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="9" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="9" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="9" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="9" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="9" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="9" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="9" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="9" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="9" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="9" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="9" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="9" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="9" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="9" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="9" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="9" t="n"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="9" t="n"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="9" t="n"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="9" t="n"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="9" t="n"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="9" t="n"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="9" t="n"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="9" t="n"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="9" t="n"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="9" t="n"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="9" t="n"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="9" t="n"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="9" t="n"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="9" t="n"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="9" t="n"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="9" t="n"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="9" t="n"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="9" t="n"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="9" t="n"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="9" t="n"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="9" t="n"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="9" t="n"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="9" t="n"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="9" t="n"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="9" t="n"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="9" t="n"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="9" t="n"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="9" t="n"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="9" t="n"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="9" t="n"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="9" t="n"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="9" t="n"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="9" t="n"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="9" t="n"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="9" t="n"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="9" t="n"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="9" t="n"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="9" t="n"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="9" t="n"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="9" t="n"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="9" t="n"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="9" t="n"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="9" t="n"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="9" t="n"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="9" t="n"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="9" t="n"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="9" t="n"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="9" t="n"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="9" t="n"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="9" t="n"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="9" t="n"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="9" t="n"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="9" t="n"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="9" t="n"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="9" t="n"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="9" t="n"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="9" t="n"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="9" t="n"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="9" t="n"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="9" t="n"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="9" t="n"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="9" t="n"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="9" t="n"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="9" t="n"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="9" t="n"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="9" t="n"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="9" t="n"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="9" t="n"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="9" t="n"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="9" t="n"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="9" t="n"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="9" t="n"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="9" t="n"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="9" t="n"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="9" t="n"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="9" t="n"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="9" t="n"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="9" t="n"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="9" t="n"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="9" t="n"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="9" t="n"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="9" t="n"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="9" t="n"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="9" t="n"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="9" t="n"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="9" t="n"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="9" t="n"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="9" t="n"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="9" t="n"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="9" t="n"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="9" t="n"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="9" t="n"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="9" t="n"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="9" t="n"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="9" t="n"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="9" t="n"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="9" t="n"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="9" t="n"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="9" t="n"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="9" t="n"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="9" t="n"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="9" t="n"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="9" t="n"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="9" t="n"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="9" t="n"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="9" t="n"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="9" t="n"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="9" t="n"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="9" t="n"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="9" t="n"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="9" t="n"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="9" t="n"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="9" t="n"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="9" t="n"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="9" t="n"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="9" t="n"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="9" t="n"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="9" t="n"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="9" t="n"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="9" t="n"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="9" t="n"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="9" t="n"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="9" t="n"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="9" t="n"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="9" t="n"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="9" t="n"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="9" t="n"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="9" t="n"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="9" t="n"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="9" t="n"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="9" t="n"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="9" t="n"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="9" t="n"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="9" t="n"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="9" t="n"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="9" t="n"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="9" t="n"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="9" t="n"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="9" t="n"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="9" t="n"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="9" t="n"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="9" t="n"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="9" t="n"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="9" t="n"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="9" t="n"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="9" t="n"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="9" t="n"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="9" t="n"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="9" t="n"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="9" t="n"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="9" t="n"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="9" t="n"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="9" t="n"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="9" t="n"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="9" t="n"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="9" t="n"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="9" t="n"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="9" t="n"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="9" t="n"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="9" t="n"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="9" t="n"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="9" t="n"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="9" t="n"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="9" t="n"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="9" t="n"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="9" t="n"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="9" t="n"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="9" t="n"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="9" t="n"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="9" t="n"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="9" t="n"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="9" t="n"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="9" t="n"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="9" t="n"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="9" t="n"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="9" t="n"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="9" t="n"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="9" t="n"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="9" t="n"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="9" t="n"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="9" t="n"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="9" t="n"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="9" t="n"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="9" t="n"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="9" t="n"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="9" t="n"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="9" t="n"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="9" t="n"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="9" t="n"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="9" t="n"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="9" t="n"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="9" t="n"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="9" t="n"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="9" t="n"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="9" t="n"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="9" t="n"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="9" t="n"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="9" t="n"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="9" t="n"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="9" t="n"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="9" t="n"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="9" t="n"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="9" t="n"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="9" t="n"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="9" t="n"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="9" t="n"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="9" t="n"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="9" t="n"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="9" t="n"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="9" t="n"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="9" t="n"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="9" t="n"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="9" t="n"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="9" t="n"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="9" t="n"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="9" t="n"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="9" t="n"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="9" t="n"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="9" t="n"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="9" t="n"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="9" t="n"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="9" t="n"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="9" t="n"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="9" t="n"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="9" t="n"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="9" t="n"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="9" t="n"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="9" t="n"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="9" t="n"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="9" t="n"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="9" t="n"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="9" t="n"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="9" t="n"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="9" t="n"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="9" t="n"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="9" t="n"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="9" t="n"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="9" t="n"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="9" t="n"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="9" t="n"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="9" t="n"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="9" t="n"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="9" t="n"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="9" t="n"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="9" t="n"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="9" t="n"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="9" t="n"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="9" t="n"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="9" t="n"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="9" t="n"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="9" t="n"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="9" t="n"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="9" t="n"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="9" t="n"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="9" t="n"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="9" t="n"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="9" t="n"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="9" t="n"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="9" t="n"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="9" t="n"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="9" t="n"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="9" t="n"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="9" t="n"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="9" t="n"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="9" t="n"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="9" t="n"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="9" t="n"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="9" t="n"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="9" t="n"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="9" t="n"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="9" t="n"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="9" t="n"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="9" t="n"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="9" t="n"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="9" t="n"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="9" t="n"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="9" t="n"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="9" t="n"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="9" t="n"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="9" t="n"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="9" t="n"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="9" t="n"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="9" t="n"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="9" t="n"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="9" t="n"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="9" t="n"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="9" t="n"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="9" t="n"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="9" t="n"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="9" t="n"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="9" t="n"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="9" t="n"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="9" t="n"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="9" t="n"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="9" t="n"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="9" t="n"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="9" t="n"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="9" t="n"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="9" t="n"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="9" t="n"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="9" t="n"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="9" t="n"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="9" t="n"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="9" t="n"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="9" t="n"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="9" t="n"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="9" t="n"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="9" t="n"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="9" t="n"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="9" t="n"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="9" t="n"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="9" t="n"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="9" t="n"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="9" t="n"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="9" t="n"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="9" t="n"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="9" t="n"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="9" t="n"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="9" t="n"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="9" t="n"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="9" t="n"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="9" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="9" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="9" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="9" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="9" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="9" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="9" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="9" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="9" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="9" t="n"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="9" t="n"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="9" t="n"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="9" t="n"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="9" t="n"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="9" t="n"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="9" t="n"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="9" t="n"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="9" t="n"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="9" t="n"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="9" t="n"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="9" t="n"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="9" t="n"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="9" t="n"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="9" t="n"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="9" t="n"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="9" t="n"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="9" t="n"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="9" t="n"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="9" t="n"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="9" t="n"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="9" t="n"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="9" t="n"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="9" t="n"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="9" t="n"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="9" t="n"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="9" t="n"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="9" t="n"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="9" t="n"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="9" t="n"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="9" t="n"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="9" t="n"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="9" t="n"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="9" t="n"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="9" t="n"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="9" t="n"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="9" t="n"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="9" t="n"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="9" t="n"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="9" t="n"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="9" t="n"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="9" t="n"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="9" t="n"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="9" t="n"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="9" t="n"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="9" t="n"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="9" t="n"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="9" t="n"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="9" t="n"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="9" t="n"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="9" t="n"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="9" t="n"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="9" t="n"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="9" t="n"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="9" t="n"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="9" t="n"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="9" t="n"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="9" t="n"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="9" t="n"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="9" t="n"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="9" t="n"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="9" t="n"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="9" t="n"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="9" t="n"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="9" t="n"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="9" t="n"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="9" t="n"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="9" t="n"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="9" t="n"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="9" t="n"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="9" t="n"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="9" t="n"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="9" t="n"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="9" t="n"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="9" t="n"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="9" t="n"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="9" t="n"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="9" t="n"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="9" t="n"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="9" t="n"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="9" t="n"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="9" t="n"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="9" t="n"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="9" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="9" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="9" t="n"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="9" t="n"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="9" t="n"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="9" t="n"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="9" t="n"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="9" t="n"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="9" t="n"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="9" t="n"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="9" t="n"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="9" t="n"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="9" t="n"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="9" t="n"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="9" t="n"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="9" t="n"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="9" t="n"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="9" t="n"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="9" t="n"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="9" t="n"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="9" t="n"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="9" t="n"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="9" t="n"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="9" t="n"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="9" t="n"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="9" t="n"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="9" t="n"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="9" t="n"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="9" t="n"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="9" t="n"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="9" t="n"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="9" t="n"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="9" t="n"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="9" t="n"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="9" t="n"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="9" t="n"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="9" t="n"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="9" t="n"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="9" t="n"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="9" t="n"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="9" t="n"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="9" t="n"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="9" t="n"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="9" t="n"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="9" t="n"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="9" t="n"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="9" t="n"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="9" t="n"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="9" t="n"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="9" t="n"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="9" t="n"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="9" t="n"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="9" t="n"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="9" t="n"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="9" t="n"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="9" t="n"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="9" t="n"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="9" t="n"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="9" t="n"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="9" t="n"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="9" t="n"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="9" t="n"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="9" t="n"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="9" t="n"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="9" t="n"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="9" t="n"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="9" t="n"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="9" t="n"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="9" t="n"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="9" t="n"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="9" t="n"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="9" t="n"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="9" t="n"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="9" t="n"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="9" t="n"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="9" t="n"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="9" t="n"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="9" t="n"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="9" t="n"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="9" t="n"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="9" t="n"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="9" t="n"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="9" t="n"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="9" t="n"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="9" t="n"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="9" t="n"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="9" t="n"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="9" t="n"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="9" t="n"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="9" t="n"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="9" t="n"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="9" t="n"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="9" t="n"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="9" t="n"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="9" t="n"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="9" t="n"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="9" t="n"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="9" t="n"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="9" t="n"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="9" t="n"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="9" t="n"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="9" t="n"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="9" t="n"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="9" t="n"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="9" t="n"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="9" t="n"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="9" t="n"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="9" t="n"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="9" t="n"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="9" t="n"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="9" t="n"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="9" t="n"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="9" t="n"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="9" t="n"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="9" t="n"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="9" t="n"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="9" t="n"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="9" t="n"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="9" t="n"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="9" t="n"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="9" t="n"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="9" t="n"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="9" t="n"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="9" t="n"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="9" t="n"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="9" t="n"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="9" t="n"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="9" t="n"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="9" t="n"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="9" t="n"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="9" t="n"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="9" t="n"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="9" t="n"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="9" t="n"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="9" t="n"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="9" t="n"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="9" t="n"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="9" t="n"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="9" t="n"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="9" t="n"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="9" t="n"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="9" t="n"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="9" t="n"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="9" t="n"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="9" t="n"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="9" t="n"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="9" t="n"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="9" t="n"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="9" t="n"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="9" t="n"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="9" t="n"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="9" t="n"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="9" t="n"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="9" t="n"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="9" t="n"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="9" t="n"/>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="9" t="n"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="9" t="n"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="9" t="n"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="9" t="n"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="9" t="n"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="9" t="n"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="9" t="n"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="9" t="n"/>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="9" t="n"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="9" t="n"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="9" t="n"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="9" t="n"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="9" t="n"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="9" t="n"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="9" t="n"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="9" t="n"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="9" t="n"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="9" t="n"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="9" t="n"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="9" t="n"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="9" t="n"/>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="9" t="n"/>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="9" t="n"/>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="9" t="n"/>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="9" t="n"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="9" t="n"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="9" t="n"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="9" t="n"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="9" t="n"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="9" t="n"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="9" t="n"/>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="9" t="n"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="9" t="n"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="9" t="n"/>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="9" t="n"/>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="9" t="n"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="9" t="n"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="9" t="n"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="9" t="n"/>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="9" t="n"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="9" t="n"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="9" t="n"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="9" t="n"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="9" t="n"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="9" t="n"/>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="9" t="n"/>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="9" t="n"/>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="9" t="n"/>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="9" t="n"/>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="9" t="n"/>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="9" t="n"/>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="9" t="n"/>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="9" t="n"/>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="9" t="n"/>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="9" t="n"/>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="9" t="n"/>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="9" t="n"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="9" t="n"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="9" t="n"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="9" t="n"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="9" t="n"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="9" t="n"/>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="9" t="n"/>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="9" t="n"/>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="9" t="n"/>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="9" t="n"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="9" t="n"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="9" t="n"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="9" t="n"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="9" t="n"/>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="9" t="n"/>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="9" t="n"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="9" t="n"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="9" t="n"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="9" t="n"/>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="9" t="n"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="9" t="n"/>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="9" t="n"/>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="9" t="n"/>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="9" t="n"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="9" t="n"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="9" t="n"/>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="9" t="n"/>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="9" t="n"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="9" t="n"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="9" t="n"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="9" t="n"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="9" t="n"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="9" t="n"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="9" t="n"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="9" t="n"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="9" t="n"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="9" t="n"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="9" t="n"/>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="9" t="n"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="9" t="n"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="9" t="n"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="9" t="n"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="9" t="n"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="9" t="n"/>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="9" t="n"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="9" t="n"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="9" t="n"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="9" t="n"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="9" t="n"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="9" t="n"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="9" t="n"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="9" t="n"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="9" t="n"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="9" t="n"/>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="9" t="n"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="9" t="n"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="9" t="n"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="9" t="n"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="9" t="n"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="9" t="n"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="9" t="n"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="9" t="n"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="9" t="n"/>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="9" t="n"/>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="9" t="n"/>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="9" t="n"/>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="9" t="n"/>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="9" t="n"/>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="9" t="n"/>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="9" t="n"/>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="9" t="n"/>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="9" t="n"/>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="9" t="n"/>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="9" t="n"/>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="9" t="n"/>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="9" t="n"/>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="9" t="n"/>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="9" t="n"/>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="9" t="n"/>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="9" t="n"/>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="9" t="n"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="9" t="n"/>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="9" t="n"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="9" t="n"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="9" t="n"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="9" t="n"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="9" t="n"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="9" t="n"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="9" t="n"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="9" t="n"/>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="9" t="n"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="9" t="n"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="9" t="n"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="9" t="n"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="9" t="n"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="9" t="n"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="9" t="n"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="9" t="n"/>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="9" t="n"/>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="9" t="n"/>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="9" t="n"/>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="9" t="n"/>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="9" t="n"/>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="9" t="n"/>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="9" t="n"/>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="9" t="n"/>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="9" t="n"/>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="9" t="n"/>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="9" t="n"/>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="9" t="n"/>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="9" t="n"/>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="9" t="n"/>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="9" t="n"/>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="9" t="n"/>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="9" t="n"/>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="9" t="n"/>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="9" t="n"/>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="9" t="n"/>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="9" t="n"/>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="9" t="n"/>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="9" t="n"/>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="9" t="n"/>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="9" t="n"/>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="9" t="n"/>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="9" t="n"/>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="9" t="n"/>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="9" t="n"/>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="9" t="n"/>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="9" t="n"/>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="9" t="n"/>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="9" t="n"/>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="9" t="n"/>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="9" t="n"/>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="9" t="n"/>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="9" t="n"/>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="9" t="n"/>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="9" t="n"/>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="9" t="n"/>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="9" t="n"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="9" t="n"/>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="9" t="n"/>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="9" t="n"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="9" t="n"/>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="9" t="n"/>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="9" t="n"/>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="9" t="n"/>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="9" t="n"/>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="9" t="n"/>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="9" t="n"/>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="9" t="n"/>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="9" t="n"/>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="9" t="n"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="9" t="n"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="9" t="n"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="9" t="n"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="9" t="n"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="9" t="n"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="9" t="n"/>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="9" t="n"/>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="9" t="n"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="9" t="n"/>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="9" t="n"/>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="9" t="n"/>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="9" t="n"/>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="9" t="n"/>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="9" t="n"/>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="9" t="n"/>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="9" t="n"/>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="9" t="n"/>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="9" t="n"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="9" t="n"/>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="9" t="n"/>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="9" t="n"/>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="9" t="n"/>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="9" t="n"/>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="9" t="n"/>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="9" t="n"/>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="9" t="n"/>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="9" t="n"/>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="9" t="n"/>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="9" t="n"/>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="9" t="n"/>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="9" t="n"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="9" t="n"/>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="9" t="n"/>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="9" t="n"/>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="9" t="n"/>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="9" t="n"/>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="9" t="n"/>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="9" t="n"/>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="9" t="n"/>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="9" t="n"/>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="9" t="n"/>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="9" t="n"/>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="9" t="n"/>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="9" t="n"/>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="9" t="n"/>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="9" t="n"/>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="9" t="n"/>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="9" t="n"/>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="9" t="n"/>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="9" t="n"/>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="9" t="n"/>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="9" t="n"/>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="9" t="n"/>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="9" t="n"/>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="9" t="n"/>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="9" t="n"/>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="9" t="n"/>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="9" t="n"/>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="9" t="n"/>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="9" t="n"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="9" t="n"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="9" t="n"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="9" t="n"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="9" t="n"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="9" t="n"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="9" t="n"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="9" t="n"/>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="9" t="n"/>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="9" t="n"/>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="9" t="n"/>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="9" t="n"/>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="9" t="n"/>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="9" t="n"/>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="9" t="n"/>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="9" t="n"/>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="9" t="n"/>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="9" t="n"/>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="9" t="n"/>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="9" t="n"/>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="9" t="n"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="9" t="n"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="9" t="n"/>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="9" t="n"/>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="9" t="n"/>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="9" t="n"/>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="9" t="n"/>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="9" t="n"/>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="9" t="n"/>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="9" t="n"/>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="9" t="n"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="9" t="n"/>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="9" t="n"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="9" t="n"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="9" t="n"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="9" t="n"/>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="9" t="n"/>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="9" t="n"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="9" t="n"/>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="9" t="n"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="9" t="n"/>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="9" t="n"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="9" t="n"/>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="9" t="n"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="9" t="n"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="9" t="n"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="9" t="n"/>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="9" t="n"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="9" t="n"/>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="9" t="n"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="9" t="n"/>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="9" t="n"/>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="9" t="n"/>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="9" t="n"/>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="9" t="n"/>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="9" t="n"/>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="9" t="n"/>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="9" t="n"/>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="9" t="n"/>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="9" t="n"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="9" t="n"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="9" t="n"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="9" t="n"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="9" t="n"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="9" t="n"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="9" t="n"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="9" t="n"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="9" t="n"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="9" t="n"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="9" t="n"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="9" t="n"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="9" t="n"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="9" t="n"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="9" t="n"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="9" t="n"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="9" t="n"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="9" t="n"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="9" t="n"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="9" t="n"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="9" t="n"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="9" t="n"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="9" t="n"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="9" t="n"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="9" t="n"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="9" t="n"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="9" t="n"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="9" t="n"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="9" t="n"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="9" t="n"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="9" t="n"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="9" t="n"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="9" t="n"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="9" t="n"/>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="9" t="n"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="9" t="n"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="9" t="n"/>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="9" t="n"/>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="9" t="n"/>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="9" t="n"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="9" t="n"/>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="9" t="n"/>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="9" t="n"/>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="9" t="n"/>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="9" t="n"/>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="9" t="n"/>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="9" t="n"/>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="9" t="n"/>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="9" t="n"/>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="9" t="n"/>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="9" t="n"/>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="9" t="n"/>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="9" t="n"/>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="9" t="n"/>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="9" t="n"/>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="9" t="n"/>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="9" t="n"/>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="9" t="n"/>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="9" t="n"/>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="9" t="n"/>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="9" t="n"/>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="9" t="n"/>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="9" t="n"/>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="9" t="n"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="9" t="n"/>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="9" t="n"/>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="9" t="n"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="9" t="n"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="9" t="n"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="9" t="n"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="9" t="n"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="9" t="n"/>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="9" t="n"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="9" t="n"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="9" t="n"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="9" t="n"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="9" t="n"/>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="9" t="n"/>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="9" t="n"/>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="9" t="n"/>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="9" t="n"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="9" t="n"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="9" t="n"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="9" t="n"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="9" t="n"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="9" t="n"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="9" t="n"/>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="9" t="n"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="9" t="n"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="9" t="n"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="9" t="n"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="9" t="n"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="9" t="n"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="9" t="n"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="9" t="n"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="9" t="n"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="9" t="n"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="9" t="n"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="9" t="n"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="9" t="n"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="9" t="n"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="9" t="n"/>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="9" t="n"/>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="9" t="n"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="9" t="n"/>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="9" t="n"/>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="9" t="n"/>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="9" t="n"/>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="9" t="n"/>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="9" t="n"/>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="9" t="n"/>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="9" t="n"/>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="9" t="n"/>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="9" t="n"/>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="9" t="n"/>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="9" t="n"/>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="9" t="n"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="9" t="n"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="9" t="n"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="9" t="n"/>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="9" t="n"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="9" t="n"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="9" t="n"/>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="9" t="n"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="9" t="n"/>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="9" t="n"/>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="9" t="n"/>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="9" t="n"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="9" t="n"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="9" t="n"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="9" t="n"/>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="9" t="n"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="9" t="n"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="9" t="n"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="9" t="n"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="9" t="n"/>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="9" t="n"/>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="9" t="n"/>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="9" t="n"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="9" t="n"/>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="9" t="n"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="9" t="n"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="9" t="n"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="9" t="n"/>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="9" t="n"/>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="9" t="n"/>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="9" t="n"/>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="9" t="n"/>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="9" t="n"/>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="9" t="n"/>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="9" t="n"/>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="9" t="n"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="9" t="n"/>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="9" t="n"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="9" t="n"/>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="9" t="n"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="9" t="n"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="9" t="n"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="9" t="n"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="9" t="n"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="9" t="n"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="9" t="n"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="9" t="n"/>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="9" t="n"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="9" t="n"/>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="9" t="n"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="9" t="n"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="9" t="n"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="9" t="n"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="9" t="n"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="9" t="n"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="9" t="n"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="9" t="n"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="9" t="n"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="9" t="n"/>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="9" t="n"/>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="9" t="n"/>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="9" t="n"/>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="9" t="n"/>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="9" t="n"/>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="9" t="n"/>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="9" t="n"/>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="9" t="n"/>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="9" t="n"/>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="9" t="n"/>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="9" t="n"/>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="9" t="n"/>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="9" t="n"/>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="9" t="n"/>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="9" t="n"/>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="9" t="n"/>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="9" t="n"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="9" t="n"/>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="9" t="n"/>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="9" t="n"/>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="9" t="n"/>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="9" t="n"/>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="9" t="n"/>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="9" t="n"/>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="9" t="n"/>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="9" t="n"/>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="9" t="n"/>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="9" t="n"/>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="9" t="n"/>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="9" t="n"/>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="9" t="n"/>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="9" t="n"/>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="9" t="n"/>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="9" t="n"/>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="9" t="n"/>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="9" t="n"/>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="9" t="n"/>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="9" t="n"/>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="9" t="n"/>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="9" t="n"/>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="9" t="n"/>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="9" t="n"/>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="9" t="n"/>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="9" t="n"/>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="9" t="n"/>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="9" t="n"/>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="9" t="n"/>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="9" t="n"/>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="9" t="n"/>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="9" t="n"/>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="9" t="n"/>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="9" t="n"/>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="9" t="n"/>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="9" t="n"/>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="9" t="n"/>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="9" t="n"/>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="9" t="n"/>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="9" t="n"/>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="9" t="n"/>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="9" t="n"/>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="9" t="n"/>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="9" t="n"/>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="9" t="n"/>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="9" t="n"/>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="9" t="n"/>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="9" t="n"/>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="9" t="n"/>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="9" t="n"/>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="9" t="n"/>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="9" t="n"/>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="9" t="n"/>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="9" t="n"/>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="9" t="n"/>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="9" t="n"/>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="9" t="n"/>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="9" t="n"/>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="9" t="n"/>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="9" t="n"/>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="9" t="n"/>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="9" t="n"/>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="9" t="n"/>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="9" t="n"/>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="9" t="n"/>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="9" t="n"/>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="9" t="n"/>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="9" t="n"/>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="9" t="n"/>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="9" t="n"/>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="9" t="n"/>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="9" t="n"/>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="9" t="n"/>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="9" t="n"/>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="9" t="n"/>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="9" t="n"/>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="9" t="n"/>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="9" t="n"/>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="9" t="n"/>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="9" t="n"/>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="9" t="n"/>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="9" t="n"/>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="9" t="n"/>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="9" t="n"/>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="9" t="n"/>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="9" t="n"/>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="9" t="n"/>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="9" t="n"/>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="9" t="n"/>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="9" t="n"/>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="9" t="n"/>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="9" t="n"/>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="9" t="n"/>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="9" t="n"/>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="9" t="n"/>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="9" t="n"/>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="9" t="n"/>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="9" t="n"/>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="9" t="n"/>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="9" t="n"/>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="9" t="n"/>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="9" t="n"/>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="9" t="n"/>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="9" t="n"/>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="9" t="n"/>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="9" t="n"/>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="9" t="n"/>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="9" t="n"/>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="9" t="n"/>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="9" t="n"/>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="9" t="n"/>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="9" t="n"/>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="9" t="n"/>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="9" t="n"/>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="9" t="n"/>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="9" t="n"/>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="9" t="n"/>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="9" t="n"/>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="9" t="n"/>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="9" t="n"/>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="9" t="n"/>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="9" t="n"/>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="9" t="n"/>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="9" t="n"/>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="9" t="n"/>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="9" t="n"/>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="9" t="n"/>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="9" t="n"/>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="9" t="n"/>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="9" t="n"/>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="9" t="n"/>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="9" t="n"/>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="9" t="n"/>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="9" t="n"/>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="9" t="n"/>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="9" t="n"/>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="9" t="n"/>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="9" t="n"/>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="9" t="n"/>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="9" t="n"/>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="9" t="n"/>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="9" t="n"/>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="9" t="n"/>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="9" t="n"/>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="9" t="n"/>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="9" t="n"/>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="9" t="n"/>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="9" t="n"/>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="9" t="n"/>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="9" t="n"/>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="9" t="n"/>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="9" t="n"/>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="9" t="n"/>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="9" t="n"/>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="9" t="n"/>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="9" t="n"/>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="9" t="n"/>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="9" t="n"/>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="9" t="n"/>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="9" t="n"/>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="9" t="n"/>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="9" t="n"/>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="9" t="n"/>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="9" t="n"/>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="9" t="n"/>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="9" t="n"/>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="9" t="n"/>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="9" t="n"/>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="9" t="n"/>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="9" t="n"/>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="9" t="n"/>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="9" t="n"/>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="9" t="n"/>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="9" t="n"/>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="9" t="n"/>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="9" t="n"/>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="9" t="n"/>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="9" t="n"/>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="9" t="n"/>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="9" t="n"/>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="9" t="n"/>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="9" t="n"/>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="9" t="n"/>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="9" t="n"/>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="9" t="n"/>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="9" t="n"/>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="9" t="n"/>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="9" t="n"/>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="9" t="n"/>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="9" t="n"/>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="9" t="n"/>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="9" t="n"/>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="9" t="n"/>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="9" t="n"/>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="9" t="n"/>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="9" t="n"/>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="9" t="n"/>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="9" t="n"/>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="9" t="n"/>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="9" t="n"/>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="9" t="n"/>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="9" t="n"/>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="9" t="n"/>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="9" t="n"/>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="9" t="n"/>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="9" t="n"/>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="9" t="n"/>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="9" t="n"/>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="9" t="n"/>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="9" t="n"/>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="9" t="n"/>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="9" t="n"/>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="9" t="n"/>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="9" t="n"/>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="9" t="n"/>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="9" t="n"/>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="9" t="n"/>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="9" t="n"/>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="9" t="n"/>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="9" t="n"/>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="9" t="n"/>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="9" t="n"/>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="9" t="n"/>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="9" t="n"/>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="9" t="n"/>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="9" t="n"/>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="9" t="n"/>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="9" t="n"/>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="9" t="n"/>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="9" t="n"/>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="9" t="n"/>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="9" t="n"/>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="9" t="n"/>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="9" t="n"/>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="9" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="공정순서 오류" error="1 이상의 정수를 입력하세요." type="whole" operator="greaterThan">
@@ -696,7 +6674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="B2:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -829,6 +6807,13 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>※ TM-NO 열은 '텍스트 서식'으로 지정되어 있습니다. 서식을 바꾸거나 다른 파일에서 붙여넣을 때 날짜로 변환되지 않았는지 확인하세요. 날짜로 변환된 값은 업로드 시 오류로 거부됩니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/제품마스터_양식.xlsx
+++ b/templates/제품마스터_양식.xlsx
@@ -103,10 +103,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -117,8 +119,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,6141 +522,6141 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TM-10001</t>
+          <t>1545-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TM-10001</t>
+          <t>1545-01</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TM-10001</t>
+          <t>1545-01</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>310</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TM-10001</t>
+          <t>1545-01</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TM-20002</t>
+          <t>2233-02</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>오일펌프 로터</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TM-20002</t>
+          <t>2233-02</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>오일펌프 로터</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TM-20002</t>
+          <t>2233-02</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>오일펌프 로터</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>228</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
+      <c r="A9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
+      <c r="A11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
+      <c r="A12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
+      <c r="A13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
+      <c r="A14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
+      <c r="A15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
+      <c r="A16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
+      <c r="A17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
+      <c r="A19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
+      <c r="A20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
+      <c r="A21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
+      <c r="A22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
+      <c r="A23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
+      <c r="A24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
+      <c r="A25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
+      <c r="A26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
+      <c r="A27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
+      <c r="A28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
+      <c r="A29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
+      <c r="A30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n"/>
+      <c r="A31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
+      <c r="A32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n"/>
+      <c r="A33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n"/>
+      <c r="A34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n"/>
+      <c r="A35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n"/>
+      <c r="A36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n"/>
+      <c r="A37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
+      <c r="A38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n"/>
+      <c r="A39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n"/>
+      <c r="A40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n"/>
+      <c r="A41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
+      <c r="A42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n"/>
+      <c r="A43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
+      <c r="A44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n"/>
+      <c r="A45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
+      <c r="A46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n"/>
+      <c r="A47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n"/>
+      <c r="A48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n"/>
+      <c r="A49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
+      <c r="A50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n"/>
+      <c r="A51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n"/>
+      <c r="A52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="n"/>
+      <c r="A53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n"/>
+      <c r="A54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n"/>
+      <c r="A55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n"/>
+      <c r="A56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="n"/>
+      <c r="A57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="n"/>
+      <c r="A58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n"/>
+      <c r="A59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="n"/>
+      <c r="A60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="n"/>
+      <c r="A61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n"/>
+      <c r="A62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="n"/>
+      <c r="A63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n"/>
+      <c r="A64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n"/>
+      <c r="A65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n"/>
+      <c r="A66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="n"/>
+      <c r="A67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n"/>
+      <c r="A68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="n"/>
+      <c r="A69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n"/>
+      <c r="A70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="n"/>
+      <c r="A71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n"/>
+      <c r="A72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="n"/>
+      <c r="A73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n"/>
+      <c r="A74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="n"/>
+      <c r="A75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="n"/>
+      <c r="A76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="n"/>
+      <c r="A77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="n"/>
+      <c r="A78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="n"/>
+      <c r="A79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="n"/>
+      <c r="A80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="n"/>
+      <c r="A81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="n"/>
+      <c r="A82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="n"/>
+      <c r="A83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="n"/>
+      <c r="A84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="n"/>
+      <c r="A85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n"/>
+      <c r="A86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="n"/>
+      <c r="A87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="n"/>
+      <c r="A88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="n"/>
+      <c r="A89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n"/>
+      <c r="A90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="n"/>
+      <c r="A91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="n"/>
+      <c r="A92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="n"/>
+      <c r="A93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="n"/>
+      <c r="A94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="n"/>
+      <c r="A95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="n"/>
+      <c r="A96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="n"/>
+      <c r="A97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="n"/>
+      <c r="A98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="n"/>
+      <c r="A99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="n"/>
+      <c r="A100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="n"/>
+      <c r="A101" s="5" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="n"/>
+      <c r="A102" s="5" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="n"/>
+      <c r="A103" s="5" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="n"/>
+      <c r="A104" s="5" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="n"/>
+      <c r="A105" s="5" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="n"/>
+      <c r="A106" s="5" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="n"/>
+      <c r="A107" s="5" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="n"/>
+      <c r="A108" s="5" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="n"/>
+      <c r="A109" s="5" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="n"/>
+      <c r="A110" s="5" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="n"/>
+      <c r="A111" s="5" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="n"/>
+      <c r="A112" s="5" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="n"/>
+      <c r="A113" s="5" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="n"/>
+      <c r="A114" s="5" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="n"/>
+      <c r="A115" s="5" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="n"/>
+      <c r="A116" s="5" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="n"/>
+      <c r="A117" s="5" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="n"/>
+      <c r="A118" s="5" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="n"/>
+      <c r="A119" s="5" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="n"/>
+      <c r="A120" s="5" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="n"/>
+      <c r="A121" s="5" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="n"/>
+      <c r="A122" s="5" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="n"/>
+      <c r="A123" s="5" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="n"/>
+      <c r="A124" s="5" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="n"/>
+      <c r="A125" s="5" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="n"/>
+      <c r="A126" s="5" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="n"/>
+      <c r="A127" s="5" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="n"/>
+      <c r="A128" s="5" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="n"/>
+      <c r="A129" s="5" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="n"/>
+      <c r="A130" s="5" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="n"/>
+      <c r="A131" s="5" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="n"/>
+      <c r="A132" s="5" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="n"/>
+      <c r="A133" s="5" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="n"/>
+      <c r="A134" s="5" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="n"/>
+      <c r="A135" s="5" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="n"/>
+      <c r="A136" s="5" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="n"/>
+      <c r="A137" s="5" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="n"/>
+      <c r="A138" s="5" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="n"/>
+      <c r="A139" s="5" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="n"/>
+      <c r="A140" s="5" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="n"/>
+      <c r="A141" s="5" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="n"/>
+      <c r="A142" s="5" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="n"/>
+      <c r="A143" s="5" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="n"/>
+      <c r="A144" s="5" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="n"/>
+      <c r="A145" s="5" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="n"/>
+      <c r="A146" s="5" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="n"/>
+      <c r="A147" s="5" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="n"/>
+      <c r="A148" s="5" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="n"/>
+      <c r="A149" s="5" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="9" t="n"/>
+      <c r="A150" s="5" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="n"/>
+      <c r="A151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="n"/>
+      <c r="A152" s="5" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="n"/>
+      <c r="A153" s="5" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="n"/>
+      <c r="A154" s="5" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="n"/>
+      <c r="A155" s="5" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="9" t="n"/>
+      <c r="A156" s="5" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="n"/>
+      <c r="A157" s="5" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="n"/>
+      <c r="A158" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="n"/>
+      <c r="A159" s="5" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="n"/>
+      <c r="A160" s="5" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="n"/>
+      <c r="A161" s="5" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="n"/>
+      <c r="A162" s="5" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="n"/>
+      <c r="A163" s="5" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="n"/>
+      <c r="A164" s="5" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="n"/>
+      <c r="A165" s="5" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="9" t="n"/>
+      <c r="A166" s="5" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="n"/>
+      <c r="A167" s="5" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="9" t="n"/>
+      <c r="A168" s="5" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="n"/>
+      <c r="A169" s="5" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="9" t="n"/>
+      <c r="A170" s="5" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="n"/>
+      <c r="A171" s="5" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="9" t="n"/>
+      <c r="A172" s="5" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="9" t="n"/>
+      <c r="A173" s="5" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="9" t="n"/>
+      <c r="A174" s="5" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="9" t="n"/>
+      <c r="A175" s="5" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="9" t="n"/>
+      <c r="A176" s="5" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="n"/>
+      <c r="A177" s="5" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="n"/>
+      <c r="A178" s="5" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="n"/>
+      <c r="A179" s="5" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="9" t="n"/>
+      <c r="A180" s="5" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="n"/>
+      <c r="A181" s="5" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="9" t="n"/>
+      <c r="A182" s="5" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="9" t="n"/>
+      <c r="A183" s="5" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="9" t="n"/>
+      <c r="A184" s="5" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="9" t="n"/>
+      <c r="A185" s="5" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="9" t="n"/>
+      <c r="A186" s="5" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="9" t="n"/>
+      <c r="A187" s="5" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="9" t="n"/>
+      <c r="A188" s="5" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="9" t="n"/>
+      <c r="A189" s="5" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="9" t="n"/>
+      <c r="A190" s="5" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="9" t="n"/>
+      <c r="A191" s="5" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="9" t="n"/>
+      <c r="A192" s="5" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="9" t="n"/>
+      <c r="A193" s="5" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="9" t="n"/>
+      <c r="A194" s="5" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="9" t="n"/>
+      <c r="A195" s="5" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="9" t="n"/>
+      <c r="A196" s="5" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="9" t="n"/>
+      <c r="A197" s="5" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="9" t="n"/>
+      <c r="A198" s="5" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="9" t="n"/>
+      <c r="A199" s="5" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="9" t="n"/>
+      <c r="A200" s="5" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="9" t="n"/>
+      <c r="A201" s="5" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="9" t="n"/>
+      <c r="A202" s="5" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="9" t="n"/>
+      <c r="A203" s="5" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="9" t="n"/>
+      <c r="A204" s="5" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="9" t="n"/>
+      <c r="A205" s="5" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="9" t="n"/>
+      <c r="A206" s="5" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="9" t="n"/>
+      <c r="A207" s="5" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="9" t="n"/>
+      <c r="A208" s="5" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="9" t="n"/>
+      <c r="A209" s="5" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="9" t="n"/>
+      <c r="A210" s="5" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="9" t="n"/>
+      <c r="A211" s="5" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="9" t="n"/>
+      <c r="A212" s="5" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="9" t="n"/>
+      <c r="A213" s="5" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="9" t="n"/>
+      <c r="A214" s="5" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="9" t="n"/>
+      <c r="A215" s="5" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="9" t="n"/>
+      <c r="A216" s="5" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="9" t="n"/>
+      <c r="A217" s="5" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="9" t="n"/>
+      <c r="A218" s="5" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="9" t="n"/>
+      <c r="A219" s="5" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="9" t="n"/>
+      <c r="A220" s="5" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="9" t="n"/>
+      <c r="A221" s="5" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="9" t="n"/>
+      <c r="A222" s="5" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="9" t="n"/>
+      <c r="A223" s="5" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="9" t="n"/>
+      <c r="A224" s="5" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="9" t="n"/>
+      <c r="A225" s="5" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="9" t="n"/>
+      <c r="A226" s="5" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="9" t="n"/>
+      <c r="A227" s="5" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="9" t="n"/>
+      <c r="A228" s="5" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="9" t="n"/>
+      <c r="A229" s="5" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="9" t="n"/>
+      <c r="A230" s="5" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="9" t="n"/>
+      <c r="A231" s="5" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="9" t="n"/>
+      <c r="A232" s="5" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="9" t="n"/>
+      <c r="A233" s="5" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="9" t="n"/>
+      <c r="A234" s="5" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="9" t="n"/>
+      <c r="A235" s="5" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="9" t="n"/>
+      <c r="A236" s="5" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="9" t="n"/>
+      <c r="A237" s="5" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="9" t="n"/>
+      <c r="A238" s="5" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="9" t="n"/>
+      <c r="A239" s="5" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="9" t="n"/>
+      <c r="A240" s="5" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="9" t="n"/>
+      <c r="A241" s="5" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="9" t="n"/>
+      <c r="A242" s="5" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="9" t="n"/>
+      <c r="A243" s="5" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="9" t="n"/>
+      <c r="A244" s="5" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="9" t="n"/>
+      <c r="A245" s="5" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="9" t="n"/>
+      <c r="A246" s="5" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="9" t="n"/>
+      <c r="A247" s="5" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="9" t="n"/>
+      <c r="A248" s="5" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="9" t="n"/>
+      <c r="A249" s="5" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="9" t="n"/>
+      <c r="A250" s="5" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="9" t="n"/>
+      <c r="A251" s="5" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="9" t="n"/>
+      <c r="A252" s="5" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="9" t="n"/>
+      <c r="A253" s="5" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="9" t="n"/>
+      <c r="A254" s="5" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="9" t="n"/>
+      <c r="A255" s="5" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="9" t="n"/>
+      <c r="A256" s="5" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="9" t="n"/>
+      <c r="A257" s="5" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="9" t="n"/>
+      <c r="A258" s="5" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="9" t="n"/>
+      <c r="A259" s="5" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="9" t="n"/>
+      <c r="A260" s="5" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="9" t="n"/>
+      <c r="A261" s="5" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="9" t="n"/>
+      <c r="A262" s="5" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="9" t="n"/>
+      <c r="A263" s="5" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="9" t="n"/>
+      <c r="A264" s="5" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="9" t="n"/>
+      <c r="A265" s="5" t="n"/>
     </row>
     <row r="266">
-      <c r="A266" s="9" t="n"/>
+      <c r="A266" s="5" t="n"/>
     </row>
     <row r="267">
-      <c r="A267" s="9" t="n"/>
+      <c r="A267" s="5" t="n"/>
     </row>
     <row r="268">
-      <c r="A268" s="9" t="n"/>
+      <c r="A268" s="5" t="n"/>
     </row>
     <row r="269">
-      <c r="A269" s="9" t="n"/>
+      <c r="A269" s="5" t="n"/>
     </row>
     <row r="270">
-      <c r="A270" s="9" t="n"/>
+      <c r="A270" s="5" t="n"/>
     </row>
     <row r="271">
-      <c r="A271" s="9" t="n"/>
+      <c r="A271" s="5" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="9" t="n"/>
+      <c r="A272" s="5" t="n"/>
     </row>
     <row r="273">
-      <c r="A273" s="9" t="n"/>
+      <c r="A273" s="5" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="9" t="n"/>
+      <c r="A274" s="5" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="9" t="n"/>
+      <c r="A275" s="5" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="9" t="n"/>
+      <c r="A276" s="5" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="9" t="n"/>
+      <c r="A277" s="5" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="9" t="n"/>
+      <c r="A278" s="5" t="n"/>
     </row>
     <row r="279">
-      <c r="A279" s="9" t="n"/>
+      <c r="A279" s="5" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="9" t="n"/>
+      <c r="A280" s="5" t="n"/>
     </row>
     <row r="281">
-      <c r="A281" s="9" t="n"/>
+      <c r="A281" s="5" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="9" t="n"/>
+      <c r="A282" s="5" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="9" t="n"/>
+      <c r="A283" s="5" t="n"/>
     </row>
     <row r="284">
-      <c r="A284" s="9" t="n"/>
+      <c r="A284" s="5" t="n"/>
     </row>
     <row r="285">
-      <c r="A285" s="9" t="n"/>
+      <c r="A285" s="5" t="n"/>
     </row>
     <row r="286">
-      <c r="A286" s="9" t="n"/>
+      <c r="A286" s="5" t="n"/>
     </row>
     <row r="287">
-      <c r="A287" s="9" t="n"/>
+      <c r="A287" s="5" t="n"/>
     </row>
     <row r="288">
-      <c r="A288" s="9" t="n"/>
+      <c r="A288" s="5" t="n"/>
     </row>
     <row r="289">
-      <c r="A289" s="9" t="n"/>
+      <c r="A289" s="5" t="n"/>
     </row>
     <row r="290">
-      <c r="A290" s="9" t="n"/>
+      <c r="A290" s="5" t="n"/>
     </row>
     <row r="291">
-      <c r="A291" s="9" t="n"/>
+      <c r="A291" s="5" t="n"/>
     </row>
     <row r="292">
-      <c r="A292" s="9" t="n"/>
+      <c r="A292" s="5" t="n"/>
     </row>
     <row r="293">
-      <c r="A293" s="9" t="n"/>
+      <c r="A293" s="5" t="n"/>
     </row>
     <row r="294">
-      <c r="A294" s="9" t="n"/>
+      <c r="A294" s="5" t="n"/>
     </row>
     <row r="295">
-      <c r="A295" s="9" t="n"/>
+      <c r="A295" s="5" t="n"/>
     </row>
     <row r="296">
-      <c r="A296" s="9" t="n"/>
+      <c r="A296" s="5" t="n"/>
     </row>
     <row r="297">
-      <c r="A297" s="9" t="n"/>
+      <c r="A297" s="5" t="n"/>
     </row>
     <row r="298">
-      <c r="A298" s="9" t="n"/>
+      <c r="A298" s="5" t="n"/>
     </row>
     <row r="299">
-      <c r="A299" s="9" t="n"/>
+      <c r="A299" s="5" t="n"/>
     </row>
     <row r="300">
-      <c r="A300" s="9" t="n"/>
+      <c r="A300" s="5" t="n"/>
     </row>
     <row r="301">
-      <c r="A301" s="9" t="n"/>
+      <c r="A301" s="5" t="n"/>
     </row>
     <row r="302">
-      <c r="A302" s="9" t="n"/>
+      <c r="A302" s="5" t="n"/>
     </row>
     <row r="303">
-      <c r="A303" s="9" t="n"/>
+      <c r="A303" s="5" t="n"/>
     </row>
     <row r="304">
-      <c r="A304" s="9" t="n"/>
+      <c r="A304" s="5" t="n"/>
     </row>
     <row r="305">
-      <c r="A305" s="9" t="n"/>
+      <c r="A305" s="5" t="n"/>
     </row>
     <row r="306">
-      <c r="A306" s="9" t="n"/>
+      <c r="A306" s="5" t="n"/>
     </row>
     <row r="307">
-      <c r="A307" s="9" t="n"/>
+      <c r="A307" s="5" t="n"/>
     </row>
     <row r="308">
-      <c r="A308" s="9" t="n"/>
+      <c r="A308" s="5" t="n"/>
     </row>
     <row r="309">
-      <c r="A309" s="9" t="n"/>
+      <c r="A309" s="5" t="n"/>
     </row>
     <row r="310">
-      <c r="A310" s="9" t="n"/>
+      <c r="A310" s="5" t="n"/>
     </row>
     <row r="311">
-      <c r="A311" s="9" t="n"/>
+      <c r="A311" s="5" t="n"/>
     </row>
     <row r="312">
-      <c r="A312" s="9" t="n"/>
+      <c r="A312" s="5" t="n"/>
     </row>
     <row r="313">
-      <c r="A313" s="9" t="n"/>
+      <c r="A313" s="5" t="n"/>
     </row>
     <row r="314">
-      <c r="A314" s="9" t="n"/>
+      <c r="A314" s="5" t="n"/>
     </row>
     <row r="315">
-      <c r="A315" s="9" t="n"/>
+      <c r="A315" s="5" t="n"/>
     </row>
     <row r="316">
-      <c r="A316" s="9" t="n"/>
+      <c r="A316" s="5" t="n"/>
     </row>
     <row r="317">
-      <c r="A317" s="9" t="n"/>
+      <c r="A317" s="5" t="n"/>
     </row>
     <row r="318">
-      <c r="A318" s="9" t="n"/>
+      <c r="A318" s="5" t="n"/>
     </row>
     <row r="319">
-      <c r="A319" s="9" t="n"/>
+      <c r="A319" s="5" t="n"/>
     </row>
     <row r="320">
-      <c r="A320" s="9" t="n"/>
+      <c r="A320" s="5" t="n"/>
     </row>
     <row r="321">
-      <c r="A321" s="9" t="n"/>
+      <c r="A321" s="5" t="n"/>
     </row>
     <row r="322">
-      <c r="A322" s="9" t="n"/>
+      <c r="A322" s="5" t="n"/>
     </row>
     <row r="323">
-      <c r="A323" s="9" t="n"/>
+      <c r="A323" s="5" t="n"/>
     </row>
     <row r="324">
-      <c r="A324" s="9" t="n"/>
+      <c r="A324" s="5" t="n"/>
     </row>
     <row r="325">
-      <c r="A325" s="9" t="n"/>
+      <c r="A325" s="5" t="n"/>
     </row>
     <row r="326">
-      <c r="A326" s="9" t="n"/>
+      <c r="A326" s="5" t="n"/>
     </row>
     <row r="327">
-      <c r="A327" s="9" t="n"/>
+      <c r="A327" s="5" t="n"/>
     </row>
     <row r="328">
-      <c r="A328" s="9" t="n"/>
+      <c r="A328" s="5" t="n"/>
     </row>
     <row r="329">
-      <c r="A329" s="9" t="n"/>
+      <c r="A329" s="5" t="n"/>
     </row>
     <row r="330">
-      <c r="A330" s="9" t="n"/>
+      <c r="A330" s="5" t="n"/>
     </row>
     <row r="331">
-      <c r="A331" s="9" t="n"/>
+      <c r="A331" s="5" t="n"/>
     </row>
     <row r="332">
-      <c r="A332" s="9" t="n"/>
+      <c r="A332" s="5" t="n"/>
     </row>
     <row r="333">
-      <c r="A333" s="9" t="n"/>
+      <c r="A333" s="5" t="n"/>
     </row>
     <row r="334">
-      <c r="A334" s="9" t="n"/>
+      <c r="A334" s="5" t="n"/>
     </row>
     <row r="335">
-      <c r="A335" s="9" t="n"/>
+      <c r="A335" s="5" t="n"/>
     </row>
     <row r="336">
-      <c r="A336" s="9" t="n"/>
+      <c r="A336" s="5" t="n"/>
     </row>
     <row r="337">
-      <c r="A337" s="9" t="n"/>
+      <c r="A337" s="5" t="n"/>
     </row>
     <row r="338">
-      <c r="A338" s="9" t="n"/>
+      <c r="A338" s="5" t="n"/>
     </row>
     <row r="339">
-      <c r="A339" s="9" t="n"/>
+      <c r="A339" s="5" t="n"/>
     </row>
     <row r="340">
-      <c r="A340" s="9" t="n"/>
+      <c r="A340" s="5" t="n"/>
     </row>
     <row r="341">
-      <c r="A341" s="9" t="n"/>
+      <c r="A341" s="5" t="n"/>
     </row>
     <row r="342">
-      <c r="A342" s="9" t="n"/>
+      <c r="A342" s="5" t="n"/>
     </row>
     <row r="343">
-      <c r="A343" s="9" t="n"/>
+      <c r="A343" s="5" t="n"/>
     </row>
     <row r="344">
-      <c r="A344" s="9" t="n"/>
+      <c r="A344" s="5" t="n"/>
     </row>
     <row r="345">
-      <c r="A345" s="9" t="n"/>
+      <c r="A345" s="5" t="n"/>
     </row>
     <row r="346">
-      <c r="A346" s="9" t="n"/>
+      <c r="A346" s="5" t="n"/>
     </row>
     <row r="347">
-      <c r="A347" s="9" t="n"/>
+      <c r="A347" s="5" t="n"/>
     </row>
     <row r="348">
-      <c r="A348" s="9" t="n"/>
+      <c r="A348" s="5" t="n"/>
     </row>
     <row r="349">
-      <c r="A349" s="9" t="n"/>
+      <c r="A349" s="5" t="n"/>
     </row>
     <row r="350">
-      <c r="A350" s="9" t="n"/>
+      <c r="A350" s="5" t="n"/>
     </row>
     <row r="351">
-      <c r="A351" s="9" t="n"/>
+      <c r="A351" s="5" t="n"/>
     </row>
     <row r="352">
-      <c r="A352" s="9" t="n"/>
+      <c r="A352" s="5" t="n"/>
     </row>
     <row r="353">
-      <c r="A353" s="9" t="n"/>
+      <c r="A353" s="5" t="n"/>
     </row>
     <row r="354">
-      <c r="A354" s="9" t="n"/>
+      <c r="A354" s="5" t="n"/>
     </row>
     <row r="355">
-      <c r="A355" s="9" t="n"/>
+      <c r="A355" s="5" t="n"/>
     </row>
     <row r="356">
-      <c r="A356" s="9" t="n"/>
+      <c r="A356" s="5" t="n"/>
     </row>
     <row r="357">
-      <c r="A357" s="9" t="n"/>
+      <c r="A357" s="5" t="n"/>
     </row>
     <row r="358">
-      <c r="A358" s="9" t="n"/>
+      <c r="A358" s="5" t="n"/>
     </row>
     <row r="359">
-      <c r="A359" s="9" t="n"/>
+      <c r="A359" s="5" t="n"/>
     </row>
     <row r="360">
-      <c r="A360" s="9" t="n"/>
+      <c r="A360" s="5" t="n"/>
     </row>
     <row r="361">
-      <c r="A361" s="9" t="n"/>
+      <c r="A361" s="5" t="n"/>
     </row>
     <row r="362">
-      <c r="A362" s="9" t="n"/>
+      <c r="A362" s="5" t="n"/>
     </row>
     <row r="363">
-      <c r="A363" s="9" t="n"/>
+      <c r="A363" s="5" t="n"/>
     </row>
     <row r="364">
-      <c r="A364" s="9" t="n"/>
+      <c r="A364" s="5" t="n"/>
     </row>
     <row r="365">
-      <c r="A365" s="9" t="n"/>
+      <c r="A365" s="5" t="n"/>
     </row>
     <row r="366">
-      <c r="A366" s="9" t="n"/>
+      <c r="A366" s="5" t="n"/>
     </row>
     <row r="367">
-      <c r="A367" s="9" t="n"/>
+      <c r="A367" s="5" t="n"/>
     </row>
     <row r="368">
-      <c r="A368" s="9" t="n"/>
+      <c r="A368" s="5" t="n"/>
     </row>
     <row r="369">
-      <c r="A369" s="9" t="n"/>
+      <c r="A369" s="5" t="n"/>
     </row>
     <row r="370">
-      <c r="A370" s="9" t="n"/>
+      <c r="A370" s="5" t="n"/>
     </row>
     <row r="371">
-      <c r="A371" s="9" t="n"/>
+      <c r="A371" s="5" t="n"/>
     </row>
     <row r="372">
-      <c r="A372" s="9" t="n"/>
+      <c r="A372" s="5" t="n"/>
     </row>
     <row r="373">
-      <c r="A373" s="9" t="n"/>
+      <c r="A373" s="5" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="9" t="n"/>
+      <c r="A374" s="5" t="n"/>
     </row>
     <row r="375">
-      <c r="A375" s="9" t="n"/>
+      <c r="A375" s="5" t="n"/>
     </row>
     <row r="376">
-      <c r="A376" s="9" t="n"/>
+      <c r="A376" s="5" t="n"/>
     </row>
     <row r="377">
-      <c r="A377" s="9" t="n"/>
+      <c r="A377" s="5" t="n"/>
     </row>
     <row r="378">
-      <c r="A378" s="9" t="n"/>
+      <c r="A378" s="5" t="n"/>
     </row>
     <row r="379">
-      <c r="A379" s="9" t="n"/>
+      <c r="A379" s="5" t="n"/>
     </row>
     <row r="380">
-      <c r="A380" s="9" t="n"/>
+      <c r="A380" s="5" t="n"/>
     </row>
     <row r="381">
-      <c r="A381" s="9" t="n"/>
+      <c r="A381" s="5" t="n"/>
     </row>
     <row r="382">
-      <c r="A382" s="9" t="n"/>
+      <c r="A382" s="5" t="n"/>
     </row>
     <row r="383">
-      <c r="A383" s="9" t="n"/>
+      <c r="A383" s="5" t="n"/>
     </row>
     <row r="384">
-      <c r="A384" s="9" t="n"/>
+      <c r="A384" s="5" t="n"/>
     </row>
     <row r="385">
-      <c r="A385" s="9" t="n"/>
+      <c r="A385" s="5" t="n"/>
     </row>
     <row r="386">
-      <c r="A386" s="9" t="n"/>
+      <c r="A386" s="5" t="n"/>
     </row>
     <row r="387">
-      <c r="A387" s="9" t="n"/>
+      <c r="A387" s="5" t="n"/>
     </row>
     <row r="388">
-      <c r="A388" s="9" t="n"/>
+      <c r="A388" s="5" t="n"/>
     </row>
     <row r="389">
-      <c r="A389" s="9" t="n"/>
+      <c r="A389" s="5" t="n"/>
     </row>
     <row r="390">
-      <c r="A390" s="9" t="n"/>
+      <c r="A390" s="5" t="n"/>
     </row>
     <row r="391">
-      <c r="A391" s="9" t="n"/>
+      <c r="A391" s="5" t="n"/>
     </row>
     <row r="392">
-      <c r="A392" s="9" t="n"/>
+      <c r="A392" s="5" t="n"/>
     </row>
     <row r="393">
-      <c r="A393" s="9" t="n"/>
+      <c r="A393" s="5" t="n"/>
     </row>
     <row r="394">
-      <c r="A394" s="9" t="n"/>
+      <c r="A394" s="5" t="n"/>
     </row>
     <row r="395">
-      <c r="A395" s="9" t="n"/>
+      <c r="A395" s="5" t="n"/>
     </row>
     <row r="396">
-      <c r="A396" s="9" t="n"/>
+      <c r="A396" s="5" t="n"/>
     </row>
     <row r="397">
-      <c r="A397" s="9" t="n"/>
+      <c r="A397" s="5" t="n"/>
     </row>
     <row r="398">
-      <c r="A398" s="9" t="n"/>
+      <c r="A398" s="5" t="n"/>
     </row>
     <row r="399">
-      <c r="A399" s="9" t="n"/>
+      <c r="A399" s="5" t="n"/>
     </row>
     <row r="400">
-      <c r="A400" s="9" t="n"/>
+      <c r="A400" s="5" t="n"/>
     </row>
     <row r="401">
-      <c r="A401" s="9" t="n"/>
+      <c r="A401" s="5" t="n"/>
     </row>
     <row r="402">
-      <c r="A402" s="9" t="n"/>
+      <c r="A402" s="5" t="n"/>
     </row>
     <row r="403">
-      <c r="A403" s="9" t="n"/>
+      <c r="A403" s="5" t="n"/>
     </row>
     <row r="404">
-      <c r="A404" s="9" t="n"/>
+      <c r="A404" s="5" t="n"/>
     </row>
     <row r="405">
-      <c r="A405" s="9" t="n"/>
+      <c r="A405" s="5" t="n"/>
     </row>
     <row r="406">
-      <c r="A406" s="9" t="n"/>
+      <c r="A406" s="5" t="n"/>
     </row>
     <row r="407">
-      <c r="A407" s="9" t="n"/>
+      <c r="A407" s="5" t="n"/>
     </row>
     <row r="408">
-      <c r="A408" s="9" t="n"/>
+      <c r="A408" s="5" t="n"/>
     </row>
     <row r="409">
-      <c r="A409" s="9" t="n"/>
+      <c r="A409" s="5" t="n"/>
     </row>
     <row r="410">
-      <c r="A410" s="9" t="n"/>
+      <c r="A410" s="5" t="n"/>
     </row>
     <row r="411">
-      <c r="A411" s="9" t="n"/>
+      <c r="A411" s="5" t="n"/>
     </row>
     <row r="412">
-      <c r="A412" s="9" t="n"/>
+      <c r="A412" s="5" t="n"/>
     </row>
     <row r="413">
-      <c r="A413" s="9" t="n"/>
+      <c r="A413" s="5" t="n"/>
     </row>
     <row r="414">
-      <c r="A414" s="9" t="n"/>
+      <c r="A414" s="5" t="n"/>
     </row>
     <row r="415">
-      <c r="A415" s="9" t="n"/>
+      <c r="A415" s="5" t="n"/>
     </row>
     <row r="416">
-      <c r="A416" s="9" t="n"/>
+      <c r="A416" s="5" t="n"/>
     </row>
     <row r="417">
-      <c r="A417" s="9" t="n"/>
+      <c r="A417" s="5" t="n"/>
     </row>
     <row r="418">
-      <c r="A418" s="9" t="n"/>
+      <c r="A418" s="5" t="n"/>
     </row>
     <row r="419">
-      <c r="A419" s="9" t="n"/>
+      <c r="A419" s="5" t="n"/>
     </row>
     <row r="420">
-      <c r="A420" s="9" t="n"/>
+      <c r="A420" s="5" t="n"/>
     </row>
     <row r="421">
-      <c r="A421" s="9" t="n"/>
+      <c r="A421" s="5" t="n"/>
     </row>
     <row r="422">
-      <c r="A422" s="9" t="n"/>
+      <c r="A422" s="5" t="n"/>
     </row>
     <row r="423">
-      <c r="A423" s="9" t="n"/>
+      <c r="A423" s="5" t="n"/>
     </row>
     <row r="424">
-      <c r="A424" s="9" t="n"/>
+      <c r="A424" s="5" t="n"/>
     </row>
     <row r="425">
-      <c r="A425" s="9" t="n"/>
+      <c r="A425" s="5" t="n"/>
     </row>
     <row r="426">
-      <c r="A426" s="9" t="n"/>
+      <c r="A426" s="5" t="n"/>
     </row>
     <row r="427">
-      <c r="A427" s="9" t="n"/>
+      <c r="A427" s="5" t="n"/>
     </row>
     <row r="428">
-      <c r="A428" s="9" t="n"/>
+      <c r="A428" s="5" t="n"/>
     </row>
     <row r="429">
-      <c r="A429" s="9" t="n"/>
+      <c r="A429" s="5" t="n"/>
     </row>
     <row r="430">
-      <c r="A430" s="9" t="n"/>
+      <c r="A430" s="5" t="n"/>
     </row>
     <row r="431">
-      <c r="A431" s="9" t="n"/>
+      <c r="A431" s="5" t="n"/>
     </row>
     <row r="432">
-      <c r="A432" s="9" t="n"/>
+      <c r="A432" s="5" t="n"/>
     </row>
     <row r="433">
-      <c r="A433" s="9" t="n"/>
+      <c r="A433" s="5" t="n"/>
     </row>
     <row r="434">
-      <c r="A434" s="9" t="n"/>
+      <c r="A434" s="5" t="n"/>
     </row>
     <row r="435">
-      <c r="A435" s="9" t="n"/>
+      <c r="A435" s="5" t="n"/>
     </row>
     <row r="436">
-      <c r="A436" s="9" t="n"/>
+      <c r="A436" s="5" t="n"/>
     </row>
     <row r="437">
-      <c r="A437" s="9" t="n"/>
+      <c r="A437" s="5" t="n"/>
     </row>
     <row r="438">
-      <c r="A438" s="9" t="n"/>
+      <c r="A438" s="5" t="n"/>
     </row>
     <row r="439">
-      <c r="A439" s="9" t="n"/>
+      <c r="A439" s="5" t="n"/>
     </row>
     <row r="440">
-      <c r="A440" s="9" t="n"/>
+      <c r="A440" s="5" t="n"/>
     </row>
     <row r="441">
-      <c r="A441" s="9" t="n"/>
+      <c r="A441" s="5" t="n"/>
     </row>
     <row r="442">
-      <c r="A442" s="9" t="n"/>
+      <c r="A442" s="5" t="n"/>
     </row>
     <row r="443">
-      <c r="A443" s="9" t="n"/>
+      <c r="A443" s="5" t="n"/>
     </row>
     <row r="444">
-      <c r="A444" s="9" t="n"/>
+      <c r="A444" s="5" t="n"/>
     </row>
     <row r="445">
-      <c r="A445" s="9" t="n"/>
+      <c r="A445" s="5" t="n"/>
     </row>
     <row r="446">
-      <c r="A446" s="9" t="n"/>
+      <c r="A446" s="5" t="n"/>
     </row>
     <row r="447">
-      <c r="A447" s="9" t="n"/>
+      <c r="A447" s="5" t="n"/>
     </row>
     <row r="448">
-      <c r="A448" s="9" t="n"/>
+      <c r="A448" s="5" t="n"/>
     </row>
     <row r="449">
-      <c r="A449" s="9" t="n"/>
+      <c r="A449" s="5" t="n"/>
     </row>
     <row r="450">
-      <c r="A450" s="9" t="n"/>
+      <c r="A450" s="5" t="n"/>
     </row>
     <row r="451">
-      <c r="A451" s="9" t="n"/>
+      <c r="A451" s="5" t="n"/>
     </row>
     <row r="452">
-      <c r="A452" s="9" t="n"/>
+      <c r="A452" s="5" t="n"/>
     </row>
     <row r="453">
-      <c r="A453" s="9" t="n"/>
+      <c r="A453" s="5" t="n"/>
     </row>
     <row r="454">
-      <c r="A454" s="9" t="n"/>
+      <c r="A454" s="5" t="n"/>
     </row>
     <row r="455">
-      <c r="A455" s="9" t="n"/>
+      <c r="A455" s="5" t="n"/>
     </row>
     <row r="456">
-      <c r="A456" s="9" t="n"/>
+      <c r="A456" s="5" t="n"/>
     </row>
     <row r="457">
-      <c r="A457" s="9" t="n"/>
+      <c r="A457" s="5" t="n"/>
     </row>
     <row r="458">
-      <c r="A458" s="9" t="n"/>
+      <c r="A458" s="5" t="n"/>
     </row>
     <row r="459">
-      <c r="A459" s="9" t="n"/>
+      <c r="A459" s="5" t="n"/>
     </row>
     <row r="460">
-      <c r="A460" s="9" t="n"/>
+      <c r="A460" s="5" t="n"/>
     </row>
     <row r="461">
-      <c r="A461" s="9" t="n"/>
+      <c r="A461" s="5" t="n"/>
     </row>
     <row r="462">
-      <c r="A462" s="9" t="n"/>
+      <c r="A462" s="5" t="n"/>
     </row>
     <row r="463">
-      <c r="A463" s="9" t="n"/>
+      <c r="A463" s="5" t="n"/>
     </row>
     <row r="464">
-      <c r="A464" s="9" t="n"/>
+      <c r="A464" s="5" t="n"/>
     </row>
     <row r="465">
-      <c r="A465" s="9" t="n"/>
+      <c r="A465" s="5" t="n"/>
     </row>
     <row r="466">
-      <c r="A466" s="9" t="n"/>
+      <c r="A466" s="5" t="n"/>
     </row>
     <row r="467">
-      <c r="A467" s="9" t="n"/>
+      <c r="A467" s="5" t="n"/>
     </row>
     <row r="468">
-      <c r="A468" s="9" t="n"/>
+      <c r="A468" s="5" t="n"/>
     </row>
     <row r="469">
-      <c r="A469" s="9" t="n"/>
+      <c r="A469" s="5" t="n"/>
     </row>
     <row r="470">
-      <c r="A470" s="9" t="n"/>
+      <c r="A470" s="5" t="n"/>
     </row>
     <row r="471">
-      <c r="A471" s="9" t="n"/>
+      <c r="A471" s="5" t="n"/>
     </row>
     <row r="472">
-      <c r="A472" s="9" t="n"/>
+      <c r="A472" s="5" t="n"/>
     </row>
     <row r="473">
-      <c r="A473" s="9" t="n"/>
+      <c r="A473" s="5" t="n"/>
     </row>
     <row r="474">
-      <c r="A474" s="9" t="n"/>
+      <c r="A474" s="5" t="n"/>
     </row>
     <row r="475">
-      <c r="A475" s="9" t="n"/>
+      <c r="A475" s="5" t="n"/>
     </row>
     <row r="476">
-      <c r="A476" s="9" t="n"/>
+      <c r="A476" s="5" t="n"/>
     </row>
     <row r="477">
-      <c r="A477" s="9" t="n"/>
+      <c r="A477" s="5" t="n"/>
     </row>
     <row r="478">
-      <c r="A478" s="9" t="n"/>
+      <c r="A478" s="5" t="n"/>
     </row>
     <row r="479">
-      <c r="A479" s="9" t="n"/>
+      <c r="A479" s="5" t="n"/>
     </row>
     <row r="480">
-      <c r="A480" s="9" t="n"/>
+      <c r="A480" s="5" t="n"/>
     </row>
     <row r="481">
-      <c r="A481" s="9" t="n"/>
+      <c r="A481" s="5" t="n"/>
     </row>
     <row r="482">
-      <c r="A482" s="9" t="n"/>
+      <c r="A482" s="5" t="n"/>
     </row>
     <row r="483">
-      <c r="A483" s="9" t="n"/>
+      <c r="A483" s="5" t="n"/>
     </row>
     <row r="484">
-      <c r="A484" s="9" t="n"/>
+      <c r="A484" s="5" t="n"/>
     </row>
     <row r="485">
-      <c r="A485" s="9" t="n"/>
+      <c r="A485" s="5" t="n"/>
     </row>
     <row r="486">
-      <c r="A486" s="9" t="n"/>
+      <c r="A486" s="5" t="n"/>
     </row>
     <row r="487">
-      <c r="A487" s="9" t="n"/>
+      <c r="A487" s="5" t="n"/>
     </row>
     <row r="488">
-      <c r="A488" s="9" t="n"/>
+      <c r="A488" s="5" t="n"/>
     </row>
     <row r="489">
-      <c r="A489" s="9" t="n"/>
+      <c r="A489" s="5" t="n"/>
     </row>
     <row r="490">
-      <c r="A490" s="9" t="n"/>
+      <c r="A490" s="5" t="n"/>
     </row>
     <row r="491">
-      <c r="A491" s="9" t="n"/>
+      <c r="A491" s="5" t="n"/>
     </row>
     <row r="492">
-      <c r="A492" s="9" t="n"/>
+      <c r="A492" s="5" t="n"/>
     </row>
     <row r="493">
-      <c r="A493" s="9" t="n"/>
+      <c r="A493" s="5" t="n"/>
     </row>
     <row r="494">
-      <c r="A494" s="9" t="n"/>
+      <c r="A494" s="5" t="n"/>
     </row>
     <row r="495">
-      <c r="A495" s="9" t="n"/>
+      <c r="A495" s="5" t="n"/>
     </row>
     <row r="496">
-      <c r="A496" s="9" t="n"/>
+      <c r="A496" s="5" t="n"/>
     </row>
     <row r="497">
-      <c r="A497" s="9" t="n"/>
+      <c r="A497" s="5" t="n"/>
     </row>
     <row r="498">
-      <c r="A498" s="9" t="n"/>
+      <c r="A498" s="5" t="n"/>
     </row>
     <row r="499">
-      <c r="A499" s="9" t="n"/>
+      <c r="A499" s="5" t="n"/>
     </row>
     <row r="500">
-      <c r="A500" s="9" t="n"/>
+      <c r="A500" s="5" t="n"/>
     </row>
     <row r="501">
-      <c r="A501" s="9" t="n"/>
+      <c r="A501" s="5" t="n"/>
     </row>
     <row r="502">
-      <c r="A502" s="9" t="n"/>
+      <c r="A502" s="5" t="n"/>
     </row>
     <row r="503">
-      <c r="A503" s="9" t="n"/>
+      <c r="A503" s="5" t="n"/>
     </row>
     <row r="504">
-      <c r="A504" s="9" t="n"/>
+      <c r="A504" s="5" t="n"/>
     </row>
     <row r="505">
-      <c r="A505" s="9" t="n"/>
+      <c r="A505" s="5" t="n"/>
     </row>
     <row r="506">
-      <c r="A506" s="9" t="n"/>
+      <c r="A506" s="5" t="n"/>
     </row>
     <row r="507">
-      <c r="A507" s="9" t="n"/>
+      <c r="A507" s="5" t="n"/>
     </row>
     <row r="508">
-      <c r="A508" s="9" t="n"/>
+      <c r="A508" s="5" t="n"/>
     </row>
     <row r="509">
-      <c r="A509" s="9" t="n"/>
+      <c r="A509" s="5" t="n"/>
     </row>
     <row r="510">
-      <c r="A510" s="9" t="n"/>
+      <c r="A510" s="5" t="n"/>
     </row>
     <row r="511">
-      <c r="A511" s="9" t="n"/>
+      <c r="A511" s="5" t="n"/>
     </row>
     <row r="512">
-      <c r="A512" s="9" t="n"/>
+      <c r="A512" s="5" t="n"/>
     </row>
     <row r="513">
-      <c r="A513" s="9" t="n"/>
+      <c r="A513" s="5" t="n"/>
     </row>
     <row r="514">
-      <c r="A514" s="9" t="n"/>
+      <c r="A514" s="5" t="n"/>
     </row>
     <row r="515">
-      <c r="A515" s="9" t="n"/>
+      <c r="A515" s="5" t="n"/>
     </row>
     <row r="516">
-      <c r="A516" s="9" t="n"/>
+      <c r="A516" s="5" t="n"/>
     </row>
     <row r="517">
-      <c r="A517" s="9" t="n"/>
+      <c r="A517" s="5" t="n"/>
     </row>
     <row r="518">
-      <c r="A518" s="9" t="n"/>
+      <c r="A518" s="5" t="n"/>
     </row>
     <row r="519">
-      <c r="A519" s="9" t="n"/>
+      <c r="A519" s="5" t="n"/>
     </row>
     <row r="520">
-      <c r="A520" s="9" t="n"/>
+      <c r="A520" s="5" t="n"/>
     </row>
     <row r="521">
-      <c r="A521" s="9" t="n"/>
+      <c r="A521" s="5" t="n"/>
     </row>
     <row r="522">
-      <c r="A522" s="9" t="n"/>
+      <c r="A522" s="5" t="n"/>
     </row>
     <row r="523">
-      <c r="A523" s="9" t="n"/>
+      <c r="A523" s="5" t="n"/>
     </row>
     <row r="524">
-      <c r="A524" s="9" t="n"/>
+      <c r="A524" s="5" t="n"/>
     </row>
     <row r="525">
-      <c r="A525" s="9" t="n"/>
+      <c r="A525" s="5" t="n"/>
     </row>
     <row r="526">
-      <c r="A526" s="9" t="n"/>
+      <c r="A526" s="5" t="n"/>
     </row>
     <row r="527">
-      <c r="A527" s="9" t="n"/>
+      <c r="A527" s="5" t="n"/>
     </row>
     <row r="528">
-      <c r="A528" s="9" t="n"/>
+      <c r="A528" s="5" t="n"/>
     </row>
     <row r="529">
-      <c r="A529" s="9" t="n"/>
+      <c r="A529" s="5" t="n"/>
     </row>
     <row r="530">
-      <c r="A530" s="9" t="n"/>
+      <c r="A530" s="5" t="n"/>
     </row>
     <row r="531">
-      <c r="A531" s="9" t="n"/>
+      <c r="A531" s="5" t="n"/>
     </row>
     <row r="532">
-      <c r="A532" s="9" t="n"/>
+      <c r="A532" s="5" t="n"/>
     </row>
     <row r="533">
-      <c r="A533" s="9" t="n"/>
+      <c r="A533" s="5" t="n"/>
     </row>
     <row r="534">
-      <c r="A534" s="9" t="n"/>
+      <c r="A534" s="5" t="n"/>
     </row>
     <row r="535">
-      <c r="A535" s="9" t="n"/>
+      <c r="A535" s="5" t="n"/>
     </row>
     <row r="536">
-      <c r="A536" s="9" t="n"/>
+      <c r="A536" s="5" t="n"/>
     </row>
     <row r="537">
-      <c r="A537" s="9" t="n"/>
+      <c r="A537" s="5" t="n"/>
     </row>
     <row r="538">
-      <c r="A538" s="9" t="n"/>
+      <c r="A538" s="5" t="n"/>
     </row>
     <row r="539">
-      <c r="A539" s="9" t="n"/>
+      <c r="A539" s="5" t="n"/>
     </row>
     <row r="540">
-      <c r="A540" s="9" t="n"/>
+      <c r="A540" s="5" t="n"/>
     </row>
     <row r="541">
-      <c r="A541" s="9" t="n"/>
+      <c r="A541" s="5" t="n"/>
     </row>
     <row r="542">
-      <c r="A542" s="9" t="n"/>
+      <c r="A542" s="5" t="n"/>
     </row>
     <row r="543">
-      <c r="A543" s="9" t="n"/>
+      <c r="A543" s="5" t="n"/>
     </row>
     <row r="544">
-      <c r="A544" s="9" t="n"/>
+      <c r="A544" s="5" t="n"/>
     </row>
     <row r="545">
-      <c r="A545" s="9" t="n"/>
+      <c r="A545" s="5" t="n"/>
     </row>
     <row r="546">
-      <c r="A546" s="9" t="n"/>
+      <c r="A546" s="5" t="n"/>
     </row>
     <row r="547">
-      <c r="A547" s="9" t="n"/>
+      <c r="A547" s="5" t="n"/>
     </row>
     <row r="548">
-      <c r="A548" s="9" t="n"/>
+      <c r="A548" s="5" t="n"/>
     </row>
     <row r="549">
-      <c r="A549" s="9" t="n"/>
+      <c r="A549" s="5" t="n"/>
     </row>
     <row r="550">
-      <c r="A550" s="9" t="n"/>
+      <c r="A550" s="5" t="n"/>
     </row>
     <row r="551">
-      <c r="A551" s="9" t="n"/>
+      <c r="A551" s="5" t="n"/>
     </row>
     <row r="552">
-      <c r="A552" s="9" t="n"/>
+      <c r="A552" s="5" t="n"/>
     </row>
     <row r="553">
-      <c r="A553" s="9" t="n"/>
+      <c r="A553" s="5" t="n"/>
     </row>
     <row r="554">
-      <c r="A554" s="9" t="n"/>
+      <c r="A554" s="5" t="n"/>
     </row>
     <row r="555">
-      <c r="A555" s="9" t="n"/>
+      <c r="A555" s="5" t="n"/>
     </row>
     <row r="556">
-      <c r="A556" s="9" t="n"/>
+      <c r="A556" s="5" t="n"/>
     </row>
     <row r="557">
-      <c r="A557" s="9" t="n"/>
+      <c r="A557" s="5" t="n"/>
     </row>
     <row r="558">
-      <c r="A558" s="9" t="n"/>
+      <c r="A558" s="5" t="n"/>
     </row>
     <row r="559">
-      <c r="A559" s="9" t="n"/>
+      <c r="A559" s="5" t="n"/>
     </row>
     <row r="560">
-      <c r="A560" s="9" t="n"/>
+      <c r="A560" s="5" t="n"/>
     </row>
     <row r="561">
-      <c r="A561" s="9" t="n"/>
+      <c r="A561" s="5" t="n"/>
     </row>
     <row r="562">
-      <c r="A562" s="9" t="n"/>
+      <c r="A562" s="5" t="n"/>
     </row>
     <row r="563">
-      <c r="A563" s="9" t="n"/>
+      <c r="A563" s="5" t="n"/>
     </row>
     <row r="564">
-      <c r="A564" s="9" t="n"/>
+      <c r="A564" s="5" t="n"/>
     </row>
     <row r="565">
-      <c r="A565" s="9" t="n"/>
+      <c r="A565" s="5" t="n"/>
     </row>
     <row r="566">
-      <c r="A566" s="9" t="n"/>
+      <c r="A566" s="5" t="n"/>
     </row>
     <row r="567">
-      <c r="A567" s="9" t="n"/>
+      <c r="A567" s="5" t="n"/>
     </row>
     <row r="568">
-      <c r="A568" s="9" t="n"/>
+      <c r="A568" s="5" t="n"/>
     </row>
     <row r="569">
-      <c r="A569" s="9" t="n"/>
+      <c r="A569" s="5" t="n"/>
     </row>
     <row r="570">
-      <c r="A570" s="9" t="n"/>
+      <c r="A570" s="5" t="n"/>
     </row>
     <row r="571">
-      <c r="A571" s="9" t="n"/>
+      <c r="A571" s="5" t="n"/>
     </row>
     <row r="572">
-      <c r="A572" s="9" t="n"/>
+      <c r="A572" s="5" t="n"/>
     </row>
     <row r="573">
-      <c r="A573" s="9" t="n"/>
+      <c r="A573" s="5" t="n"/>
     </row>
     <row r="574">
-      <c r="A574" s="9" t="n"/>
+      <c r="A574" s="5" t="n"/>
     </row>
     <row r="575">
-      <c r="A575" s="9" t="n"/>
+      <c r="A575" s="5" t="n"/>
     </row>
     <row r="576">
-      <c r="A576" s="9" t="n"/>
+      <c r="A576" s="5" t="n"/>
     </row>
     <row r="577">
-      <c r="A577" s="9" t="n"/>
+      <c r="A577" s="5" t="n"/>
     </row>
     <row r="578">
-      <c r="A578" s="9" t="n"/>
+      <c r="A578" s="5" t="n"/>
     </row>
     <row r="579">
-      <c r="A579" s="9" t="n"/>
+      <c r="A579" s="5" t="n"/>
     </row>
     <row r="580">
-      <c r="A580" s="9" t="n"/>
+      <c r="A580" s="5" t="n"/>
     </row>
     <row r="581">
-      <c r="A581" s="9" t="n"/>
+      <c r="A581" s="5" t="n"/>
     </row>
     <row r="582">
-      <c r="A582" s="9" t="n"/>
+      <c r="A582" s="5" t="n"/>
     </row>
     <row r="583">
-      <c r="A583" s="9" t="n"/>
+      <c r="A583" s="5" t="n"/>
     </row>
     <row r="584">
-      <c r="A584" s="9" t="n"/>
+      <c r="A584" s="5" t="n"/>
     </row>
     <row r="585">
-      <c r="A585" s="9" t="n"/>
+      <c r="A585" s="5" t="n"/>
     </row>
     <row r="586">
-      <c r="A586" s="9" t="n"/>
+      <c r="A586" s="5" t="n"/>
     </row>
     <row r="587">
-      <c r="A587" s="9" t="n"/>
+      <c r="A587" s="5" t="n"/>
     </row>
     <row r="588">
-      <c r="A588" s="9" t="n"/>
+      <c r="A588" s="5" t="n"/>
     </row>
     <row r="589">
-      <c r="A589" s="9" t="n"/>
+      <c r="A589" s="5" t="n"/>
     </row>
     <row r="590">
-      <c r="A590" s="9" t="n"/>
+      <c r="A590" s="5" t="n"/>
     </row>
     <row r="591">
-      <c r="A591" s="9" t="n"/>
+      <c r="A591" s="5" t="n"/>
     </row>
     <row r="592">
-      <c r="A592" s="9" t="n"/>
+      <c r="A592" s="5" t="n"/>
     </row>
     <row r="593">
-      <c r="A593" s="9" t="n"/>
+      <c r="A593" s="5" t="n"/>
     </row>
     <row r="594">
-      <c r="A594" s="9" t="n"/>
+      <c r="A594" s="5" t="n"/>
     </row>
     <row r="595">
-      <c r="A595" s="9" t="n"/>
+      <c r="A595" s="5" t="n"/>
     </row>
     <row r="596">
-      <c r="A596" s="9" t="n"/>
+      <c r="A596" s="5" t="n"/>
     </row>
     <row r="597">
-      <c r="A597" s="9" t="n"/>
+      <c r="A597" s="5" t="n"/>
     </row>
     <row r="598">
-      <c r="A598" s="9" t="n"/>
+      <c r="A598" s="5" t="n"/>
     </row>
     <row r="599">
-      <c r="A599" s="9" t="n"/>
+      <c r="A599" s="5" t="n"/>
     </row>
     <row r="600">
-      <c r="A600" s="9" t="n"/>
+      <c r="A600" s="5" t="n"/>
     </row>
     <row r="601">
-      <c r="A601" s="9" t="n"/>
+      <c r="A601" s="5" t="n"/>
     </row>
     <row r="602">
-      <c r="A602" s="9" t="n"/>
+      <c r="A602" s="5" t="n"/>
     </row>
     <row r="603">
-      <c r="A603" s="9" t="n"/>
+      <c r="A603" s="5" t="n"/>
     </row>
     <row r="604">
-      <c r="A604" s="9" t="n"/>
+      <c r="A604" s="5" t="n"/>
     </row>
     <row r="605">
-      <c r="A605" s="9" t="n"/>
+      <c r="A605" s="5" t="n"/>
     </row>
     <row r="606">
-      <c r="A606" s="9" t="n"/>
+      <c r="A606" s="5" t="n"/>
     </row>
     <row r="607">
-      <c r="A607" s="9" t="n"/>
+      <c r="A607" s="5" t="n"/>
     </row>
     <row r="608">
-      <c r="A608" s="9" t="n"/>
+      <c r="A608" s="5" t="n"/>
     </row>
     <row r="609">
-      <c r="A609" s="9" t="n"/>
+      <c r="A609" s="5" t="n"/>
     </row>
     <row r="610">
-      <c r="A610" s="9" t="n"/>
+      <c r="A610" s="5" t="n"/>
     </row>
     <row r="611">
-      <c r="A611" s="9" t="n"/>
+      <c r="A611" s="5" t="n"/>
     </row>
     <row r="612">
-      <c r="A612" s="9" t="n"/>
+      <c r="A612" s="5" t="n"/>
     </row>
     <row r="613">
-      <c r="A613" s="9" t="n"/>
+      <c r="A613" s="5" t="n"/>
     </row>
     <row r="614">
-      <c r="A614" s="9" t="n"/>
+      <c r="A614" s="5" t="n"/>
     </row>
     <row r="615">
-      <c r="A615" s="9" t="n"/>
+      <c r="A615" s="5" t="n"/>
     </row>
     <row r="616">
-      <c r="A616" s="9" t="n"/>
+      <c r="A616" s="5" t="n"/>
     </row>
     <row r="617">
-      <c r="A617" s="9" t="n"/>
+      <c r="A617" s="5" t="n"/>
     </row>
     <row r="618">
-      <c r="A618" s="9" t="n"/>
+      <c r="A618" s="5" t="n"/>
     </row>
     <row r="619">
-      <c r="A619" s="9" t="n"/>
+      <c r="A619" s="5" t="n"/>
     </row>
     <row r="620">
-      <c r="A620" s="9" t="n"/>
+      <c r="A620" s="5" t="n"/>
     </row>
     <row r="621">
-      <c r="A621" s="9" t="n"/>
+      <c r="A621" s="5" t="n"/>
     </row>
     <row r="622">
-      <c r="A622" s="9" t="n"/>
+      <c r="A622" s="5" t="n"/>
     </row>
     <row r="623">
-      <c r="A623" s="9" t="n"/>
+      <c r="A623" s="5" t="n"/>
     </row>
     <row r="624">
-      <c r="A624" s="9" t="n"/>
+      <c r="A624" s="5" t="n"/>
     </row>
     <row r="625">
-      <c r="A625" s="9" t="n"/>
+      <c r="A625" s="5" t="n"/>
     </row>
     <row r="626">
-      <c r="A626" s="9" t="n"/>
+      <c r="A626" s="5" t="n"/>
     </row>
     <row r="627">
-      <c r="A627" s="9" t="n"/>
+      <c r="A627" s="5" t="n"/>
     </row>
     <row r="628">
-      <c r="A628" s="9" t="n"/>
+      <c r="A628" s="5" t="n"/>
     </row>
     <row r="629">
-      <c r="A629" s="9" t="n"/>
+      <c r="A629" s="5" t="n"/>
     </row>
     <row r="630">
-      <c r="A630" s="9" t="n"/>
+      <c r="A630" s="5" t="n"/>
     </row>
     <row r="631">
-      <c r="A631" s="9" t="n"/>
+      <c r="A631" s="5" t="n"/>
     </row>
     <row r="632">
-      <c r="A632" s="9" t="n"/>
+      <c r="A632" s="5" t="n"/>
     </row>
     <row r="633">
-      <c r="A633" s="9" t="n"/>
+      <c r="A633" s="5" t="n"/>
     </row>
     <row r="634">
-      <c r="A634" s="9" t="n"/>
+      <c r="A634" s="5" t="n"/>
     </row>
     <row r="635">
-      <c r="A635" s="9" t="n"/>
+      <c r="A635" s="5" t="n"/>
     </row>
     <row r="636">
-      <c r="A636" s="9" t="n"/>
+      <c r="A636" s="5" t="n"/>
     </row>
     <row r="637">
-      <c r="A637" s="9" t="n"/>
+      <c r="A637" s="5" t="n"/>
     </row>
     <row r="638">
-      <c r="A638" s="9" t="n"/>
+      <c r="A638" s="5" t="n"/>
     </row>
     <row r="639">
-      <c r="A639" s="9" t="n"/>
+      <c r="A639" s="5" t="n"/>
     </row>
     <row r="640">
-      <c r="A640" s="9" t="n"/>
+      <c r="A640" s="5" t="n"/>
     </row>
     <row r="641">
-      <c r="A641" s="9" t="n"/>
+      <c r="A641" s="5" t="n"/>
     </row>
     <row r="642">
-      <c r="A642" s="9" t="n"/>
+      <c r="A642" s="5" t="n"/>
     </row>
     <row r="643">
-      <c r="A643" s="9" t="n"/>
+      <c r="A643" s="5" t="n"/>
     </row>
     <row r="644">
-      <c r="A644" s="9" t="n"/>
+      <c r="A644" s="5" t="n"/>
     </row>
     <row r="645">
-      <c r="A645" s="9" t="n"/>
+      <c r="A645" s="5" t="n"/>
     </row>
     <row r="646">
-      <c r="A646" s="9" t="n"/>
+      <c r="A646" s="5" t="n"/>
     </row>
     <row r="647">
-      <c r="A647" s="9" t="n"/>
+      <c r="A647" s="5" t="n"/>
     </row>
     <row r="648">
-      <c r="A648" s="9" t="n"/>
+      <c r="A648" s="5" t="n"/>
     </row>
     <row r="649">
-      <c r="A649" s="9" t="n"/>
+      <c r="A649" s="5" t="n"/>
     </row>
     <row r="650">
-      <c r="A650" s="9" t="n"/>
+      <c r="A650" s="5" t="n"/>
     </row>
     <row r="651">
-      <c r="A651" s="9" t="n"/>
+      <c r="A651" s="5" t="n"/>
     </row>
     <row r="652">
-      <c r="A652" s="9" t="n"/>
+      <c r="A652" s="5" t="n"/>
     </row>
     <row r="653">
-      <c r="A653" s="9" t="n"/>
+      <c r="A653" s="5" t="n"/>
     </row>
     <row r="654">
-      <c r="A654" s="9" t="n"/>
+      <c r="A654" s="5" t="n"/>
     </row>
     <row r="655">
-      <c r="A655" s="9" t="n"/>
+      <c r="A655" s="5" t="n"/>
     </row>
     <row r="656">
-      <c r="A656" s="9" t="n"/>
+      <c r="A656" s="5" t="n"/>
     </row>
     <row r="657">
-      <c r="A657" s="9" t="n"/>
+      <c r="A657" s="5" t="n"/>
     </row>
     <row r="658">
-      <c r="A658" s="9" t="n"/>
+      <c r="A658" s="5" t="n"/>
     </row>
     <row r="659">
-      <c r="A659" s="9" t="n"/>
+      <c r="A659" s="5" t="n"/>
     </row>
     <row r="660">
-      <c r="A660" s="9" t="n"/>
+      <c r="A660" s="5" t="n"/>
     </row>
     <row r="661">
-      <c r="A661" s="9" t="n"/>
+      <c r="A661" s="5" t="n"/>
     </row>
     <row r="662">
-      <c r="A662" s="9" t="n"/>
+      <c r="A662" s="5" t="n"/>
     </row>
     <row r="663">
-      <c r="A663" s="9" t="n"/>
+      <c r="A663" s="5" t="n"/>
     </row>
     <row r="664">
-      <c r="A664" s="9" t="n"/>
+      <c r="A664" s="5" t="n"/>
     </row>
     <row r="665">
-      <c r="A665" s="9" t="n"/>
+      <c r="A665" s="5" t="n"/>
     </row>
     <row r="666">
-      <c r="A666" s="9" t="n"/>
+      <c r="A666" s="5" t="n"/>
     </row>
     <row r="667">
-      <c r="A667" s="9" t="n"/>
+      <c r="A667" s="5" t="n"/>
     </row>
     <row r="668">
-      <c r="A668" s="9" t="n"/>
+      <c r="A668" s="5" t="n"/>
     </row>
     <row r="669">
-      <c r="A669" s="9" t="n"/>
+      <c r="A669" s="5" t="n"/>
     </row>
     <row r="670">
-      <c r="A670" s="9" t="n"/>
+      <c r="A670" s="5" t="n"/>
     </row>
     <row r="671">
-      <c r="A671" s="9" t="n"/>
+      <c r="A671" s="5" t="n"/>
     </row>
     <row r="672">
-      <c r="A672" s="9" t="n"/>
+      <c r="A672" s="5" t="n"/>
     </row>
     <row r="673">
-      <c r="A673" s="9" t="n"/>
+      <c r="A673" s="5" t="n"/>
     </row>
     <row r="674">
-      <c r="A674" s="9" t="n"/>
+      <c r="A674" s="5" t="n"/>
     </row>
     <row r="675">
-      <c r="A675" s="9" t="n"/>
+      <c r="A675" s="5" t="n"/>
     </row>
     <row r="676">
-      <c r="A676" s="9" t="n"/>
+      <c r="A676" s="5" t="n"/>
     </row>
     <row r="677">
-      <c r="A677" s="9" t="n"/>
+      <c r="A677" s="5" t="n"/>
     </row>
     <row r="678">
-      <c r="A678" s="9" t="n"/>
+      <c r="A678" s="5" t="n"/>
     </row>
     <row r="679">
-      <c r="A679" s="9" t="n"/>
+      <c r="A679" s="5" t="n"/>
     </row>
     <row r="680">
-      <c r="A680" s="9" t="n"/>
+      <c r="A680" s="5" t="n"/>
     </row>
     <row r="681">
-      <c r="A681" s="9" t="n"/>
+      <c r="A681" s="5" t="n"/>
     </row>
     <row r="682">
-      <c r="A682" s="9" t="n"/>
+      <c r="A682" s="5" t="n"/>
     </row>
     <row r="683">
-      <c r="A683" s="9" t="n"/>
+      <c r="A683" s="5" t="n"/>
     </row>
     <row r="684">
-      <c r="A684" s="9" t="n"/>
+      <c r="A684" s="5" t="n"/>
     </row>
     <row r="685">
-      <c r="A685" s="9" t="n"/>
+      <c r="A685" s="5" t="n"/>
     </row>
     <row r="686">
-      <c r="A686" s="9" t="n"/>
+      <c r="A686" s="5" t="n"/>
     </row>
     <row r="687">
-      <c r="A687" s="9" t="n"/>
+      <c r="A687" s="5" t="n"/>
     </row>
     <row r="688">
-      <c r="A688" s="9" t="n"/>
+      <c r="A688" s="5" t="n"/>
     </row>
     <row r="689">
-      <c r="A689" s="9" t="n"/>
+      <c r="A689" s="5" t="n"/>
     </row>
     <row r="690">
-      <c r="A690" s="9" t="n"/>
+      <c r="A690" s="5" t="n"/>
     </row>
     <row r="691">
-      <c r="A691" s="9" t="n"/>
+      <c r="A691" s="5" t="n"/>
     </row>
     <row r="692">
-      <c r="A692" s="9" t="n"/>
+      <c r="A692" s="5" t="n"/>
     </row>
     <row r="693">
-      <c r="A693" s="9" t="n"/>
+      <c r="A693" s="5" t="n"/>
     </row>
     <row r="694">
-      <c r="A694" s="9" t="n"/>
+      <c r="A694" s="5" t="n"/>
     </row>
     <row r="695">
-      <c r="A695" s="9" t="n"/>
+      <c r="A695" s="5" t="n"/>
     </row>
     <row r="696">
-      <c r="A696" s="9" t="n"/>
+      <c r="A696" s="5" t="n"/>
     </row>
     <row r="697">
-      <c r="A697" s="9" t="n"/>
+      <c r="A697" s="5" t="n"/>
     </row>
     <row r="698">
-      <c r="A698" s="9" t="n"/>
+      <c r="A698" s="5" t="n"/>
     </row>
     <row r="699">
-      <c r="A699" s="9" t="n"/>
+      <c r="A699" s="5" t="n"/>
     </row>
     <row r="700">
-      <c r="A700" s="9" t="n"/>
+      <c r="A700" s="5" t="n"/>
     </row>
     <row r="701">
-      <c r="A701" s="9" t="n"/>
+      <c r="A701" s="5" t="n"/>
     </row>
     <row r="702">
-      <c r="A702" s="9" t="n"/>
+      <c r="A702" s="5" t="n"/>
     </row>
     <row r="703">
-      <c r="A703" s="9" t="n"/>
+      <c r="A703" s="5" t="n"/>
     </row>
     <row r="704">
-      <c r="A704" s="9" t="n"/>
+      <c r="A704" s="5" t="n"/>
     </row>
     <row r="705">
-      <c r="A705" s="9" t="n"/>
+      <c r="A705" s="5" t="n"/>
     </row>
     <row r="706">
-      <c r="A706" s="9" t="n"/>
+      <c r="A706" s="5" t="n"/>
     </row>
     <row r="707">
-      <c r="A707" s="9" t="n"/>
+      <c r="A707" s="5" t="n"/>
     </row>
     <row r="708">
-      <c r="A708" s="9" t="n"/>
+      <c r="A708" s="5" t="n"/>
     </row>
     <row r="709">
-      <c r="A709" s="9" t="n"/>
+      <c r="A709" s="5" t="n"/>
     </row>
     <row r="710">
-      <c r="A710" s="9" t="n"/>
+      <c r="A710" s="5" t="n"/>
     </row>
     <row r="711">
-      <c r="A711" s="9" t="n"/>
+      <c r="A711" s="5" t="n"/>
     </row>
     <row r="712">
-      <c r="A712" s="9" t="n"/>
+      <c r="A712" s="5" t="n"/>
     </row>
     <row r="713">
-      <c r="A713" s="9" t="n"/>
+      <c r="A713" s="5" t="n"/>
     </row>
     <row r="714">
-      <c r="A714" s="9" t="n"/>
+      <c r="A714" s="5" t="n"/>
     </row>
     <row r="715">
-      <c r="A715" s="9" t="n"/>
+      <c r="A715" s="5" t="n"/>
     </row>
     <row r="716">
-      <c r="A716" s="9" t="n"/>
+      <c r="A716" s="5" t="n"/>
     </row>
     <row r="717">
-      <c r="A717" s="9" t="n"/>
+      <c r="A717" s="5" t="n"/>
     </row>
     <row r="718">
-      <c r="A718" s="9" t="n"/>
+      <c r="A718" s="5" t="n"/>
     </row>
     <row r="719">
-      <c r="A719" s="9" t="n"/>
+      <c r="A719" s="5" t="n"/>
     </row>
     <row r="720">
-      <c r="A720" s="9" t="n"/>
+      <c r="A720" s="5" t="n"/>
     </row>
     <row r="721">
-      <c r="A721" s="9" t="n"/>
+      <c r="A721" s="5" t="n"/>
     </row>
     <row r="722">
-      <c r="A722" s="9" t="n"/>
+      <c r="A722" s="5" t="n"/>
     </row>
     <row r="723">
-      <c r="A723" s="9" t="n"/>
+      <c r="A723" s="5" t="n"/>
     </row>
     <row r="724">
-      <c r="A724" s="9" t="n"/>
+      <c r="A724" s="5" t="n"/>
     </row>
     <row r="725">
-      <c r="A725" s="9" t="n"/>
+      <c r="A725" s="5" t="n"/>
     </row>
     <row r="726">
-      <c r="A726" s="9" t="n"/>
+      <c r="A726" s="5" t="n"/>
     </row>
     <row r="727">
-      <c r="A727" s="9" t="n"/>
+      <c r="A727" s="5" t="n"/>
     </row>
     <row r="728">
-      <c r="A728" s="9" t="n"/>
+      <c r="A728" s="5" t="n"/>
     </row>
     <row r="729">
-      <c r="A729" s="9" t="n"/>
+      <c r="A729" s="5" t="n"/>
     </row>
     <row r="730">
-      <c r="A730" s="9" t="n"/>
+      <c r="A730" s="5" t="n"/>
     </row>
     <row r="731">
-      <c r="A731" s="9" t="n"/>
+      <c r="A731" s="5" t="n"/>
     </row>
     <row r="732">
-      <c r="A732" s="9" t="n"/>
+      <c r="A732" s="5" t="n"/>
     </row>
     <row r="733">
-      <c r="A733" s="9" t="n"/>
+      <c r="A733" s="5" t="n"/>
     </row>
     <row r="734">
-      <c r="A734" s="9" t="n"/>
+      <c r="A734" s="5" t="n"/>
     </row>
     <row r="735">
-      <c r="A735" s="9" t="n"/>
+      <c r="A735" s="5" t="n"/>
     </row>
     <row r="736">
-      <c r="A736" s="9" t="n"/>
+      <c r="A736" s="5" t="n"/>
     </row>
     <row r="737">
-      <c r="A737" s="9" t="n"/>
+      <c r="A737" s="5" t="n"/>
     </row>
     <row r="738">
-      <c r="A738" s="9" t="n"/>
+      <c r="A738" s="5" t="n"/>
     </row>
     <row r="739">
-      <c r="A739" s="9" t="n"/>
+      <c r="A739" s="5" t="n"/>
     </row>
     <row r="740">
-      <c r="A740" s="9" t="n"/>
+      <c r="A740" s="5" t="n"/>
     </row>
     <row r="741">
-      <c r="A741" s="9" t="n"/>
+      <c r="A741" s="5" t="n"/>
     </row>
     <row r="742">
-      <c r="A742" s="9" t="n"/>
+      <c r="A742" s="5" t="n"/>
     </row>
     <row r="743">
-      <c r="A743" s="9" t="n"/>
+      <c r="A743" s="5" t="n"/>
     </row>
     <row r="744">
-      <c r="A744" s="9" t="n"/>
+      <c r="A744" s="5" t="n"/>
     </row>
     <row r="745">
-      <c r="A745" s="9" t="n"/>
+      <c r="A745" s="5" t="n"/>
     </row>
     <row r="746">
-      <c r="A746" s="9" t="n"/>
+      <c r="A746" s="5" t="n"/>
     </row>
     <row r="747">
-      <c r="A747" s="9" t="n"/>
+      <c r="A747" s="5" t="n"/>
     </row>
     <row r="748">
-      <c r="A748" s="9" t="n"/>
+      <c r="A748" s="5" t="n"/>
     </row>
     <row r="749">
-      <c r="A749" s="9" t="n"/>
+      <c r="A749" s="5" t="n"/>
     </row>
     <row r="750">
-      <c r="A750" s="9" t="n"/>
+      <c r="A750" s="5" t="n"/>
     </row>
     <row r="751">
-      <c r="A751" s="9" t="n"/>
+      <c r="A751" s="5" t="n"/>
     </row>
     <row r="752">
-      <c r="A752" s="9" t="n"/>
+      <c r="A752" s="5" t="n"/>
     </row>
     <row r="753">
-      <c r="A753" s="9" t="n"/>
+      <c r="A753" s="5" t="n"/>
     </row>
     <row r="754">
-      <c r="A754" s="9" t="n"/>
+      <c r="A754" s="5" t="n"/>
     </row>
     <row r="755">
-      <c r="A755" s="9" t="n"/>
+      <c r="A755" s="5" t="n"/>
     </row>
     <row r="756">
-      <c r="A756" s="9" t="n"/>
+      <c r="A756" s="5" t="n"/>
     </row>
     <row r="757">
-      <c r="A757" s="9" t="n"/>
+      <c r="A757" s="5" t="n"/>
     </row>
     <row r="758">
-      <c r="A758" s="9" t="n"/>
+      <c r="A758" s="5" t="n"/>
     </row>
     <row r="759">
-      <c r="A759" s="9" t="n"/>
+      <c r="A759" s="5" t="n"/>
     </row>
     <row r="760">
-      <c r="A760" s="9" t="n"/>
+      <c r="A760" s="5" t="n"/>
     </row>
     <row r="761">
-      <c r="A761" s="9" t="n"/>
+      <c r="A761" s="5" t="n"/>
     </row>
     <row r="762">
-      <c r="A762" s="9" t="n"/>
+      <c r="A762" s="5" t="n"/>
     </row>
     <row r="763">
-      <c r="A763" s="9" t="n"/>
+      <c r="A763" s="5" t="n"/>
     </row>
     <row r="764">
-      <c r="A764" s="9" t="n"/>
+      <c r="A764" s="5" t="n"/>
     </row>
     <row r="765">
-      <c r="A765" s="9" t="n"/>
+      <c r="A765" s="5" t="n"/>
     </row>
     <row r="766">
-      <c r="A766" s="9" t="n"/>
+      <c r="A766" s="5" t="n"/>
     </row>
     <row r="767">
-      <c r="A767" s="9" t="n"/>
+      <c r="A767" s="5" t="n"/>
     </row>
     <row r="768">
-      <c r="A768" s="9" t="n"/>
+      <c r="A768" s="5" t="n"/>
     </row>
     <row r="769">
-      <c r="A769" s="9" t="n"/>
+      <c r="A769" s="5" t="n"/>
     </row>
     <row r="770">
-      <c r="A770" s="9" t="n"/>
+      <c r="A770" s="5" t="n"/>
     </row>
     <row r="771">
-      <c r="A771" s="9" t="n"/>
+      <c r="A771" s="5" t="n"/>
     </row>
     <row r="772">
-      <c r="A772" s="9" t="n"/>
+      <c r="A772" s="5" t="n"/>
     </row>
     <row r="773">
-      <c r="A773" s="9" t="n"/>
+      <c r="A773" s="5" t="n"/>
     </row>
     <row r="774">
-      <c r="A774" s="9" t="n"/>
+      <c r="A774" s="5" t="n"/>
     </row>
     <row r="775">
-      <c r="A775" s="9" t="n"/>
+      <c r="A775" s="5" t="n"/>
     </row>
     <row r="776">
-      <c r="A776" s="9" t="n"/>
+      <c r="A776" s="5" t="n"/>
     </row>
     <row r="777">
-      <c r="A777" s="9" t="n"/>
+      <c r="A777" s="5" t="n"/>
     </row>
     <row r="778">
-      <c r="A778" s="9" t="n"/>
+      <c r="A778" s="5" t="n"/>
     </row>
     <row r="779">
-      <c r="A779" s="9" t="n"/>
+      <c r="A779" s="5" t="n"/>
     </row>
     <row r="780">
-      <c r="A780" s="9" t="n"/>
+      <c r="A780" s="5" t="n"/>
     </row>
     <row r="781">
-      <c r="A781" s="9" t="n"/>
+      <c r="A781" s="5" t="n"/>
     </row>
     <row r="782">
-      <c r="A782" s="9" t="n"/>
+      <c r="A782" s="5" t="n"/>
     </row>
     <row r="783">
-      <c r="A783" s="9" t="n"/>
+      <c r="A783" s="5" t="n"/>
     </row>
     <row r="784">
-      <c r="A784" s="9" t="n"/>
+      <c r="A784" s="5" t="n"/>
     </row>
     <row r="785">
-      <c r="A785" s="9" t="n"/>
+      <c r="A785" s="5" t="n"/>
     </row>
     <row r="786">
-      <c r="A786" s="9" t="n"/>
+      <c r="A786" s="5" t="n"/>
     </row>
     <row r="787">
-      <c r="A787" s="9" t="n"/>
+      <c r="A787" s="5" t="n"/>
     </row>
     <row r="788">
-      <c r="A788" s="9" t="n"/>
+      <c r="A788" s="5" t="n"/>
     </row>
     <row r="789">
-      <c r="A789" s="9" t="n"/>
+      <c r="A789" s="5" t="n"/>
     </row>
     <row r="790">
-      <c r="A790" s="9" t="n"/>
+      <c r="A790" s="5" t="n"/>
     </row>
     <row r="791">
-      <c r="A791" s="9" t="n"/>
+      <c r="A791" s="5" t="n"/>
     </row>
     <row r="792">
-      <c r="A792" s="9" t="n"/>
+      <c r="A792" s="5" t="n"/>
     </row>
     <row r="793">
-      <c r="A793" s="9" t="n"/>
+      <c r="A793" s="5" t="n"/>
     </row>
     <row r="794">
-      <c r="A794" s="9" t="n"/>
+      <c r="A794" s="5" t="n"/>
     </row>
     <row r="795">
-      <c r="A795" s="9" t="n"/>
+      <c r="A795" s="5" t="n"/>
     </row>
     <row r="796">
-      <c r="A796" s="9" t="n"/>
+      <c r="A796" s="5" t="n"/>
     </row>
     <row r="797">
-      <c r="A797" s="9" t="n"/>
+      <c r="A797" s="5" t="n"/>
     </row>
     <row r="798">
-      <c r="A798" s="9" t="n"/>
+      <c r="A798" s="5" t="n"/>
     </row>
     <row r="799">
-      <c r="A799" s="9" t="n"/>
+      <c r="A799" s="5" t="n"/>
     </row>
     <row r="800">
-      <c r="A800" s="9" t="n"/>
+      <c r="A800" s="5" t="n"/>
     </row>
     <row r="801">
-      <c r="A801" s="9" t="n"/>
+      <c r="A801" s="5" t="n"/>
     </row>
     <row r="802">
-      <c r="A802" s="9" t="n"/>
+      <c r="A802" s="5" t="n"/>
     </row>
     <row r="803">
-      <c r="A803" s="9" t="n"/>
+      <c r="A803" s="5" t="n"/>
     </row>
     <row r="804">
-      <c r="A804" s="9" t="n"/>
+      <c r="A804" s="5" t="n"/>
     </row>
     <row r="805">
-      <c r="A805" s="9" t="n"/>
+      <c r="A805" s="5" t="n"/>
     </row>
     <row r="806">
-      <c r="A806" s="9" t="n"/>
+      <c r="A806" s="5" t="n"/>
     </row>
     <row r="807">
-      <c r="A807" s="9" t="n"/>
+      <c r="A807" s="5" t="n"/>
     </row>
     <row r="808">
-      <c r="A808" s="9" t="n"/>
+      <c r="A808" s="5" t="n"/>
     </row>
     <row r="809">
-      <c r="A809" s="9" t="n"/>
+      <c r="A809" s="5" t="n"/>
     </row>
     <row r="810">
-      <c r="A810" s="9" t="n"/>
+      <c r="A810" s="5" t="n"/>
     </row>
     <row r="811">
-      <c r="A811" s="9" t="n"/>
+      <c r="A811" s="5" t="n"/>
     </row>
     <row r="812">
-      <c r="A812" s="9" t="n"/>
+      <c r="A812" s="5" t="n"/>
     </row>
     <row r="813">
-      <c r="A813" s="9" t="n"/>
+      <c r="A813" s="5" t="n"/>
     </row>
     <row r="814">
-      <c r="A814" s="9" t="n"/>
+      <c r="A814" s="5" t="n"/>
     </row>
     <row r="815">
-      <c r="A815" s="9" t="n"/>
+      <c r="A815" s="5" t="n"/>
     </row>
     <row r="816">
-      <c r="A816" s="9" t="n"/>
+      <c r="A816" s="5" t="n"/>
     </row>
     <row r="817">
-      <c r="A817" s="9" t="n"/>
+      <c r="A817" s="5" t="n"/>
     </row>
     <row r="818">
-      <c r="A818" s="9" t="n"/>
+      <c r="A818" s="5" t="n"/>
     </row>
     <row r="819">
-      <c r="A819" s="9" t="n"/>
+      <c r="A819" s="5" t="n"/>
     </row>
     <row r="820">
-      <c r="A820" s="9" t="n"/>
+      <c r="A820" s="5" t="n"/>
     </row>
     <row r="821">
-      <c r="A821" s="9" t="n"/>
+      <c r="A821" s="5" t="n"/>
     </row>
     <row r="822">
-      <c r="A822" s="9" t="n"/>
+      <c r="A822" s="5" t="n"/>
     </row>
     <row r="823">
-      <c r="A823" s="9" t="n"/>
+      <c r="A823" s="5" t="n"/>
     </row>
     <row r="824">
-      <c r="A824" s="9" t="n"/>
+      <c r="A824" s="5" t="n"/>
     </row>
     <row r="825">
-      <c r="A825" s="9" t="n"/>
+      <c r="A825" s="5" t="n"/>
     </row>
     <row r="826">
-      <c r="A826" s="9" t="n"/>
+      <c r="A826" s="5" t="n"/>
     </row>
     <row r="827">
-      <c r="A827" s="9" t="n"/>
+      <c r="A827" s="5" t="n"/>
     </row>
     <row r="828">
-      <c r="A828" s="9" t="n"/>
+      <c r="A828" s="5" t="n"/>
     </row>
     <row r="829">
-      <c r="A829" s="9" t="n"/>
+      <c r="A829" s="5" t="n"/>
     </row>
     <row r="830">
-      <c r="A830" s="9" t="n"/>
+      <c r="A830" s="5" t="n"/>
     </row>
     <row r="831">
-      <c r="A831" s="9" t="n"/>
+      <c r="A831" s="5" t="n"/>
     </row>
     <row r="832">
-      <c r="A832" s="9" t="n"/>
+      <c r="A832" s="5" t="n"/>
     </row>
     <row r="833">
-      <c r="A833" s="9" t="n"/>
+      <c r="A833" s="5" t="n"/>
     </row>
     <row r="834">
-      <c r="A834" s="9" t="n"/>
+      <c r="A834" s="5" t="n"/>
     </row>
     <row r="835">
-      <c r="A835" s="9" t="n"/>
+      <c r="A835" s="5" t="n"/>
     </row>
     <row r="836">
-      <c r="A836" s="9" t="n"/>
+      <c r="A836" s="5" t="n"/>
     </row>
     <row r="837">
-      <c r="A837" s="9" t="n"/>
+      <c r="A837" s="5" t="n"/>
     </row>
     <row r="838">
-      <c r="A838" s="9" t="n"/>
+      <c r="A838" s="5" t="n"/>
     </row>
     <row r="839">
-      <c r="A839" s="9" t="n"/>
+      <c r="A839" s="5" t="n"/>
     </row>
     <row r="840">
-      <c r="A840" s="9" t="n"/>
+      <c r="A840" s="5" t="n"/>
     </row>
     <row r="841">
-      <c r="A841" s="9" t="n"/>
+      <c r="A841" s="5" t="n"/>
     </row>
     <row r="842">
-      <c r="A842" s="9" t="n"/>
+      <c r="A842" s="5" t="n"/>
     </row>
     <row r="843">
-      <c r="A843" s="9" t="n"/>
+      <c r="A843" s="5" t="n"/>
     </row>
     <row r="844">
-      <c r="A844" s="9" t="n"/>
+      <c r="A844" s="5" t="n"/>
     </row>
     <row r="845">
-      <c r="A845" s="9" t="n"/>
+      <c r="A845" s="5" t="n"/>
     </row>
     <row r="846">
-      <c r="A846" s="9" t="n"/>
+      <c r="A846" s="5" t="n"/>
     </row>
     <row r="847">
-      <c r="A847" s="9" t="n"/>
+      <c r="A847" s="5" t="n"/>
     </row>
     <row r="848">
-      <c r="A848" s="9" t="n"/>
+      <c r="A848" s="5" t="n"/>
     </row>
     <row r="849">
-      <c r="A849" s="9" t="n"/>
+      <c r="A849" s="5" t="n"/>
     </row>
     <row r="850">
-      <c r="A850" s="9" t="n"/>
+      <c r="A850" s="5" t="n"/>
     </row>
     <row r="851">
-      <c r="A851" s="9" t="n"/>
+      <c r="A851" s="5" t="n"/>
     </row>
     <row r="852">
-      <c r="A852" s="9" t="n"/>
+      <c r="A852" s="5" t="n"/>
     </row>
     <row r="853">
-      <c r="A853" s="9" t="n"/>
+      <c r="A853" s="5" t="n"/>
     </row>
     <row r="854">
-      <c r="A854" s="9" t="n"/>
+      <c r="A854" s="5" t="n"/>
     </row>
     <row r="855">
-      <c r="A855" s="9" t="n"/>
+      <c r="A855" s="5" t="n"/>
     </row>
     <row r="856">
-      <c r="A856" s="9" t="n"/>
+      <c r="A856" s="5" t="n"/>
     </row>
     <row r="857">
-      <c r="A857" s="9" t="n"/>
+      <c r="A857" s="5" t="n"/>
     </row>
     <row r="858">
-      <c r="A858" s="9" t="n"/>
+      <c r="A858" s="5" t="n"/>
     </row>
     <row r="859">
-      <c r="A859" s="9" t="n"/>
+      <c r="A859" s="5" t="n"/>
     </row>
     <row r="860">
-      <c r="A860" s="9" t="n"/>
+      <c r="A860" s="5" t="n"/>
     </row>
     <row r="861">
-      <c r="A861" s="9" t="n"/>
+      <c r="A861" s="5" t="n"/>
     </row>
     <row r="862">
-      <c r="A862" s="9" t="n"/>
+      <c r="A862" s="5" t="n"/>
     </row>
     <row r="863">
-      <c r="A863" s="9" t="n"/>
+      <c r="A863" s="5" t="n"/>
     </row>
     <row r="864">
-      <c r="A864" s="9" t="n"/>
+      <c r="A864" s="5" t="n"/>
     </row>
     <row r="865">
-      <c r="A865" s="9" t="n"/>
+      <c r="A865" s="5" t="n"/>
     </row>
     <row r="866">
-      <c r="A866" s="9" t="n"/>
+      <c r="A866" s="5" t="n"/>
     </row>
     <row r="867">
-      <c r="A867" s="9" t="n"/>
+      <c r="A867" s="5" t="n"/>
     </row>
     <row r="868">
-      <c r="A868" s="9" t="n"/>
+      <c r="A868" s="5" t="n"/>
     </row>
     <row r="869">
-      <c r="A869" s="9" t="n"/>
+      <c r="A869" s="5" t="n"/>
     </row>
     <row r="870">
-      <c r="A870" s="9" t="n"/>
+      <c r="A870" s="5" t="n"/>
     </row>
     <row r="871">
-      <c r="A871" s="9" t="n"/>
+      <c r="A871" s="5" t="n"/>
     </row>
     <row r="872">
-      <c r="A872" s="9" t="n"/>
+      <c r="A872" s="5" t="n"/>
     </row>
     <row r="873">
-      <c r="A873" s="9" t="n"/>
+      <c r="A873" s="5" t="n"/>
     </row>
     <row r="874">
-      <c r="A874" s="9" t="n"/>
+      <c r="A874" s="5" t="n"/>
     </row>
     <row r="875">
-      <c r="A875" s="9" t="n"/>
+      <c r="A875" s="5" t="n"/>
     </row>
     <row r="876">
-      <c r="A876" s="9" t="n"/>
+      <c r="A876" s="5" t="n"/>
     </row>
     <row r="877">
-      <c r="A877" s="9" t="n"/>
+      <c r="A877" s="5" t="n"/>
     </row>
     <row r="878">
-      <c r="A878" s="9" t="n"/>
+      <c r="A878" s="5" t="n"/>
     </row>
     <row r="879">
-      <c r="A879" s="9" t="n"/>
+      <c r="A879" s="5" t="n"/>
     </row>
     <row r="880">
-      <c r="A880" s="9" t="n"/>
+      <c r="A880" s="5" t="n"/>
     </row>
     <row r="881">
-      <c r="A881" s="9" t="n"/>
+      <c r="A881" s="5" t="n"/>
     </row>
     <row r="882">
-      <c r="A882" s="9" t="n"/>
+      <c r="A882" s="5" t="n"/>
     </row>
     <row r="883">
-      <c r="A883" s="9" t="n"/>
+      <c r="A883" s="5" t="n"/>
     </row>
     <row r="884">
-      <c r="A884" s="9" t="n"/>
+      <c r="A884" s="5" t="n"/>
     </row>
     <row r="885">
-      <c r="A885" s="9" t="n"/>
+      <c r="A885" s="5" t="n"/>
     </row>
     <row r="886">
-      <c r="A886" s="9" t="n"/>
+      <c r="A886" s="5" t="n"/>
     </row>
     <row r="887">
-      <c r="A887" s="9" t="n"/>
+      <c r="A887" s="5" t="n"/>
     </row>
     <row r="888">
-      <c r="A888" s="9" t="n"/>
+      <c r="A888" s="5" t="n"/>
     </row>
     <row r="889">
-      <c r="A889" s="9" t="n"/>
+      <c r="A889" s="5" t="n"/>
     </row>
     <row r="890">
-      <c r="A890" s="9" t="n"/>
+      <c r="A890" s="5" t="n"/>
     </row>
     <row r="891">
-      <c r="A891" s="9" t="n"/>
+      <c r="A891" s="5" t="n"/>
     </row>
     <row r="892">
-      <c r="A892" s="9" t="n"/>
+      <c r="A892" s="5" t="n"/>
     </row>
     <row r="893">
-      <c r="A893" s="9" t="n"/>
+      <c r="A893" s="5" t="n"/>
     </row>
     <row r="894">
-      <c r="A894" s="9" t="n"/>
+      <c r="A894" s="5" t="n"/>
     </row>
     <row r="895">
-      <c r="A895" s="9" t="n"/>
+      <c r="A895" s="5" t="n"/>
     </row>
     <row r="896">
-      <c r="A896" s="9" t="n"/>
+      <c r="A896" s="5" t="n"/>
     </row>
     <row r="897">
-      <c r="A897" s="9" t="n"/>
+      <c r="A897" s="5" t="n"/>
     </row>
     <row r="898">
-      <c r="A898" s="9" t="n"/>
+      <c r="A898" s="5" t="n"/>
     </row>
     <row r="899">
-      <c r="A899" s="9" t="n"/>
+      <c r="A899" s="5" t="n"/>
     </row>
     <row r="900">
-      <c r="A900" s="9" t="n"/>
+      <c r="A900" s="5" t="n"/>
     </row>
     <row r="901">
-      <c r="A901" s="9" t="n"/>
+      <c r="A901" s="5" t="n"/>
     </row>
     <row r="902">
-      <c r="A902" s="9" t="n"/>
+      <c r="A902" s="5" t="n"/>
     </row>
     <row r="903">
-      <c r="A903" s="9" t="n"/>
+      <c r="A903" s="5" t="n"/>
     </row>
     <row r="904">
-      <c r="A904" s="9" t="n"/>
+      <c r="A904" s="5" t="n"/>
     </row>
     <row r="905">
-      <c r="A905" s="9" t="n"/>
+      <c r="A905" s="5" t="n"/>
     </row>
     <row r="906">
-      <c r="A906" s="9" t="n"/>
+      <c r="A906" s="5" t="n"/>
     </row>
     <row r="907">
-      <c r="A907" s="9" t="n"/>
+      <c r="A907" s="5" t="n"/>
     </row>
     <row r="908">
-      <c r="A908" s="9" t="n"/>
+      <c r="A908" s="5" t="n"/>
     </row>
     <row r="909">
-      <c r="A909" s="9" t="n"/>
+      <c r="A909" s="5" t="n"/>
     </row>
     <row r="910">
-      <c r="A910" s="9" t="n"/>
+      <c r="A910" s="5" t="n"/>
     </row>
     <row r="911">
-      <c r="A911" s="9" t="n"/>
+      <c r="A911" s="5" t="n"/>
     </row>
     <row r="912">
-      <c r="A912" s="9" t="n"/>
+      <c r="A912" s="5" t="n"/>
     </row>
     <row r="913">
-      <c r="A913" s="9" t="n"/>
+      <c r="A913" s="5" t="n"/>
     </row>
     <row r="914">
-      <c r="A914" s="9" t="n"/>
+      <c r="A914" s="5" t="n"/>
     </row>
     <row r="915">
-      <c r="A915" s="9" t="n"/>
+      <c r="A915" s="5" t="n"/>
     </row>
     <row r="916">
-      <c r="A916" s="9" t="n"/>
+      <c r="A916" s="5" t="n"/>
     </row>
     <row r="917">
-      <c r="A917" s="9" t="n"/>
+      <c r="A917" s="5" t="n"/>
     </row>
     <row r="918">
-      <c r="A918" s="9" t="n"/>
+      <c r="A918" s="5" t="n"/>
     </row>
     <row r="919">
-      <c r="A919" s="9" t="n"/>
+      <c r="A919" s="5" t="n"/>
     </row>
     <row r="920">
-      <c r="A920" s="9" t="n"/>
+      <c r="A920" s="5" t="n"/>
     </row>
     <row r="921">
-      <c r="A921" s="9" t="n"/>
+      <c r="A921" s="5" t="n"/>
     </row>
     <row r="922">
-      <c r="A922" s="9" t="n"/>
+      <c r="A922" s="5" t="n"/>
     </row>
     <row r="923">
-      <c r="A923" s="9" t="n"/>
+      <c r="A923" s="5" t="n"/>
     </row>
     <row r="924">
-      <c r="A924" s="9" t="n"/>
+      <c r="A924" s="5" t="n"/>
     </row>
     <row r="925">
-      <c r="A925" s="9" t="n"/>
+      <c r="A925" s="5" t="n"/>
     </row>
     <row r="926">
-      <c r="A926" s="9" t="n"/>
+      <c r="A926" s="5" t="n"/>
     </row>
     <row r="927">
-      <c r="A927" s="9" t="n"/>
+      <c r="A927" s="5" t="n"/>
     </row>
     <row r="928">
-      <c r="A928" s="9" t="n"/>
+      <c r="A928" s="5" t="n"/>
     </row>
     <row r="929">
-      <c r="A929" s="9" t="n"/>
+      <c r="A929" s="5" t="n"/>
     </row>
     <row r="930">
-      <c r="A930" s="9" t="n"/>
+      <c r="A930" s="5" t="n"/>
     </row>
     <row r="931">
-      <c r="A931" s="9" t="n"/>
+      <c r="A931" s="5" t="n"/>
     </row>
     <row r="932">
-      <c r="A932" s="9" t="n"/>
+      <c r="A932" s="5" t="n"/>
     </row>
     <row r="933">
-      <c r="A933" s="9" t="n"/>
+      <c r="A933" s="5" t="n"/>
     </row>
     <row r="934">
-      <c r="A934" s="9" t="n"/>
+      <c r="A934" s="5" t="n"/>
     </row>
     <row r="935">
-      <c r="A935" s="9" t="n"/>
+      <c r="A935" s="5" t="n"/>
     </row>
     <row r="936">
-      <c r="A936" s="9" t="n"/>
+      <c r="A936" s="5" t="n"/>
     </row>
     <row r="937">
-      <c r="A937" s="9" t="n"/>
+      <c r="A937" s="5" t="n"/>
     </row>
     <row r="938">
-      <c r="A938" s="9" t="n"/>
+      <c r="A938" s="5" t="n"/>
     </row>
     <row r="939">
-      <c r="A939" s="9" t="n"/>
+      <c r="A939" s="5" t="n"/>
     </row>
     <row r="940">
-      <c r="A940" s="9" t="n"/>
+      <c r="A940" s="5" t="n"/>
     </row>
     <row r="941">
-      <c r="A941" s="9" t="n"/>
+      <c r="A941" s="5" t="n"/>
     </row>
     <row r="942">
-      <c r="A942" s="9" t="n"/>
+      <c r="A942" s="5" t="n"/>
     </row>
     <row r="943">
-      <c r="A943" s="9" t="n"/>
+      <c r="A943" s="5" t="n"/>
     </row>
     <row r="944">
-      <c r="A944" s="9" t="n"/>
+      <c r="A944" s="5" t="n"/>
     </row>
     <row r="945">
-      <c r="A945" s="9" t="n"/>
+      <c r="A945" s="5" t="n"/>
     </row>
     <row r="946">
-      <c r="A946" s="9" t="n"/>
+      <c r="A946" s="5" t="n"/>
     </row>
     <row r="947">
-      <c r="A947" s="9" t="n"/>
+      <c r="A947" s="5" t="n"/>
     </row>
     <row r="948">
-      <c r="A948" s="9" t="n"/>
+      <c r="A948" s="5" t="n"/>
     </row>
     <row r="949">
-      <c r="A949" s="9" t="n"/>
+      <c r="A949" s="5" t="n"/>
     </row>
     <row r="950">
-      <c r="A950" s="9" t="n"/>
+      <c r="A950" s="5" t="n"/>
     </row>
     <row r="951">
-      <c r="A951" s="9" t="n"/>
+      <c r="A951" s="5" t="n"/>
     </row>
     <row r="952">
-      <c r="A952" s="9" t="n"/>
+      <c r="A952" s="5" t="n"/>
     </row>
     <row r="953">
-      <c r="A953" s="9" t="n"/>
+      <c r="A953" s="5" t="n"/>
     </row>
     <row r="954">
-      <c r="A954" s="9" t="n"/>
+      <c r="A954" s="5" t="n"/>
     </row>
     <row r="955">
-      <c r="A955" s="9" t="n"/>
+      <c r="A955" s="5" t="n"/>
     </row>
     <row r="956">
-      <c r="A956" s="9" t="n"/>
+      <c r="A956" s="5" t="n"/>
     </row>
     <row r="957">
-      <c r="A957" s="9" t="n"/>
+      <c r="A957" s="5" t="n"/>
     </row>
     <row r="958">
-      <c r="A958" s="9" t="n"/>
+      <c r="A958" s="5" t="n"/>
     </row>
     <row r="959">
-      <c r="A959" s="9" t="n"/>
+      <c r="A959" s="5" t="n"/>
     </row>
     <row r="960">
-      <c r="A960" s="9" t="n"/>
+      <c r="A960" s="5" t="n"/>
     </row>
     <row r="961">
-      <c r="A961" s="9" t="n"/>
+      <c r="A961" s="5" t="n"/>
     </row>
     <row r="962">
-      <c r="A962" s="9" t="n"/>
+      <c r="A962" s="5" t="n"/>
     </row>
     <row r="963">
-      <c r="A963" s="9" t="n"/>
+      <c r="A963" s="5" t="n"/>
     </row>
     <row r="964">
-      <c r="A964" s="9" t="n"/>
+      <c r="A964" s="5" t="n"/>
     </row>
     <row r="965">
-      <c r="A965" s="9" t="n"/>
+      <c r="A965" s="5" t="n"/>
     </row>
     <row r="966">
-      <c r="A966" s="9" t="n"/>
+      <c r="A966" s="5" t="n"/>
     </row>
     <row r="967">
-      <c r="A967" s="9" t="n"/>
+      <c r="A967" s="5" t="n"/>
     </row>
     <row r="968">
-      <c r="A968" s="9" t="n"/>
+      <c r="A968" s="5" t="n"/>
     </row>
     <row r="969">
-      <c r="A969" s="9" t="n"/>
+      <c r="A969" s="5" t="n"/>
     </row>
     <row r="970">
-      <c r="A970" s="9" t="n"/>
+      <c r="A970" s="5" t="n"/>
     </row>
     <row r="971">
-      <c r="A971" s="9" t="n"/>
+      <c r="A971" s="5" t="n"/>
     </row>
     <row r="972">
-      <c r="A972" s="9" t="n"/>
+      <c r="A972" s="5" t="n"/>
     </row>
     <row r="973">
-      <c r="A973" s="9" t="n"/>
+      <c r="A973" s="5" t="n"/>
     </row>
     <row r="974">
-      <c r="A974" s="9" t="n"/>
+      <c r="A974" s="5" t="n"/>
     </row>
     <row r="975">
-      <c r="A975" s="9" t="n"/>
+      <c r="A975" s="5" t="n"/>
     </row>
     <row r="976">
-      <c r="A976" s="9" t="n"/>
+      <c r="A976" s="5" t="n"/>
     </row>
     <row r="977">
-      <c r="A977" s="9" t="n"/>
+      <c r="A977" s="5" t="n"/>
     </row>
     <row r="978">
-      <c r="A978" s="9" t="n"/>
+      <c r="A978" s="5" t="n"/>
     </row>
     <row r="979">
-      <c r="A979" s="9" t="n"/>
+      <c r="A979" s="5" t="n"/>
     </row>
     <row r="980">
-      <c r="A980" s="9" t="n"/>
+      <c r="A980" s="5" t="n"/>
     </row>
     <row r="981">
-      <c r="A981" s="9" t="n"/>
+      <c r="A981" s="5" t="n"/>
     </row>
     <row r="982">
-      <c r="A982" s="9" t="n"/>
+      <c r="A982" s="5" t="n"/>
     </row>
     <row r="983">
-      <c r="A983" s="9" t="n"/>
+      <c r="A983" s="5" t="n"/>
     </row>
     <row r="984">
-      <c r="A984" s="9" t="n"/>
+      <c r="A984" s="5" t="n"/>
     </row>
     <row r="985">
-      <c r="A985" s="9" t="n"/>
+      <c r="A985" s="5" t="n"/>
     </row>
     <row r="986">
-      <c r="A986" s="9" t="n"/>
+      <c r="A986" s="5" t="n"/>
     </row>
     <row r="987">
-      <c r="A987" s="9" t="n"/>
+      <c r="A987" s="5" t="n"/>
     </row>
     <row r="988">
-      <c r="A988" s="9" t="n"/>
+      <c r="A988" s="5" t="n"/>
     </row>
     <row r="989">
-      <c r="A989" s="9" t="n"/>
+      <c r="A989" s="5" t="n"/>
     </row>
     <row r="990">
-      <c r="A990" s="9" t="n"/>
+      <c r="A990" s="5" t="n"/>
     </row>
     <row r="991">
-      <c r="A991" s="9" t="n"/>
+      <c r="A991" s="5" t="n"/>
     </row>
     <row r="992">
-      <c r="A992" s="9" t="n"/>
+      <c r="A992" s="5" t="n"/>
     </row>
     <row r="993">
-      <c r="A993" s="9" t="n"/>
+      <c r="A993" s="5" t="n"/>
     </row>
     <row r="994">
-      <c r="A994" s="9" t="n"/>
+      <c r="A994" s="5" t="n"/>
     </row>
     <row r="995">
-      <c r="A995" s="9" t="n"/>
+      <c r="A995" s="5" t="n"/>
     </row>
     <row r="996">
-      <c r="A996" s="9" t="n"/>
+      <c r="A996" s="5" t="n"/>
     </row>
     <row r="997">
-      <c r="A997" s="9" t="n"/>
+      <c r="A997" s="5" t="n"/>
     </row>
     <row r="998">
-      <c r="A998" s="9" t="n"/>
+      <c r="A998" s="5" t="n"/>
     </row>
     <row r="999">
-      <c r="A999" s="9" t="n"/>
+      <c r="A999" s="5" t="n"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="9" t="n"/>
+      <c r="A1000" s="5" t="n"/>
     </row>
     <row r="1001">
-      <c r="A1001" s="9" t="n"/>
+      <c r="A1001" s="5" t="n"/>
     </row>
     <row r="1002">
-      <c r="A1002" s="9" t="n"/>
+      <c r="A1002" s="5" t="n"/>
     </row>
     <row r="1003">
-      <c r="A1003" s="9" t="n"/>
+      <c r="A1003" s="5" t="n"/>
     </row>
     <row r="1004">
-      <c r="A1004" s="9" t="n"/>
+      <c r="A1004" s="5" t="n"/>
     </row>
     <row r="1005">
-      <c r="A1005" s="9" t="n"/>
+      <c r="A1005" s="5" t="n"/>
     </row>
     <row r="1006">
-      <c r="A1006" s="9" t="n"/>
+      <c r="A1006" s="5" t="n"/>
     </row>
     <row r="1007">
-      <c r="A1007" s="9" t="n"/>
+      <c r="A1007" s="5" t="n"/>
     </row>
     <row r="1008">
-      <c r="A1008" s="9" t="n"/>
+      <c r="A1008" s="5" t="n"/>
     </row>
     <row r="1009">
-      <c r="A1009" s="9" t="n"/>
+      <c r="A1009" s="5" t="n"/>
     </row>
     <row r="1010">
-      <c r="A1010" s="9" t="n"/>
+      <c r="A1010" s="5" t="n"/>
     </row>
     <row r="1011">
-      <c r="A1011" s="9" t="n"/>
+      <c r="A1011" s="5" t="n"/>
     </row>
     <row r="1012">
-      <c r="A1012" s="9" t="n"/>
+      <c r="A1012" s="5" t="n"/>
     </row>
     <row r="1013">
-      <c r="A1013" s="9" t="n"/>
+      <c r="A1013" s="5" t="n"/>
     </row>
     <row r="1014">
-      <c r="A1014" s="9" t="n"/>
+      <c r="A1014" s="5" t="n"/>
     </row>
     <row r="1015">
-      <c r="A1015" s="9" t="n"/>
+      <c r="A1015" s="5" t="n"/>
     </row>
     <row r="1016">
-      <c r="A1016" s="9" t="n"/>
+      <c r="A1016" s="5" t="n"/>
     </row>
     <row r="1017">
-      <c r="A1017" s="9" t="n"/>
+      <c r="A1017" s="5" t="n"/>
     </row>
     <row r="1018">
-      <c r="A1018" s="9" t="n"/>
+      <c r="A1018" s="5" t="n"/>
     </row>
     <row r="1019">
-      <c r="A1019" s="9" t="n"/>
+      <c r="A1019" s="5" t="n"/>
     </row>
     <row r="1020">
-      <c r="A1020" s="9" t="n"/>
+      <c r="A1020" s="5" t="n"/>
     </row>
     <row r="1021">
-      <c r="A1021" s="9" t="n"/>
+      <c r="A1021" s="5" t="n"/>
     </row>
     <row r="1022">
-      <c r="A1022" s="9" t="n"/>
+      <c r="A1022" s="5" t="n"/>
     </row>
     <row r="1023">
-      <c r="A1023" s="9" t="n"/>
+      <c r="A1023" s="5" t="n"/>
     </row>
     <row r="1024">
-      <c r="A1024" s="9" t="n"/>
+      <c r="A1024" s="5" t="n"/>
     </row>
     <row r="1025">
-      <c r="A1025" s="9" t="n"/>
+      <c r="A1025" s="5" t="n"/>
     </row>
     <row r="1026">
-      <c r="A1026" s="9" t="n"/>
+      <c r="A1026" s="5" t="n"/>
     </row>
     <row r="1027">
-      <c r="A1027" s="9" t="n"/>
+      <c r="A1027" s="5" t="n"/>
     </row>
     <row r="1028">
-      <c r="A1028" s="9" t="n"/>
+      <c r="A1028" s="5" t="n"/>
     </row>
     <row r="1029">
-      <c r="A1029" s="9" t="n"/>
+      <c r="A1029" s="5" t="n"/>
     </row>
     <row r="1030">
-      <c r="A1030" s="9" t="n"/>
+      <c r="A1030" s="5" t="n"/>
     </row>
     <row r="1031">
-      <c r="A1031" s="9" t="n"/>
+      <c r="A1031" s="5" t="n"/>
     </row>
     <row r="1032">
-      <c r="A1032" s="9" t="n"/>
+      <c r="A1032" s="5" t="n"/>
     </row>
     <row r="1033">
-      <c r="A1033" s="9" t="n"/>
+      <c r="A1033" s="5" t="n"/>
     </row>
     <row r="1034">
-      <c r="A1034" s="9" t="n"/>
+      <c r="A1034" s="5" t="n"/>
     </row>
     <row r="1035">
-      <c r="A1035" s="9" t="n"/>
+      <c r="A1035" s="5" t="n"/>
     </row>
     <row r="1036">
-      <c r="A1036" s="9" t="n"/>
+      <c r="A1036" s="5" t="n"/>
     </row>
     <row r="1037">
-      <c r="A1037" s="9" t="n"/>
+      <c r="A1037" s="5" t="n"/>
     </row>
     <row r="1038">
-      <c r="A1038" s="9" t="n"/>
+      <c r="A1038" s="5" t="n"/>
     </row>
     <row r="1039">
-      <c r="A1039" s="9" t="n"/>
+      <c r="A1039" s="5" t="n"/>
     </row>
     <row r="1040">
-      <c r="A1040" s="9" t="n"/>
+      <c r="A1040" s="5" t="n"/>
     </row>
     <row r="1041">
-      <c r="A1041" s="9" t="n"/>
+      <c r="A1041" s="5" t="n"/>
     </row>
     <row r="1042">
-      <c r="A1042" s="9" t="n"/>
+      <c r="A1042" s="5" t="n"/>
     </row>
     <row r="1043">
-      <c r="A1043" s="9" t="n"/>
+      <c r="A1043" s="5" t="n"/>
     </row>
     <row r="1044">
-      <c r="A1044" s="9" t="n"/>
+      <c r="A1044" s="5" t="n"/>
     </row>
     <row r="1045">
-      <c r="A1045" s="9" t="n"/>
+      <c r="A1045" s="5" t="n"/>
     </row>
     <row r="1046">
-      <c r="A1046" s="9" t="n"/>
+      <c r="A1046" s="5" t="n"/>
     </row>
     <row r="1047">
-      <c r="A1047" s="9" t="n"/>
+      <c r="A1047" s="5" t="n"/>
     </row>
     <row r="1048">
-      <c r="A1048" s="9" t="n"/>
+      <c r="A1048" s="5" t="n"/>
     </row>
     <row r="1049">
-      <c r="A1049" s="9" t="n"/>
+      <c r="A1049" s="5" t="n"/>
     </row>
     <row r="1050">
-      <c r="A1050" s="9" t="n"/>
+      <c r="A1050" s="5" t="n"/>
     </row>
     <row r="1051">
-      <c r="A1051" s="9" t="n"/>
+      <c r="A1051" s="5" t="n"/>
     </row>
     <row r="1052">
-      <c r="A1052" s="9" t="n"/>
+      <c r="A1052" s="5" t="n"/>
     </row>
     <row r="1053">
-      <c r="A1053" s="9" t="n"/>
+      <c r="A1053" s="5" t="n"/>
     </row>
     <row r="1054">
-      <c r="A1054" s="9" t="n"/>
+      <c r="A1054" s="5" t="n"/>
     </row>
     <row r="1055">
-      <c r="A1055" s="9" t="n"/>
+      <c r="A1055" s="5" t="n"/>
     </row>
     <row r="1056">
-      <c r="A1056" s="9" t="n"/>
+      <c r="A1056" s="5" t="n"/>
     </row>
     <row r="1057">
-      <c r="A1057" s="9" t="n"/>
+      <c r="A1057" s="5" t="n"/>
     </row>
     <row r="1058">
-      <c r="A1058" s="9" t="n"/>
+      <c r="A1058" s="5" t="n"/>
     </row>
     <row r="1059">
-      <c r="A1059" s="9" t="n"/>
+      <c r="A1059" s="5" t="n"/>
     </row>
     <row r="1060">
-      <c r="A1060" s="9" t="n"/>
+      <c r="A1060" s="5" t="n"/>
     </row>
     <row r="1061">
-      <c r="A1061" s="9" t="n"/>
+      <c r="A1061" s="5" t="n"/>
     </row>
     <row r="1062">
-      <c r="A1062" s="9" t="n"/>
+      <c r="A1062" s="5" t="n"/>
     </row>
     <row r="1063">
-      <c r="A1063" s="9" t="n"/>
+      <c r="A1063" s="5" t="n"/>
     </row>
     <row r="1064">
-      <c r="A1064" s="9" t="n"/>
+      <c r="A1064" s="5" t="n"/>
     </row>
     <row r="1065">
-      <c r="A1065" s="9" t="n"/>
+      <c r="A1065" s="5" t="n"/>
     </row>
     <row r="1066">
-      <c r="A1066" s="9" t="n"/>
+      <c r="A1066" s="5" t="n"/>
     </row>
     <row r="1067">
-      <c r="A1067" s="9" t="n"/>
+      <c r="A1067" s="5" t="n"/>
     </row>
     <row r="1068">
-      <c r="A1068" s="9" t="n"/>
+      <c r="A1068" s="5" t="n"/>
     </row>
     <row r="1069">
-      <c r="A1069" s="9" t="n"/>
+      <c r="A1069" s="5" t="n"/>
     </row>
     <row r="1070">
-      <c r="A1070" s="9" t="n"/>
+      <c r="A1070" s="5" t="n"/>
     </row>
     <row r="1071">
-      <c r="A1071" s="9" t="n"/>
+      <c r="A1071" s="5" t="n"/>
     </row>
     <row r="1072">
-      <c r="A1072" s="9" t="n"/>
+      <c r="A1072" s="5" t="n"/>
     </row>
     <row r="1073">
-      <c r="A1073" s="9" t="n"/>
+      <c r="A1073" s="5" t="n"/>
     </row>
     <row r="1074">
-      <c r="A1074" s="9" t="n"/>
+      <c r="A1074" s="5" t="n"/>
     </row>
     <row r="1075">
-      <c r="A1075" s="9" t="n"/>
+      <c r="A1075" s="5" t="n"/>
     </row>
     <row r="1076">
-      <c r="A1076" s="9" t="n"/>
+      <c r="A1076" s="5" t="n"/>
     </row>
     <row r="1077">
-      <c r="A1077" s="9" t="n"/>
+      <c r="A1077" s="5" t="n"/>
     </row>
     <row r="1078">
-      <c r="A1078" s="9" t="n"/>
+      <c r="A1078" s="5" t="n"/>
     </row>
     <row r="1079">
-      <c r="A1079" s="9" t="n"/>
+      <c r="A1079" s="5" t="n"/>
     </row>
     <row r="1080">
-      <c r="A1080" s="9" t="n"/>
+      <c r="A1080" s="5" t="n"/>
     </row>
     <row r="1081">
-      <c r="A1081" s="9" t="n"/>
+      <c r="A1081" s="5" t="n"/>
     </row>
     <row r="1082">
-      <c r="A1082" s="9" t="n"/>
+      <c r="A1082" s="5" t="n"/>
     </row>
     <row r="1083">
-      <c r="A1083" s="9" t="n"/>
+      <c r="A1083" s="5" t="n"/>
     </row>
     <row r="1084">
-      <c r="A1084" s="9" t="n"/>
+      <c r="A1084" s="5" t="n"/>
     </row>
     <row r="1085">
-      <c r="A1085" s="9" t="n"/>
+      <c r="A1085" s="5" t="n"/>
     </row>
     <row r="1086">
-      <c r="A1086" s="9" t="n"/>
+      <c r="A1086" s="5" t="n"/>
     </row>
     <row r="1087">
-      <c r="A1087" s="9" t="n"/>
+      <c r="A1087" s="5" t="n"/>
     </row>
     <row r="1088">
-      <c r="A1088" s="9" t="n"/>
+      <c r="A1088" s="5" t="n"/>
     </row>
     <row r="1089">
-      <c r="A1089" s="9" t="n"/>
+      <c r="A1089" s="5" t="n"/>
     </row>
     <row r="1090">
-      <c r="A1090" s="9" t="n"/>
+      <c r="A1090" s="5" t="n"/>
     </row>
     <row r="1091">
-      <c r="A1091" s="9" t="n"/>
+      <c r="A1091" s="5" t="n"/>
     </row>
     <row r="1092">
-      <c r="A1092" s="9" t="n"/>
+      <c r="A1092" s="5" t="n"/>
     </row>
     <row r="1093">
-      <c r="A1093" s="9" t="n"/>
+      <c r="A1093" s="5" t="n"/>
     </row>
     <row r="1094">
-      <c r="A1094" s="9" t="n"/>
+      <c r="A1094" s="5" t="n"/>
     </row>
     <row r="1095">
-      <c r="A1095" s="9" t="n"/>
+      <c r="A1095" s="5" t="n"/>
     </row>
     <row r="1096">
-      <c r="A1096" s="9" t="n"/>
+      <c r="A1096" s="5" t="n"/>
     </row>
     <row r="1097">
-      <c r="A1097" s="9" t="n"/>
+      <c r="A1097" s="5" t="n"/>
     </row>
     <row r="1098">
-      <c r="A1098" s="9" t="n"/>
+      <c r="A1098" s="5" t="n"/>
     </row>
     <row r="1099">
-      <c r="A1099" s="9" t="n"/>
+      <c r="A1099" s="5" t="n"/>
     </row>
     <row r="1100">
-      <c r="A1100" s="9" t="n"/>
+      <c r="A1100" s="5" t="n"/>
     </row>
     <row r="1101">
-      <c r="A1101" s="9" t="n"/>
+      <c r="A1101" s="5" t="n"/>
     </row>
     <row r="1102">
-      <c r="A1102" s="9" t="n"/>
+      <c r="A1102" s="5" t="n"/>
     </row>
     <row r="1103">
-      <c r="A1103" s="9" t="n"/>
+      <c r="A1103" s="5" t="n"/>
     </row>
     <row r="1104">
-      <c r="A1104" s="9" t="n"/>
+      <c r="A1104" s="5" t="n"/>
     </row>
     <row r="1105">
-      <c r="A1105" s="9" t="n"/>
+      <c r="A1105" s="5" t="n"/>
     </row>
     <row r="1106">
-      <c r="A1106" s="9" t="n"/>
+      <c r="A1106" s="5" t="n"/>
     </row>
     <row r="1107">
-      <c r="A1107" s="9" t="n"/>
+      <c r="A1107" s="5" t="n"/>
     </row>
     <row r="1108">
-      <c r="A1108" s="9" t="n"/>
+      <c r="A1108" s="5" t="n"/>
     </row>
     <row r="1109">
-      <c r="A1109" s="9" t="n"/>
+      <c r="A1109" s="5" t="n"/>
     </row>
     <row r="1110">
-      <c r="A1110" s="9" t="n"/>
+      <c r="A1110" s="5" t="n"/>
     </row>
     <row r="1111">
-      <c r="A1111" s="9" t="n"/>
+      <c r="A1111" s="5" t="n"/>
     </row>
     <row r="1112">
-      <c r="A1112" s="9" t="n"/>
+      <c r="A1112" s="5" t="n"/>
     </row>
     <row r="1113">
-      <c r="A1113" s="9" t="n"/>
+      <c r="A1113" s="5" t="n"/>
     </row>
     <row r="1114">
-      <c r="A1114" s="9" t="n"/>
+      <c r="A1114" s="5" t="n"/>
     </row>
     <row r="1115">
-      <c r="A1115" s="9" t="n"/>
+      <c r="A1115" s="5" t="n"/>
     </row>
     <row r="1116">
-      <c r="A1116" s="9" t="n"/>
+      <c r="A1116" s="5" t="n"/>
     </row>
     <row r="1117">
-      <c r="A1117" s="9" t="n"/>
+      <c r="A1117" s="5" t="n"/>
     </row>
     <row r="1118">
-      <c r="A1118" s="9" t="n"/>
+      <c r="A1118" s="5" t="n"/>
     </row>
     <row r="1119">
-      <c r="A1119" s="9" t="n"/>
+      <c r="A1119" s="5" t="n"/>
     </row>
     <row r="1120">
-      <c r="A1120" s="9" t="n"/>
+      <c r="A1120" s="5" t="n"/>
     </row>
     <row r="1121">
-      <c r="A1121" s="9" t="n"/>
+      <c r="A1121" s="5" t="n"/>
     </row>
     <row r="1122">
-      <c r="A1122" s="9" t="n"/>
+      <c r="A1122" s="5" t="n"/>
     </row>
     <row r="1123">
-      <c r="A1123" s="9" t="n"/>
+      <c r="A1123" s="5" t="n"/>
     </row>
     <row r="1124">
-      <c r="A1124" s="9" t="n"/>
+      <c r="A1124" s="5" t="n"/>
     </row>
     <row r="1125">
-      <c r="A1125" s="9" t="n"/>
+      <c r="A1125" s="5" t="n"/>
     </row>
     <row r="1126">
-      <c r="A1126" s="9" t="n"/>
+      <c r="A1126" s="5" t="n"/>
     </row>
     <row r="1127">
-      <c r="A1127" s="9" t="n"/>
+      <c r="A1127" s="5" t="n"/>
     </row>
     <row r="1128">
-      <c r="A1128" s="9" t="n"/>
+      <c r="A1128" s="5" t="n"/>
     </row>
     <row r="1129">
-      <c r="A1129" s="9" t="n"/>
+      <c r="A1129" s="5" t="n"/>
     </row>
     <row r="1130">
-      <c r="A1130" s="9" t="n"/>
+      <c r="A1130" s="5" t="n"/>
     </row>
     <row r="1131">
-      <c r="A1131" s="9" t="n"/>
+      <c r="A1131" s="5" t="n"/>
     </row>
     <row r="1132">
-      <c r="A1132" s="9" t="n"/>
+      <c r="A1132" s="5" t="n"/>
     </row>
     <row r="1133">
-      <c r="A1133" s="9" t="n"/>
+      <c r="A1133" s="5" t="n"/>
     </row>
     <row r="1134">
-      <c r="A1134" s="9" t="n"/>
+      <c r="A1134" s="5" t="n"/>
     </row>
     <row r="1135">
-      <c r="A1135" s="9" t="n"/>
+      <c r="A1135" s="5" t="n"/>
     </row>
     <row r="1136">
-      <c r="A1136" s="9" t="n"/>
+      <c r="A1136" s="5" t="n"/>
     </row>
     <row r="1137">
-      <c r="A1137" s="9" t="n"/>
+      <c r="A1137" s="5" t="n"/>
     </row>
     <row r="1138">
-      <c r="A1138" s="9" t="n"/>
+      <c r="A1138" s="5" t="n"/>
     </row>
     <row r="1139">
-      <c r="A1139" s="9" t="n"/>
+      <c r="A1139" s="5" t="n"/>
     </row>
     <row r="1140">
-      <c r="A1140" s="9" t="n"/>
+      <c r="A1140" s="5" t="n"/>
     </row>
     <row r="1141">
-      <c r="A1141" s="9" t="n"/>
+      <c r="A1141" s="5" t="n"/>
     </row>
     <row r="1142">
-      <c r="A1142" s="9" t="n"/>
+      <c r="A1142" s="5" t="n"/>
     </row>
     <row r="1143">
-      <c r="A1143" s="9" t="n"/>
+      <c r="A1143" s="5" t="n"/>
     </row>
     <row r="1144">
-      <c r="A1144" s="9" t="n"/>
+      <c r="A1144" s="5" t="n"/>
     </row>
     <row r="1145">
-      <c r="A1145" s="9" t="n"/>
+      <c r="A1145" s="5" t="n"/>
     </row>
     <row r="1146">
-      <c r="A1146" s="9" t="n"/>
+      <c r="A1146" s="5" t="n"/>
     </row>
     <row r="1147">
-      <c r="A1147" s="9" t="n"/>
+      <c r="A1147" s="5" t="n"/>
     </row>
     <row r="1148">
-      <c r="A1148" s="9" t="n"/>
+      <c r="A1148" s="5" t="n"/>
     </row>
     <row r="1149">
-      <c r="A1149" s="9" t="n"/>
+      <c r="A1149" s="5" t="n"/>
     </row>
     <row r="1150">
-      <c r="A1150" s="9" t="n"/>
+      <c r="A1150" s="5" t="n"/>
     </row>
     <row r="1151">
-      <c r="A1151" s="9" t="n"/>
+      <c r="A1151" s="5" t="n"/>
     </row>
     <row r="1152">
-      <c r="A1152" s="9" t="n"/>
+      <c r="A1152" s="5" t="n"/>
     </row>
     <row r="1153">
-      <c r="A1153" s="9" t="n"/>
+      <c r="A1153" s="5" t="n"/>
     </row>
     <row r="1154">
-      <c r="A1154" s="9" t="n"/>
+      <c r="A1154" s="5" t="n"/>
     </row>
     <row r="1155">
-      <c r="A1155" s="9" t="n"/>
+      <c r="A1155" s="5" t="n"/>
     </row>
     <row r="1156">
-      <c r="A1156" s="9" t="n"/>
+      <c r="A1156" s="5" t="n"/>
     </row>
     <row r="1157">
-      <c r="A1157" s="9" t="n"/>
+      <c r="A1157" s="5" t="n"/>
     </row>
     <row r="1158">
-      <c r="A1158" s="9" t="n"/>
+      <c r="A1158" s="5" t="n"/>
     </row>
     <row r="1159">
-      <c r="A1159" s="9" t="n"/>
+      <c r="A1159" s="5" t="n"/>
     </row>
     <row r="1160">
-      <c r="A1160" s="9" t="n"/>
+      <c r="A1160" s="5" t="n"/>
     </row>
     <row r="1161">
-      <c r="A1161" s="9" t="n"/>
+      <c r="A1161" s="5" t="n"/>
     </row>
     <row r="1162">
-      <c r="A1162" s="9" t="n"/>
+      <c r="A1162" s="5" t="n"/>
     </row>
     <row r="1163">
-      <c r="A1163" s="9" t="n"/>
+      <c r="A1163" s="5" t="n"/>
     </row>
     <row r="1164">
-      <c r="A1164" s="9" t="n"/>
+      <c r="A1164" s="5" t="n"/>
     </row>
     <row r="1165">
-      <c r="A1165" s="9" t="n"/>
+      <c r="A1165" s="5" t="n"/>
     </row>
     <row r="1166">
-      <c r="A1166" s="9" t="n"/>
+      <c r="A1166" s="5" t="n"/>
     </row>
     <row r="1167">
-      <c r="A1167" s="9" t="n"/>
+      <c r="A1167" s="5" t="n"/>
     </row>
     <row r="1168">
-      <c r="A1168" s="9" t="n"/>
+      <c r="A1168" s="5" t="n"/>
     </row>
     <row r="1169">
-      <c r="A1169" s="9" t="n"/>
+      <c r="A1169" s="5" t="n"/>
     </row>
     <row r="1170">
-      <c r="A1170" s="9" t="n"/>
+      <c r="A1170" s="5" t="n"/>
     </row>
     <row r="1171">
-      <c r="A1171" s="9" t="n"/>
+      <c r="A1171" s="5" t="n"/>
     </row>
     <row r="1172">
-      <c r="A1172" s="9" t="n"/>
+      <c r="A1172" s="5" t="n"/>
     </row>
     <row r="1173">
-      <c r="A1173" s="9" t="n"/>
+      <c r="A1173" s="5" t="n"/>
     </row>
     <row r="1174">
-      <c r="A1174" s="9" t="n"/>
+      <c r="A1174" s="5" t="n"/>
     </row>
     <row r="1175">
-      <c r="A1175" s="9" t="n"/>
+      <c r="A1175" s="5" t="n"/>
     </row>
     <row r="1176">
-      <c r="A1176" s="9" t="n"/>
+      <c r="A1176" s="5" t="n"/>
     </row>
     <row r="1177">
-      <c r="A1177" s="9" t="n"/>
+      <c r="A1177" s="5" t="n"/>
     </row>
     <row r="1178">
-      <c r="A1178" s="9" t="n"/>
+      <c r="A1178" s="5" t="n"/>
     </row>
     <row r="1179">
-      <c r="A1179" s="9" t="n"/>
+      <c r="A1179" s="5" t="n"/>
     </row>
     <row r="1180">
-      <c r="A1180" s="9" t="n"/>
+      <c r="A1180" s="5" t="n"/>
     </row>
     <row r="1181">
-      <c r="A1181" s="9" t="n"/>
+      <c r="A1181" s="5" t="n"/>
     </row>
     <row r="1182">
-      <c r="A1182" s="9" t="n"/>
+      <c r="A1182" s="5" t="n"/>
     </row>
     <row r="1183">
-      <c r="A1183" s="9" t="n"/>
+      <c r="A1183" s="5" t="n"/>
     </row>
     <row r="1184">
-      <c r="A1184" s="9" t="n"/>
+      <c r="A1184" s="5" t="n"/>
     </row>
     <row r="1185">
-      <c r="A1185" s="9" t="n"/>
+      <c r="A1185" s="5" t="n"/>
     </row>
     <row r="1186">
-      <c r="A1186" s="9" t="n"/>
+      <c r="A1186" s="5" t="n"/>
     </row>
     <row r="1187">
-      <c r="A1187" s="9" t="n"/>
+      <c r="A1187" s="5" t="n"/>
     </row>
     <row r="1188">
-      <c r="A1188" s="9" t="n"/>
+      <c r="A1188" s="5" t="n"/>
     </row>
     <row r="1189">
-      <c r="A1189" s="9" t="n"/>
+      <c r="A1189" s="5" t="n"/>
     </row>
     <row r="1190">
-      <c r="A1190" s="9" t="n"/>
+      <c r="A1190" s="5" t="n"/>
     </row>
     <row r="1191">
-      <c r="A1191" s="9" t="n"/>
+      <c r="A1191" s="5" t="n"/>
     </row>
     <row r="1192">
-      <c r="A1192" s="9" t="n"/>
+      <c r="A1192" s="5" t="n"/>
     </row>
     <row r="1193">
-      <c r="A1193" s="9" t="n"/>
+      <c r="A1193" s="5" t="n"/>
     </row>
     <row r="1194">
-      <c r="A1194" s="9" t="n"/>
+      <c r="A1194" s="5" t="n"/>
     </row>
     <row r="1195">
-      <c r="A1195" s="9" t="n"/>
+      <c r="A1195" s="5" t="n"/>
     </row>
     <row r="1196">
-      <c r="A1196" s="9" t="n"/>
+      <c r="A1196" s="5" t="n"/>
     </row>
     <row r="1197">
-      <c r="A1197" s="9" t="n"/>
+      <c r="A1197" s="5" t="n"/>
     </row>
     <row r="1198">
-      <c r="A1198" s="9" t="n"/>
+      <c r="A1198" s="5" t="n"/>
     </row>
     <row r="1199">
-      <c r="A1199" s="9" t="n"/>
+      <c r="A1199" s="5" t="n"/>
     </row>
     <row r="1200">
-      <c r="A1200" s="9" t="n"/>
+      <c r="A1200" s="5" t="n"/>
     </row>
     <row r="1201">
-      <c r="A1201" s="9" t="n"/>
+      <c r="A1201" s="5" t="n"/>
     </row>
     <row r="1202">
-      <c r="A1202" s="9" t="n"/>
+      <c r="A1202" s="5" t="n"/>
     </row>
     <row r="1203">
-      <c r="A1203" s="9" t="n"/>
+      <c r="A1203" s="5" t="n"/>
     </row>
     <row r="1204">
-      <c r="A1204" s="9" t="n"/>
+      <c r="A1204" s="5" t="n"/>
     </row>
     <row r="1205">
-      <c r="A1205" s="9" t="n"/>
+      <c r="A1205" s="5" t="n"/>
     </row>
     <row r="1206">
-      <c r="A1206" s="9" t="n"/>
+      <c r="A1206" s="5" t="n"/>
     </row>
     <row r="1207">
-      <c r="A1207" s="9" t="n"/>
+      <c r="A1207" s="5" t="n"/>
     </row>
     <row r="1208">
-      <c r="A1208" s="9" t="n"/>
+      <c r="A1208" s="5" t="n"/>
     </row>
     <row r="1209">
-      <c r="A1209" s="9" t="n"/>
+      <c r="A1209" s="5" t="n"/>
     </row>
     <row r="1210">
-      <c r="A1210" s="9" t="n"/>
+      <c r="A1210" s="5" t="n"/>
     </row>
     <row r="1211">
-      <c r="A1211" s="9" t="n"/>
+      <c r="A1211" s="5" t="n"/>
     </row>
     <row r="1212">
-      <c r="A1212" s="9" t="n"/>
+      <c r="A1212" s="5" t="n"/>
     </row>
     <row r="1213">
-      <c r="A1213" s="9" t="n"/>
+      <c r="A1213" s="5" t="n"/>
     </row>
     <row r="1214">
-      <c r="A1214" s="9" t="n"/>
+      <c r="A1214" s="5" t="n"/>
     </row>
     <row r="1215">
-      <c r="A1215" s="9" t="n"/>
+      <c r="A1215" s="5" t="n"/>
     </row>
     <row r="1216">
-      <c r="A1216" s="9" t="n"/>
+      <c r="A1216" s="5" t="n"/>
     </row>
     <row r="1217">
-      <c r="A1217" s="9" t="n"/>
+      <c r="A1217" s="5" t="n"/>
     </row>
     <row r="1218">
-      <c r="A1218" s="9" t="n"/>
+      <c r="A1218" s="5" t="n"/>
     </row>
     <row r="1219">
-      <c r="A1219" s="9" t="n"/>
+      <c r="A1219" s="5" t="n"/>
     </row>
     <row r="1220">
-      <c r="A1220" s="9" t="n"/>
+      <c r="A1220" s="5" t="n"/>
     </row>
     <row r="1221">
-      <c r="A1221" s="9" t="n"/>
+      <c r="A1221" s="5" t="n"/>
     </row>
     <row r="1222">
-      <c r="A1222" s="9" t="n"/>
+      <c r="A1222" s="5" t="n"/>
     </row>
     <row r="1223">
-      <c r="A1223" s="9" t="n"/>
+      <c r="A1223" s="5" t="n"/>
     </row>
     <row r="1224">
-      <c r="A1224" s="9" t="n"/>
+      <c r="A1224" s="5" t="n"/>
     </row>
     <row r="1225">
-      <c r="A1225" s="9" t="n"/>
+      <c r="A1225" s="5" t="n"/>
     </row>
     <row r="1226">
-      <c r="A1226" s="9" t="n"/>
+      <c r="A1226" s="5" t="n"/>
     </row>
     <row r="1227">
-      <c r="A1227" s="9" t="n"/>
+      <c r="A1227" s="5" t="n"/>
     </row>
     <row r="1228">
-      <c r="A1228" s="9" t="n"/>
+      <c r="A1228" s="5" t="n"/>
     </row>
     <row r="1229">
-      <c r="A1229" s="9" t="n"/>
+      <c r="A1229" s="5" t="n"/>
     </row>
     <row r="1230">
-      <c r="A1230" s="9" t="n"/>
+      <c r="A1230" s="5" t="n"/>
     </row>
     <row r="1231">
-      <c r="A1231" s="9" t="n"/>
+      <c r="A1231" s="5" t="n"/>
     </row>
     <row r="1232">
-      <c r="A1232" s="9" t="n"/>
+      <c r="A1232" s="5" t="n"/>
     </row>
     <row r="1233">
-      <c r="A1233" s="9" t="n"/>
+      <c r="A1233" s="5" t="n"/>
     </row>
     <row r="1234">
-      <c r="A1234" s="9" t="n"/>
+      <c r="A1234" s="5" t="n"/>
     </row>
     <row r="1235">
-      <c r="A1235" s="9" t="n"/>
+      <c r="A1235" s="5" t="n"/>
     </row>
     <row r="1236">
-      <c r="A1236" s="9" t="n"/>
+      <c r="A1236" s="5" t="n"/>
     </row>
     <row r="1237">
-      <c r="A1237" s="9" t="n"/>
+      <c r="A1237" s="5" t="n"/>
     </row>
     <row r="1238">
-      <c r="A1238" s="9" t="n"/>
+      <c r="A1238" s="5" t="n"/>
     </row>
     <row r="1239">
-      <c r="A1239" s="9" t="n"/>
+      <c r="A1239" s="5" t="n"/>
     </row>
     <row r="1240">
-      <c r="A1240" s="9" t="n"/>
+      <c r="A1240" s="5" t="n"/>
     </row>
     <row r="1241">
-      <c r="A1241" s="9" t="n"/>
+      <c r="A1241" s="5" t="n"/>
     </row>
     <row r="1242">
-      <c r="A1242" s="9" t="n"/>
+      <c r="A1242" s="5" t="n"/>
     </row>
     <row r="1243">
-      <c r="A1243" s="9" t="n"/>
+      <c r="A1243" s="5" t="n"/>
     </row>
     <row r="1244">
-      <c r="A1244" s="9" t="n"/>
+      <c r="A1244" s="5" t="n"/>
     </row>
     <row r="1245">
-      <c r="A1245" s="9" t="n"/>
+      <c r="A1245" s="5" t="n"/>
     </row>
     <row r="1246">
-      <c r="A1246" s="9" t="n"/>
+      <c r="A1246" s="5" t="n"/>
     </row>
     <row r="1247">
-      <c r="A1247" s="9" t="n"/>
+      <c r="A1247" s="5" t="n"/>
     </row>
     <row r="1248">
-      <c r="A1248" s="9" t="n"/>
+      <c r="A1248" s="5" t="n"/>
     </row>
     <row r="1249">
-      <c r="A1249" s="9" t="n"/>
+      <c r="A1249" s="5" t="n"/>
     </row>
     <row r="1250">
-      <c r="A1250" s="9" t="n"/>
+      <c r="A1250" s="5" t="n"/>
     </row>
     <row r="1251">
-      <c r="A1251" s="9" t="n"/>
+      <c r="A1251" s="5" t="n"/>
     </row>
     <row r="1252">
-      <c r="A1252" s="9" t="n"/>
+      <c r="A1252" s="5" t="n"/>
     </row>
     <row r="1253">
-      <c r="A1253" s="9" t="n"/>
+      <c r="A1253" s="5" t="n"/>
     </row>
     <row r="1254">
-      <c r="A1254" s="9" t="n"/>
+      <c r="A1254" s="5" t="n"/>
     </row>
     <row r="1255">
-      <c r="A1255" s="9" t="n"/>
+      <c r="A1255" s="5" t="n"/>
     </row>
     <row r="1256">
-      <c r="A1256" s="9" t="n"/>
+      <c r="A1256" s="5" t="n"/>
     </row>
     <row r="1257">
-      <c r="A1257" s="9" t="n"/>
+      <c r="A1257" s="5" t="n"/>
     </row>
     <row r="1258">
-      <c r="A1258" s="9" t="n"/>
+      <c r="A1258" s="5" t="n"/>
     </row>
     <row r="1259">
-      <c r="A1259" s="9" t="n"/>
+      <c r="A1259" s="5" t="n"/>
     </row>
     <row r="1260">
-      <c r="A1260" s="9" t="n"/>
+      <c r="A1260" s="5" t="n"/>
     </row>
     <row r="1261">
-      <c r="A1261" s="9" t="n"/>
+      <c r="A1261" s="5" t="n"/>
     </row>
     <row r="1262">
-      <c r="A1262" s="9" t="n"/>
+      <c r="A1262" s="5" t="n"/>
     </row>
     <row r="1263">
-      <c r="A1263" s="9" t="n"/>
+      <c r="A1263" s="5" t="n"/>
     </row>
     <row r="1264">
-      <c r="A1264" s="9" t="n"/>
+      <c r="A1264" s="5" t="n"/>
     </row>
     <row r="1265">
-      <c r="A1265" s="9" t="n"/>
+      <c r="A1265" s="5" t="n"/>
     </row>
     <row r="1266">
-      <c r="A1266" s="9" t="n"/>
+      <c r="A1266" s="5" t="n"/>
     </row>
     <row r="1267">
-      <c r="A1267" s="9" t="n"/>
+      <c r="A1267" s="5" t="n"/>
     </row>
     <row r="1268">
-      <c r="A1268" s="9" t="n"/>
+      <c r="A1268" s="5" t="n"/>
     </row>
     <row r="1269">
-      <c r="A1269" s="9" t="n"/>
+      <c r="A1269" s="5" t="n"/>
     </row>
     <row r="1270">
-      <c r="A1270" s="9" t="n"/>
+      <c r="A1270" s="5" t="n"/>
     </row>
     <row r="1271">
-      <c r="A1271" s="9" t="n"/>
+      <c r="A1271" s="5" t="n"/>
     </row>
     <row r="1272">
-      <c r="A1272" s="9" t="n"/>
+      <c r="A1272" s="5" t="n"/>
     </row>
     <row r="1273">
-      <c r="A1273" s="9" t="n"/>
+      <c r="A1273" s="5" t="n"/>
     </row>
     <row r="1274">
-      <c r="A1274" s="9" t="n"/>
+      <c r="A1274" s="5" t="n"/>
     </row>
     <row r="1275">
-      <c r="A1275" s="9" t="n"/>
+      <c r="A1275" s="5" t="n"/>
     </row>
     <row r="1276">
-      <c r="A1276" s="9" t="n"/>
+      <c r="A1276" s="5" t="n"/>
     </row>
     <row r="1277">
-      <c r="A1277" s="9" t="n"/>
+      <c r="A1277" s="5" t="n"/>
     </row>
     <row r="1278">
-      <c r="A1278" s="9" t="n"/>
+      <c r="A1278" s="5" t="n"/>
     </row>
     <row r="1279">
-      <c r="A1279" s="9" t="n"/>
+      <c r="A1279" s="5" t="n"/>
     </row>
     <row r="1280">
-      <c r="A1280" s="9" t="n"/>
+      <c r="A1280" s="5" t="n"/>
     </row>
     <row r="1281">
-      <c r="A1281" s="9" t="n"/>
+      <c r="A1281" s="5" t="n"/>
     </row>
     <row r="1282">
-      <c r="A1282" s="9" t="n"/>
+      <c r="A1282" s="5" t="n"/>
     </row>
     <row r="1283">
-      <c r="A1283" s="9" t="n"/>
+      <c r="A1283" s="5" t="n"/>
     </row>
     <row r="1284">
-      <c r="A1284" s="9" t="n"/>
+      <c r="A1284" s="5" t="n"/>
     </row>
     <row r="1285">
-      <c r="A1285" s="9" t="n"/>
+      <c r="A1285" s="5" t="n"/>
     </row>
     <row r="1286">
-      <c r="A1286" s="9" t="n"/>
+      <c r="A1286" s="5" t="n"/>
     </row>
     <row r="1287">
-      <c r="A1287" s="9" t="n"/>
+      <c r="A1287" s="5" t="n"/>
     </row>
     <row r="1288">
-      <c r="A1288" s="9" t="n"/>
+      <c r="A1288" s="5" t="n"/>
     </row>
     <row r="1289">
-      <c r="A1289" s="9" t="n"/>
+      <c r="A1289" s="5" t="n"/>
     </row>
     <row r="1290">
-      <c r="A1290" s="9" t="n"/>
+      <c r="A1290" s="5" t="n"/>
     </row>
     <row r="1291">
-      <c r="A1291" s="9" t="n"/>
+      <c r="A1291" s="5" t="n"/>
     </row>
     <row r="1292">
-      <c r="A1292" s="9" t="n"/>
+      <c r="A1292" s="5" t="n"/>
     </row>
     <row r="1293">
-      <c r="A1293" s="9" t="n"/>
+      <c r="A1293" s="5" t="n"/>
     </row>
     <row r="1294">
-      <c r="A1294" s="9" t="n"/>
+      <c r="A1294" s="5" t="n"/>
     </row>
     <row r="1295">
-      <c r="A1295" s="9" t="n"/>
+      <c r="A1295" s="5" t="n"/>
     </row>
     <row r="1296">
-      <c r="A1296" s="9" t="n"/>
+      <c r="A1296" s="5" t="n"/>
     </row>
     <row r="1297">
-      <c r="A1297" s="9" t="n"/>
+      <c r="A1297" s="5" t="n"/>
     </row>
     <row r="1298">
-      <c r="A1298" s="9" t="n"/>
+      <c r="A1298" s="5" t="n"/>
     </row>
     <row r="1299">
-      <c r="A1299" s="9" t="n"/>
+      <c r="A1299" s="5" t="n"/>
     </row>
     <row r="1300">
-      <c r="A1300" s="9" t="n"/>
+      <c r="A1300" s="5" t="n"/>
     </row>
     <row r="1301">
-      <c r="A1301" s="9" t="n"/>
+      <c r="A1301" s="5" t="n"/>
     </row>
     <row r="1302">
-      <c r="A1302" s="9" t="n"/>
+      <c r="A1302" s="5" t="n"/>
     </row>
     <row r="1303">
-      <c r="A1303" s="9" t="n"/>
+      <c r="A1303" s="5" t="n"/>
     </row>
     <row r="1304">
-      <c r="A1304" s="9" t="n"/>
+      <c r="A1304" s="5" t="n"/>
     </row>
     <row r="1305">
-      <c r="A1305" s="9" t="n"/>
+      <c r="A1305" s="5" t="n"/>
     </row>
     <row r="1306">
-      <c r="A1306" s="9" t="n"/>
+      <c r="A1306" s="5" t="n"/>
     </row>
     <row r="1307">
-      <c r="A1307" s="9" t="n"/>
+      <c r="A1307" s="5" t="n"/>
     </row>
     <row r="1308">
-      <c r="A1308" s="9" t="n"/>
+      <c r="A1308" s="5" t="n"/>
     </row>
     <row r="1309">
-      <c r="A1309" s="9" t="n"/>
+      <c r="A1309" s="5" t="n"/>
     </row>
     <row r="1310">
-      <c r="A1310" s="9" t="n"/>
+      <c r="A1310" s="5" t="n"/>
     </row>
     <row r="1311">
-      <c r="A1311" s="9" t="n"/>
+      <c r="A1311" s="5" t="n"/>
     </row>
     <row r="1312">
-      <c r="A1312" s="9" t="n"/>
+      <c r="A1312" s="5" t="n"/>
     </row>
     <row r="1313">
-      <c r="A1313" s="9" t="n"/>
+      <c r="A1313" s="5" t="n"/>
     </row>
     <row r="1314">
-      <c r="A1314" s="9" t="n"/>
+      <c r="A1314" s="5" t="n"/>
     </row>
     <row r="1315">
-      <c r="A1315" s="9" t="n"/>
+      <c r="A1315" s="5" t="n"/>
     </row>
     <row r="1316">
-      <c r="A1316" s="9" t="n"/>
+      <c r="A1316" s="5" t="n"/>
     </row>
     <row r="1317">
-      <c r="A1317" s="9" t="n"/>
+      <c r="A1317" s="5" t="n"/>
     </row>
     <row r="1318">
-      <c r="A1318" s="9" t="n"/>
+      <c r="A1318" s="5" t="n"/>
     </row>
     <row r="1319">
-      <c r="A1319" s="9" t="n"/>
+      <c r="A1319" s="5" t="n"/>
     </row>
     <row r="1320">
-      <c r="A1320" s="9" t="n"/>
+      <c r="A1320" s="5" t="n"/>
     </row>
     <row r="1321">
-      <c r="A1321" s="9" t="n"/>
+      <c r="A1321" s="5" t="n"/>
     </row>
     <row r="1322">
-      <c r="A1322" s="9" t="n"/>
+      <c r="A1322" s="5" t="n"/>
     </row>
     <row r="1323">
-      <c r="A1323" s="9" t="n"/>
+      <c r="A1323" s="5" t="n"/>
     </row>
     <row r="1324">
-      <c r="A1324" s="9" t="n"/>
+      <c r="A1324" s="5" t="n"/>
     </row>
     <row r="1325">
-      <c r="A1325" s="9" t="n"/>
+      <c r="A1325" s="5" t="n"/>
     </row>
     <row r="1326">
-      <c r="A1326" s="9" t="n"/>
+      <c r="A1326" s="5" t="n"/>
     </row>
     <row r="1327">
-      <c r="A1327" s="9" t="n"/>
+      <c r="A1327" s="5" t="n"/>
     </row>
     <row r="1328">
-      <c r="A1328" s="9" t="n"/>
+      <c r="A1328" s="5" t="n"/>
     </row>
     <row r="1329">
-      <c r="A1329" s="9" t="n"/>
+      <c r="A1329" s="5" t="n"/>
     </row>
     <row r="1330">
-      <c r="A1330" s="9" t="n"/>
+      <c r="A1330" s="5" t="n"/>
     </row>
     <row r="1331">
-      <c r="A1331" s="9" t="n"/>
+      <c r="A1331" s="5" t="n"/>
     </row>
     <row r="1332">
-      <c r="A1332" s="9" t="n"/>
+      <c r="A1332" s="5" t="n"/>
     </row>
     <row r="1333">
-      <c r="A1333" s="9" t="n"/>
+      <c r="A1333" s="5" t="n"/>
     </row>
     <row r="1334">
-      <c r="A1334" s="9" t="n"/>
+      <c r="A1334" s="5" t="n"/>
     </row>
     <row r="1335">
-      <c r="A1335" s="9" t="n"/>
+      <c r="A1335" s="5" t="n"/>
     </row>
     <row r="1336">
-      <c r="A1336" s="9" t="n"/>
+      <c r="A1336" s="5" t="n"/>
     </row>
     <row r="1337">
-      <c r="A1337" s="9" t="n"/>
+      <c r="A1337" s="5" t="n"/>
     </row>
     <row r="1338">
-      <c r="A1338" s="9" t="n"/>
+      <c r="A1338" s="5" t="n"/>
     </row>
     <row r="1339">
-      <c r="A1339" s="9" t="n"/>
+      <c r="A1339" s="5" t="n"/>
     </row>
     <row r="1340">
-      <c r="A1340" s="9" t="n"/>
+      <c r="A1340" s="5" t="n"/>
     </row>
     <row r="1341">
-      <c r="A1341" s="9" t="n"/>
+      <c r="A1341" s="5" t="n"/>
     </row>
     <row r="1342">
-      <c r="A1342" s="9" t="n"/>
+      <c r="A1342" s="5" t="n"/>
     </row>
     <row r="1343">
-      <c r="A1343" s="9" t="n"/>
+      <c r="A1343" s="5" t="n"/>
     </row>
     <row r="1344">
-      <c r="A1344" s="9" t="n"/>
+      <c r="A1344" s="5" t="n"/>
     </row>
     <row r="1345">
-      <c r="A1345" s="9" t="n"/>
+      <c r="A1345" s="5" t="n"/>
     </row>
     <row r="1346">
-      <c r="A1346" s="9" t="n"/>
+      <c r="A1346" s="5" t="n"/>
     </row>
     <row r="1347">
-      <c r="A1347" s="9" t="n"/>
+      <c r="A1347" s="5" t="n"/>
     </row>
     <row r="1348">
-      <c r="A1348" s="9" t="n"/>
+      <c r="A1348" s="5" t="n"/>
     </row>
     <row r="1349">
-      <c r="A1349" s="9" t="n"/>
+      <c r="A1349" s="5" t="n"/>
     </row>
     <row r="1350">
-      <c r="A1350" s="9" t="n"/>
+      <c r="A1350" s="5" t="n"/>
     </row>
     <row r="1351">
-      <c r="A1351" s="9" t="n"/>
+      <c r="A1351" s="5" t="n"/>
     </row>
     <row r="1352">
-      <c r="A1352" s="9" t="n"/>
+      <c r="A1352" s="5" t="n"/>
     </row>
     <row r="1353">
-      <c r="A1353" s="9" t="n"/>
+      <c r="A1353" s="5" t="n"/>
     </row>
     <row r="1354">
-      <c r="A1354" s="9" t="n"/>
+      <c r="A1354" s="5" t="n"/>
     </row>
     <row r="1355">
-      <c r="A1355" s="9" t="n"/>
+      <c r="A1355" s="5" t="n"/>
     </row>
     <row r="1356">
-      <c r="A1356" s="9" t="n"/>
+      <c r="A1356" s="5" t="n"/>
     </row>
     <row r="1357">
-      <c r="A1357" s="9" t="n"/>
+      <c r="A1357" s="5" t="n"/>
     </row>
     <row r="1358">
-      <c r="A1358" s="9" t="n"/>
+      <c r="A1358" s="5" t="n"/>
     </row>
     <row r="1359">
-      <c r="A1359" s="9" t="n"/>
+      <c r="A1359" s="5" t="n"/>
     </row>
     <row r="1360">
-      <c r="A1360" s="9" t="n"/>
+      <c r="A1360" s="5" t="n"/>
     </row>
     <row r="1361">
-      <c r="A1361" s="9" t="n"/>
+      <c r="A1361" s="5" t="n"/>
     </row>
     <row r="1362">
-      <c r="A1362" s="9" t="n"/>
+      <c r="A1362" s="5" t="n"/>
     </row>
     <row r="1363">
-      <c r="A1363" s="9" t="n"/>
+      <c r="A1363" s="5" t="n"/>
     </row>
     <row r="1364">
-      <c r="A1364" s="9" t="n"/>
+      <c r="A1364" s="5" t="n"/>
     </row>
     <row r="1365">
-      <c r="A1365" s="9" t="n"/>
+      <c r="A1365" s="5" t="n"/>
     </row>
     <row r="1366">
-      <c r="A1366" s="9" t="n"/>
+      <c r="A1366" s="5" t="n"/>
     </row>
     <row r="1367">
-      <c r="A1367" s="9" t="n"/>
+      <c r="A1367" s="5" t="n"/>
     </row>
     <row r="1368">
-      <c r="A1368" s="9" t="n"/>
+      <c r="A1368" s="5" t="n"/>
     </row>
     <row r="1369">
-      <c r="A1369" s="9" t="n"/>
+      <c r="A1369" s="5" t="n"/>
     </row>
     <row r="1370">
-      <c r="A1370" s="9" t="n"/>
+      <c r="A1370" s="5" t="n"/>
     </row>
     <row r="1371">
-      <c r="A1371" s="9" t="n"/>
+      <c r="A1371" s="5" t="n"/>
     </row>
     <row r="1372">
-      <c r="A1372" s="9" t="n"/>
+      <c r="A1372" s="5" t="n"/>
     </row>
     <row r="1373">
-      <c r="A1373" s="9" t="n"/>
+      <c r="A1373" s="5" t="n"/>
     </row>
     <row r="1374">
-      <c r="A1374" s="9" t="n"/>
+      <c r="A1374" s="5" t="n"/>
     </row>
     <row r="1375">
-      <c r="A1375" s="9" t="n"/>
+      <c r="A1375" s="5" t="n"/>
     </row>
     <row r="1376">
-      <c r="A1376" s="9" t="n"/>
+      <c r="A1376" s="5" t="n"/>
     </row>
     <row r="1377">
-      <c r="A1377" s="9" t="n"/>
+      <c r="A1377" s="5" t="n"/>
     </row>
     <row r="1378">
-      <c r="A1378" s="9" t="n"/>
+      <c r="A1378" s="5" t="n"/>
     </row>
     <row r="1379">
-      <c r="A1379" s="9" t="n"/>
+      <c r="A1379" s="5" t="n"/>
     </row>
     <row r="1380">
-      <c r="A1380" s="9" t="n"/>
+      <c r="A1380" s="5" t="n"/>
     </row>
     <row r="1381">
-      <c r="A1381" s="9" t="n"/>
+      <c r="A1381" s="5" t="n"/>
     </row>
     <row r="1382">
-      <c r="A1382" s="9" t="n"/>
+      <c r="A1382" s="5" t="n"/>
     </row>
     <row r="1383">
-      <c r="A1383" s="9" t="n"/>
+      <c r="A1383" s="5" t="n"/>
     </row>
     <row r="1384">
-      <c r="A1384" s="9" t="n"/>
+      <c r="A1384" s="5" t="n"/>
     </row>
     <row r="1385">
-      <c r="A1385" s="9" t="n"/>
+      <c r="A1385" s="5" t="n"/>
     </row>
     <row r="1386">
-      <c r="A1386" s="9" t="n"/>
+      <c r="A1386" s="5" t="n"/>
     </row>
     <row r="1387">
-      <c r="A1387" s="9" t="n"/>
+      <c r="A1387" s="5" t="n"/>
     </row>
     <row r="1388">
-      <c r="A1388" s="9" t="n"/>
+      <c r="A1388" s="5" t="n"/>
     </row>
     <row r="1389">
-      <c r="A1389" s="9" t="n"/>
+      <c r="A1389" s="5" t="n"/>
     </row>
     <row r="1390">
-      <c r="A1390" s="9" t="n"/>
+      <c r="A1390" s="5" t="n"/>
     </row>
     <row r="1391">
-      <c r="A1391" s="9" t="n"/>
+      <c r="A1391" s="5" t="n"/>
     </row>
     <row r="1392">
-      <c r="A1392" s="9" t="n"/>
+      <c r="A1392" s="5" t="n"/>
     </row>
     <row r="1393">
-      <c r="A1393" s="9" t="n"/>
+      <c r="A1393" s="5" t="n"/>
     </row>
     <row r="1394">
-      <c r="A1394" s="9" t="n"/>
+      <c r="A1394" s="5" t="n"/>
     </row>
     <row r="1395">
-      <c r="A1395" s="9" t="n"/>
+      <c r="A1395" s="5" t="n"/>
     </row>
     <row r="1396">
-      <c r="A1396" s="9" t="n"/>
+      <c r="A1396" s="5" t="n"/>
     </row>
     <row r="1397">
-      <c r="A1397" s="9" t="n"/>
+      <c r="A1397" s="5" t="n"/>
     </row>
     <row r="1398">
-      <c r="A1398" s="9" t="n"/>
+      <c r="A1398" s="5" t="n"/>
     </row>
     <row r="1399">
-      <c r="A1399" s="9" t="n"/>
+      <c r="A1399" s="5" t="n"/>
     </row>
     <row r="1400">
-      <c r="A1400" s="9" t="n"/>
+      <c r="A1400" s="5" t="n"/>
     </row>
     <row r="1401">
-      <c r="A1401" s="9" t="n"/>
+      <c r="A1401" s="5" t="n"/>
     </row>
     <row r="1402">
-      <c r="A1402" s="9" t="n"/>
+      <c r="A1402" s="5" t="n"/>
     </row>
     <row r="1403">
-      <c r="A1403" s="9" t="n"/>
+      <c r="A1403" s="5" t="n"/>
     </row>
     <row r="1404">
-      <c r="A1404" s="9" t="n"/>
+      <c r="A1404" s="5" t="n"/>
     </row>
     <row r="1405">
-      <c r="A1405" s="9" t="n"/>
+      <c r="A1405" s="5" t="n"/>
     </row>
     <row r="1406">
-      <c r="A1406" s="9" t="n"/>
+      <c r="A1406" s="5" t="n"/>
     </row>
     <row r="1407">
-      <c r="A1407" s="9" t="n"/>
+      <c r="A1407" s="5" t="n"/>
     </row>
     <row r="1408">
-      <c r="A1408" s="9" t="n"/>
+      <c r="A1408" s="5" t="n"/>
     </row>
     <row r="1409">
-      <c r="A1409" s="9" t="n"/>
+      <c r="A1409" s="5" t="n"/>
     </row>
     <row r="1410">
-      <c r="A1410" s="9" t="n"/>
+      <c r="A1410" s="5" t="n"/>
     </row>
     <row r="1411">
-      <c r="A1411" s="9" t="n"/>
+      <c r="A1411" s="5" t="n"/>
     </row>
     <row r="1412">
-      <c r="A1412" s="9" t="n"/>
+      <c r="A1412" s="5" t="n"/>
     </row>
     <row r="1413">
-      <c r="A1413" s="9" t="n"/>
+      <c r="A1413" s="5" t="n"/>
     </row>
     <row r="1414">
-      <c r="A1414" s="9" t="n"/>
+      <c r="A1414" s="5" t="n"/>
     </row>
     <row r="1415">
-      <c r="A1415" s="9" t="n"/>
+      <c r="A1415" s="5" t="n"/>
     </row>
     <row r="1416">
-      <c r="A1416" s="9" t="n"/>
+      <c r="A1416" s="5" t="n"/>
     </row>
     <row r="1417">
-      <c r="A1417" s="9" t="n"/>
+      <c r="A1417" s="5" t="n"/>
     </row>
     <row r="1418">
-      <c r="A1418" s="9" t="n"/>
+      <c r="A1418" s="5" t="n"/>
     </row>
     <row r="1419">
-      <c r="A1419" s="9" t="n"/>
+      <c r="A1419" s="5" t="n"/>
     </row>
     <row r="1420">
-      <c r="A1420" s="9" t="n"/>
+      <c r="A1420" s="5" t="n"/>
     </row>
     <row r="1421">
-      <c r="A1421" s="9" t="n"/>
+      <c r="A1421" s="5" t="n"/>
     </row>
     <row r="1422">
-      <c r="A1422" s="9" t="n"/>
+      <c r="A1422" s="5" t="n"/>
     </row>
     <row r="1423">
-      <c r="A1423" s="9" t="n"/>
+      <c r="A1423" s="5" t="n"/>
     </row>
     <row r="1424">
-      <c r="A1424" s="9" t="n"/>
+      <c r="A1424" s="5" t="n"/>
     </row>
     <row r="1425">
-      <c r="A1425" s="9" t="n"/>
+      <c r="A1425" s="5" t="n"/>
     </row>
     <row r="1426">
-      <c r="A1426" s="9" t="n"/>
+      <c r="A1426" s="5" t="n"/>
     </row>
     <row r="1427">
-      <c r="A1427" s="9" t="n"/>
+      <c r="A1427" s="5" t="n"/>
     </row>
     <row r="1428">
-      <c r="A1428" s="9" t="n"/>
+      <c r="A1428" s="5" t="n"/>
     </row>
     <row r="1429">
-      <c r="A1429" s="9" t="n"/>
+      <c r="A1429" s="5" t="n"/>
     </row>
     <row r="1430">
-      <c r="A1430" s="9" t="n"/>
+      <c r="A1430" s="5" t="n"/>
     </row>
     <row r="1431">
-      <c r="A1431" s="9" t="n"/>
+      <c r="A1431" s="5" t="n"/>
     </row>
     <row r="1432">
-      <c r="A1432" s="9" t="n"/>
+      <c r="A1432" s="5" t="n"/>
     </row>
     <row r="1433">
-      <c r="A1433" s="9" t="n"/>
+      <c r="A1433" s="5" t="n"/>
     </row>
     <row r="1434">
-      <c r="A1434" s="9" t="n"/>
+      <c r="A1434" s="5" t="n"/>
     </row>
     <row r="1435">
-      <c r="A1435" s="9" t="n"/>
+      <c r="A1435" s="5" t="n"/>
     </row>
     <row r="1436">
-      <c r="A1436" s="9" t="n"/>
+      <c r="A1436" s="5" t="n"/>
     </row>
     <row r="1437">
-      <c r="A1437" s="9" t="n"/>
+      <c r="A1437" s="5" t="n"/>
     </row>
     <row r="1438">
-      <c r="A1438" s="9" t="n"/>
+      <c r="A1438" s="5" t="n"/>
     </row>
     <row r="1439">
-      <c r="A1439" s="9" t="n"/>
+      <c r="A1439" s="5" t="n"/>
     </row>
     <row r="1440">
-      <c r="A1440" s="9" t="n"/>
+      <c r="A1440" s="5" t="n"/>
     </row>
     <row r="1441">
-      <c r="A1441" s="9" t="n"/>
+      <c r="A1441" s="5" t="n"/>
     </row>
     <row r="1442">
-      <c r="A1442" s="9" t="n"/>
+      <c r="A1442" s="5" t="n"/>
     </row>
     <row r="1443">
-      <c r="A1443" s="9" t="n"/>
+      <c r="A1443" s="5" t="n"/>
     </row>
     <row r="1444">
-      <c r="A1444" s="9" t="n"/>
+      <c r="A1444" s="5" t="n"/>
     </row>
     <row r="1445">
-      <c r="A1445" s="9" t="n"/>
+      <c r="A1445" s="5" t="n"/>
     </row>
     <row r="1446">
-      <c r="A1446" s="9" t="n"/>
+      <c r="A1446" s="5" t="n"/>
     </row>
     <row r="1447">
-      <c r="A1447" s="9" t="n"/>
+      <c r="A1447" s="5" t="n"/>
     </row>
     <row r="1448">
-      <c r="A1448" s="9" t="n"/>
+      <c r="A1448" s="5" t="n"/>
     </row>
     <row r="1449">
-      <c r="A1449" s="9" t="n"/>
+      <c r="A1449" s="5" t="n"/>
     </row>
     <row r="1450">
-      <c r="A1450" s="9" t="n"/>
+      <c r="A1450" s="5" t="n"/>
     </row>
     <row r="1451">
-      <c r="A1451" s="9" t="n"/>
+      <c r="A1451" s="5" t="n"/>
     </row>
     <row r="1452">
-      <c r="A1452" s="9" t="n"/>
+      <c r="A1452" s="5" t="n"/>
     </row>
     <row r="1453">
-      <c r="A1453" s="9" t="n"/>
+      <c r="A1453" s="5" t="n"/>
     </row>
     <row r="1454">
-      <c r="A1454" s="9" t="n"/>
+      <c r="A1454" s="5" t="n"/>
     </row>
     <row r="1455">
-      <c r="A1455" s="9" t="n"/>
+      <c r="A1455" s="5" t="n"/>
     </row>
     <row r="1456">
-      <c r="A1456" s="9" t="n"/>
+      <c r="A1456" s="5" t="n"/>
     </row>
     <row r="1457">
-      <c r="A1457" s="9" t="n"/>
+      <c r="A1457" s="5" t="n"/>
     </row>
     <row r="1458">
-      <c r="A1458" s="9" t="n"/>
+      <c r="A1458" s="5" t="n"/>
     </row>
     <row r="1459">
-      <c r="A1459" s="9" t="n"/>
+      <c r="A1459" s="5" t="n"/>
     </row>
     <row r="1460">
-      <c r="A1460" s="9" t="n"/>
+      <c r="A1460" s="5" t="n"/>
     </row>
     <row r="1461">
-      <c r="A1461" s="9" t="n"/>
+      <c r="A1461" s="5" t="n"/>
     </row>
     <row r="1462">
-      <c r="A1462" s="9" t="n"/>
+      <c r="A1462" s="5" t="n"/>
     </row>
     <row r="1463">
-      <c r="A1463" s="9" t="n"/>
+      <c r="A1463" s="5" t="n"/>
     </row>
     <row r="1464">
-      <c r="A1464" s="9" t="n"/>
+      <c r="A1464" s="5" t="n"/>
     </row>
     <row r="1465">
-      <c r="A1465" s="9" t="n"/>
+      <c r="A1465" s="5" t="n"/>
     </row>
     <row r="1466">
-      <c r="A1466" s="9" t="n"/>
+      <c r="A1466" s="5" t="n"/>
     </row>
     <row r="1467">
-      <c r="A1467" s="9" t="n"/>
+      <c r="A1467" s="5" t="n"/>
     </row>
     <row r="1468">
-      <c r="A1468" s="9" t="n"/>
+      <c r="A1468" s="5" t="n"/>
     </row>
     <row r="1469">
-      <c r="A1469" s="9" t="n"/>
+      <c r="A1469" s="5" t="n"/>
     </row>
     <row r="1470">
-      <c r="A1470" s="9" t="n"/>
+      <c r="A1470" s="5" t="n"/>
     </row>
     <row r="1471">
-      <c r="A1471" s="9" t="n"/>
+      <c r="A1471" s="5" t="n"/>
     </row>
     <row r="1472">
-      <c r="A1472" s="9" t="n"/>
+      <c r="A1472" s="5" t="n"/>
     </row>
     <row r="1473">
-      <c r="A1473" s="9" t="n"/>
+      <c r="A1473" s="5" t="n"/>
     </row>
     <row r="1474">
-      <c r="A1474" s="9" t="n"/>
+      <c r="A1474" s="5" t="n"/>
     </row>
     <row r="1475">
-      <c r="A1475" s="9" t="n"/>
+      <c r="A1475" s="5" t="n"/>
     </row>
     <row r="1476">
-      <c r="A1476" s="9" t="n"/>
+      <c r="A1476" s="5" t="n"/>
     </row>
     <row r="1477">
-      <c r="A1477" s="9" t="n"/>
+      <c r="A1477" s="5" t="n"/>
     </row>
     <row r="1478">
-      <c r="A1478" s="9" t="n"/>
+      <c r="A1478" s="5" t="n"/>
     </row>
     <row r="1479">
-      <c r="A1479" s="9" t="n"/>
+      <c r="A1479" s="5" t="n"/>
     </row>
     <row r="1480">
-      <c r="A1480" s="9" t="n"/>
+      <c r="A1480" s="5" t="n"/>
     </row>
     <row r="1481">
-      <c r="A1481" s="9" t="n"/>
+      <c r="A1481" s="5" t="n"/>
     </row>
     <row r="1482">
-      <c r="A1482" s="9" t="n"/>
+      <c r="A1482" s="5" t="n"/>
     </row>
     <row r="1483">
-      <c r="A1483" s="9" t="n"/>
+      <c r="A1483" s="5" t="n"/>
     </row>
     <row r="1484">
-      <c r="A1484" s="9" t="n"/>
+      <c r="A1484" s="5" t="n"/>
     </row>
     <row r="1485">
-      <c r="A1485" s="9" t="n"/>
+      <c r="A1485" s="5" t="n"/>
     </row>
     <row r="1486">
-      <c r="A1486" s="9" t="n"/>
+      <c r="A1486" s="5" t="n"/>
     </row>
     <row r="1487">
-      <c r="A1487" s="9" t="n"/>
+      <c r="A1487" s="5" t="n"/>
     </row>
     <row r="1488">
-      <c r="A1488" s="9" t="n"/>
+      <c r="A1488" s="5" t="n"/>
     </row>
     <row r="1489">
-      <c r="A1489" s="9" t="n"/>
+      <c r="A1489" s="5" t="n"/>
     </row>
     <row r="1490">
-      <c r="A1490" s="9" t="n"/>
+      <c r="A1490" s="5" t="n"/>
     </row>
     <row r="1491">
-      <c r="A1491" s="9" t="n"/>
+      <c r="A1491" s="5" t="n"/>
     </row>
     <row r="1492">
-      <c r="A1492" s="9" t="n"/>
+      <c r="A1492" s="5" t="n"/>
     </row>
     <row r="1493">
-      <c r="A1493" s="9" t="n"/>
+      <c r="A1493" s="5" t="n"/>
     </row>
     <row r="1494">
-      <c r="A1494" s="9" t="n"/>
+      <c r="A1494" s="5" t="n"/>
     </row>
     <row r="1495">
-      <c r="A1495" s="9" t="n"/>
+      <c r="A1495" s="5" t="n"/>
     </row>
     <row r="1496">
-      <c r="A1496" s="9" t="n"/>
+      <c r="A1496" s="5" t="n"/>
     </row>
     <row r="1497">
-      <c r="A1497" s="9" t="n"/>
+      <c r="A1497" s="5" t="n"/>
     </row>
     <row r="1498">
-      <c r="A1498" s="9" t="n"/>
+      <c r="A1498" s="5" t="n"/>
     </row>
     <row r="1499">
-      <c r="A1499" s="9" t="n"/>
+      <c r="A1499" s="5" t="n"/>
     </row>
     <row r="1500">
-      <c r="A1500" s="9" t="n"/>
+      <c r="A1500" s="5" t="n"/>
     </row>
     <row r="1501">
-      <c r="A1501" s="9" t="n"/>
+      <c r="A1501" s="5" t="n"/>
     </row>
     <row r="1502">
-      <c r="A1502" s="9" t="n"/>
+      <c r="A1502" s="5" t="n"/>
     </row>
     <row r="1503">
-      <c r="A1503" s="9" t="n"/>
+      <c r="A1503" s="5" t="n"/>
     </row>
     <row r="1504">
-      <c r="A1504" s="9" t="n"/>
+      <c r="A1504" s="5" t="n"/>
     </row>
     <row r="1505">
-      <c r="A1505" s="9" t="n"/>
+      <c r="A1505" s="5" t="n"/>
     </row>
     <row r="1506">
-      <c r="A1506" s="9" t="n"/>
+      <c r="A1506" s="5" t="n"/>
     </row>
     <row r="1507">
-      <c r="A1507" s="9" t="n"/>
+      <c r="A1507" s="5" t="n"/>
     </row>
     <row r="1508">
-      <c r="A1508" s="9" t="n"/>
+      <c r="A1508" s="5" t="n"/>
     </row>
     <row r="1509">
-      <c r="A1509" s="9" t="n"/>
+      <c r="A1509" s="5" t="n"/>
     </row>
     <row r="1510">
-      <c r="A1510" s="9" t="n"/>
+      <c r="A1510" s="5" t="n"/>
     </row>
     <row r="1511">
-      <c r="A1511" s="9" t="n"/>
+      <c r="A1511" s="5" t="n"/>
     </row>
     <row r="1512">
-      <c r="A1512" s="9" t="n"/>
+      <c r="A1512" s="5" t="n"/>
     </row>
     <row r="1513">
-      <c r="A1513" s="9" t="n"/>
+      <c r="A1513" s="5" t="n"/>
     </row>
     <row r="1514">
-      <c r="A1514" s="9" t="n"/>
+      <c r="A1514" s="5" t="n"/>
     </row>
     <row r="1515">
-      <c r="A1515" s="9" t="n"/>
+      <c r="A1515" s="5" t="n"/>
     </row>
     <row r="1516">
-      <c r="A1516" s="9" t="n"/>
+      <c r="A1516" s="5" t="n"/>
     </row>
     <row r="1517">
-      <c r="A1517" s="9" t="n"/>
+      <c r="A1517" s="5" t="n"/>
     </row>
     <row r="1518">
-      <c r="A1518" s="9" t="n"/>
+      <c r="A1518" s="5" t="n"/>
     </row>
     <row r="1519">
-      <c r="A1519" s="9" t="n"/>
+      <c r="A1519" s="5" t="n"/>
     </row>
     <row r="1520">
-      <c r="A1520" s="9" t="n"/>
+      <c r="A1520" s="5" t="n"/>
     </row>
     <row r="1521">
-      <c r="A1521" s="9" t="n"/>
+      <c r="A1521" s="5" t="n"/>
     </row>
     <row r="1522">
-      <c r="A1522" s="9" t="n"/>
+      <c r="A1522" s="5" t="n"/>
     </row>
     <row r="1523">
-      <c r="A1523" s="9" t="n"/>
+      <c r="A1523" s="5" t="n"/>
     </row>
     <row r="1524">
-      <c r="A1524" s="9" t="n"/>
+      <c r="A1524" s="5" t="n"/>
     </row>
     <row r="1525">
-      <c r="A1525" s="9" t="n"/>
+      <c r="A1525" s="5" t="n"/>
     </row>
     <row r="1526">
-      <c r="A1526" s="9" t="n"/>
+      <c r="A1526" s="5" t="n"/>
     </row>
     <row r="1527">
-      <c r="A1527" s="9" t="n"/>
+      <c r="A1527" s="5" t="n"/>
     </row>
     <row r="1528">
-      <c r="A1528" s="9" t="n"/>
+      <c r="A1528" s="5" t="n"/>
     </row>
     <row r="1529">
-      <c r="A1529" s="9" t="n"/>
+      <c r="A1529" s="5" t="n"/>
     </row>
     <row r="1530">
-      <c r="A1530" s="9" t="n"/>
+      <c r="A1530" s="5" t="n"/>
     </row>
     <row r="1531">
-      <c r="A1531" s="9" t="n"/>
+      <c r="A1531" s="5" t="n"/>
     </row>
     <row r="1532">
-      <c r="A1532" s="9" t="n"/>
+      <c r="A1532" s="5" t="n"/>
     </row>
     <row r="1533">
-      <c r="A1533" s="9" t="n"/>
+      <c r="A1533" s="5" t="n"/>
     </row>
     <row r="1534">
-      <c r="A1534" s="9" t="n"/>
+      <c r="A1534" s="5" t="n"/>
     </row>
     <row r="1535">
-      <c r="A1535" s="9" t="n"/>
+      <c r="A1535" s="5" t="n"/>
     </row>
     <row r="1536">
-      <c r="A1536" s="9" t="n"/>
+      <c r="A1536" s="5" t="n"/>
     </row>
     <row r="1537">
-      <c r="A1537" s="9" t="n"/>
+      <c r="A1537" s="5" t="n"/>
     </row>
     <row r="1538">
-      <c r="A1538" s="9" t="n"/>
+      <c r="A1538" s="5" t="n"/>
     </row>
     <row r="1539">
-      <c r="A1539" s="9" t="n"/>
+      <c r="A1539" s="5" t="n"/>
     </row>
     <row r="1540">
-      <c r="A1540" s="9" t="n"/>
+      <c r="A1540" s="5" t="n"/>
     </row>
     <row r="1541">
-      <c r="A1541" s="9" t="n"/>
+      <c r="A1541" s="5" t="n"/>
     </row>
     <row r="1542">
-      <c r="A1542" s="9" t="n"/>
+      <c r="A1542" s="5" t="n"/>
     </row>
     <row r="1543">
-      <c r="A1543" s="9" t="n"/>
+      <c r="A1543" s="5" t="n"/>
     </row>
     <row r="1544">
-      <c r="A1544" s="9" t="n"/>
+      <c r="A1544" s="5" t="n"/>
     </row>
     <row r="1545">
-      <c r="A1545" s="9" t="n"/>
+      <c r="A1545" s="5" t="n"/>
     </row>
     <row r="1546">
-      <c r="A1546" s="9" t="n"/>
+      <c r="A1546" s="5" t="n"/>
     </row>
     <row r="1547">
-      <c r="A1547" s="9" t="n"/>
+      <c r="A1547" s="5" t="n"/>
     </row>
     <row r="1548">
-      <c r="A1548" s="9" t="n"/>
+      <c r="A1548" s="5" t="n"/>
     </row>
     <row r="1549">
-      <c r="A1549" s="9" t="n"/>
+      <c r="A1549" s="5" t="n"/>
     </row>
     <row r="1550">
-      <c r="A1550" s="9" t="n"/>
+      <c r="A1550" s="5" t="n"/>
     </row>
     <row r="1551">
-      <c r="A1551" s="9" t="n"/>
+      <c r="A1551" s="5" t="n"/>
     </row>
     <row r="1552">
-      <c r="A1552" s="9" t="n"/>
+      <c r="A1552" s="5" t="n"/>
     </row>
     <row r="1553">
-      <c r="A1553" s="9" t="n"/>
+      <c r="A1553" s="5" t="n"/>
     </row>
     <row r="1554">
-      <c r="A1554" s="9" t="n"/>
+      <c r="A1554" s="5" t="n"/>
     </row>
     <row r="1555">
-      <c r="A1555" s="9" t="n"/>
+      <c r="A1555" s="5" t="n"/>
     </row>
     <row r="1556">
-      <c r="A1556" s="9" t="n"/>
+      <c r="A1556" s="5" t="n"/>
     </row>
     <row r="1557">
-      <c r="A1557" s="9" t="n"/>
+      <c r="A1557" s="5" t="n"/>
     </row>
     <row r="1558">
-      <c r="A1558" s="9" t="n"/>
+      <c r="A1558" s="5" t="n"/>
     </row>
     <row r="1559">
-      <c r="A1559" s="9" t="n"/>
+      <c r="A1559" s="5" t="n"/>
     </row>
     <row r="1560">
-      <c r="A1560" s="9" t="n"/>
+      <c r="A1560" s="5" t="n"/>
     </row>
     <row r="1561">
-      <c r="A1561" s="9" t="n"/>
+      <c r="A1561" s="5" t="n"/>
     </row>
     <row r="1562">
-      <c r="A1562" s="9" t="n"/>
+      <c r="A1562" s="5" t="n"/>
     </row>
     <row r="1563">
-      <c r="A1563" s="9" t="n"/>
+      <c r="A1563" s="5" t="n"/>
     </row>
     <row r="1564">
-      <c r="A1564" s="9" t="n"/>
+      <c r="A1564" s="5" t="n"/>
     </row>
     <row r="1565">
-      <c r="A1565" s="9" t="n"/>
+      <c r="A1565" s="5" t="n"/>
     </row>
     <row r="1566">
-      <c r="A1566" s="9" t="n"/>
+      <c r="A1566" s="5" t="n"/>
     </row>
     <row r="1567">
-      <c r="A1567" s="9" t="n"/>
+      <c r="A1567" s="5" t="n"/>
     </row>
     <row r="1568">
-      <c r="A1568" s="9" t="n"/>
+      <c r="A1568" s="5" t="n"/>
     </row>
     <row r="1569">
-      <c r="A1569" s="9" t="n"/>
+      <c r="A1569" s="5" t="n"/>
     </row>
     <row r="1570">
-      <c r="A1570" s="9" t="n"/>
+      <c r="A1570" s="5" t="n"/>
     </row>
     <row r="1571">
-      <c r="A1571" s="9" t="n"/>
+      <c r="A1571" s="5" t="n"/>
     </row>
     <row r="1572">
-      <c r="A1572" s="9" t="n"/>
+      <c r="A1572" s="5" t="n"/>
     </row>
     <row r="1573">
-      <c r="A1573" s="9" t="n"/>
+      <c r="A1573" s="5" t="n"/>
     </row>
     <row r="1574">
-      <c r="A1574" s="9" t="n"/>
+      <c r="A1574" s="5" t="n"/>
     </row>
     <row r="1575">
-      <c r="A1575" s="9" t="n"/>
+      <c r="A1575" s="5" t="n"/>
     </row>
     <row r="1576">
-      <c r="A1576" s="9" t="n"/>
+      <c r="A1576" s="5" t="n"/>
     </row>
     <row r="1577">
-      <c r="A1577" s="9" t="n"/>
+      <c r="A1577" s="5" t="n"/>
     </row>
     <row r="1578">
-      <c r="A1578" s="9" t="n"/>
+      <c r="A1578" s="5" t="n"/>
     </row>
     <row r="1579">
-      <c r="A1579" s="9" t="n"/>
+      <c r="A1579" s="5" t="n"/>
     </row>
     <row r="1580">
-      <c r="A1580" s="9" t="n"/>
+      <c r="A1580" s="5" t="n"/>
     </row>
     <row r="1581">
-      <c r="A1581" s="9" t="n"/>
+      <c r="A1581" s="5" t="n"/>
     </row>
     <row r="1582">
-      <c r="A1582" s="9" t="n"/>
+      <c r="A1582" s="5" t="n"/>
     </row>
     <row r="1583">
-      <c r="A1583" s="9" t="n"/>
+      <c r="A1583" s="5" t="n"/>
     </row>
     <row r="1584">
-      <c r="A1584" s="9" t="n"/>
+      <c r="A1584" s="5" t="n"/>
     </row>
     <row r="1585">
-      <c r="A1585" s="9" t="n"/>
+      <c r="A1585" s="5" t="n"/>
     </row>
     <row r="1586">
-      <c r="A1586" s="9" t="n"/>
+      <c r="A1586" s="5" t="n"/>
     </row>
     <row r="1587">
-      <c r="A1587" s="9" t="n"/>
+      <c r="A1587" s="5" t="n"/>
     </row>
     <row r="1588">
-      <c r="A1588" s="9" t="n"/>
+      <c r="A1588" s="5" t="n"/>
     </row>
     <row r="1589">
-      <c r="A1589" s="9" t="n"/>
+      <c r="A1589" s="5" t="n"/>
     </row>
     <row r="1590">
-      <c r="A1590" s="9" t="n"/>
+      <c r="A1590" s="5" t="n"/>
     </row>
     <row r="1591">
-      <c r="A1591" s="9" t="n"/>
+      <c r="A1591" s="5" t="n"/>
     </row>
     <row r="1592">
-      <c r="A1592" s="9" t="n"/>
+      <c r="A1592" s="5" t="n"/>
     </row>
     <row r="1593">
-      <c r="A1593" s="9" t="n"/>
+      <c r="A1593" s="5" t="n"/>
     </row>
     <row r="1594">
-      <c r="A1594" s="9" t="n"/>
+      <c r="A1594" s="5" t="n"/>
     </row>
     <row r="1595">
-      <c r="A1595" s="9" t="n"/>
+      <c r="A1595" s="5" t="n"/>
     </row>
     <row r="1596">
-      <c r="A1596" s="9" t="n"/>
+      <c r="A1596" s="5" t="n"/>
     </row>
     <row r="1597">
-      <c r="A1597" s="9" t="n"/>
+      <c r="A1597" s="5" t="n"/>
     </row>
     <row r="1598">
-      <c r="A1598" s="9" t="n"/>
+      <c r="A1598" s="5" t="n"/>
     </row>
     <row r="1599">
-      <c r="A1599" s="9" t="n"/>
+      <c r="A1599" s="5" t="n"/>
     </row>
     <row r="1600">
-      <c r="A1600" s="9" t="n"/>
+      <c r="A1600" s="5" t="n"/>
     </row>
     <row r="1601">
-      <c r="A1601" s="9" t="n"/>
+      <c r="A1601" s="5" t="n"/>
     </row>
     <row r="1602">
-      <c r="A1602" s="9" t="n"/>
+      <c r="A1602" s="5" t="n"/>
     </row>
     <row r="1603">
-      <c r="A1603" s="9" t="n"/>
+      <c r="A1603" s="5" t="n"/>
     </row>
     <row r="1604">
-      <c r="A1604" s="9" t="n"/>
+      <c r="A1604" s="5" t="n"/>
     </row>
     <row r="1605">
-      <c r="A1605" s="9" t="n"/>
+      <c r="A1605" s="5" t="n"/>
     </row>
     <row r="1606">
-      <c r="A1606" s="9" t="n"/>
+      <c r="A1606" s="5" t="n"/>
     </row>
     <row r="1607">
-      <c r="A1607" s="9" t="n"/>
+      <c r="A1607" s="5" t="n"/>
     </row>
     <row r="1608">
-      <c r="A1608" s="9" t="n"/>
+      <c r="A1608" s="5" t="n"/>
     </row>
     <row r="1609">
-      <c r="A1609" s="9" t="n"/>
+      <c r="A1609" s="5" t="n"/>
     </row>
     <row r="1610">
-      <c r="A1610" s="9" t="n"/>
+      <c r="A1610" s="5" t="n"/>
     </row>
     <row r="1611">
-      <c r="A1611" s="9" t="n"/>
+      <c r="A1611" s="5" t="n"/>
     </row>
     <row r="1612">
-      <c r="A1612" s="9" t="n"/>
+      <c r="A1612" s="5" t="n"/>
     </row>
     <row r="1613">
-      <c r="A1613" s="9" t="n"/>
+      <c r="A1613" s="5" t="n"/>
     </row>
     <row r="1614">
-      <c r="A1614" s="9" t="n"/>
+      <c r="A1614" s="5" t="n"/>
     </row>
     <row r="1615">
-      <c r="A1615" s="9" t="n"/>
+      <c r="A1615" s="5" t="n"/>
     </row>
     <row r="1616">
-      <c r="A1616" s="9" t="n"/>
+      <c r="A1616" s="5" t="n"/>
     </row>
     <row r="1617">
-      <c r="A1617" s="9" t="n"/>
+      <c r="A1617" s="5" t="n"/>
     </row>
     <row r="1618">
-      <c r="A1618" s="9" t="n"/>
+      <c r="A1618" s="5" t="n"/>
     </row>
     <row r="1619">
-      <c r="A1619" s="9" t="n"/>
+      <c r="A1619" s="5" t="n"/>
     </row>
     <row r="1620">
-      <c r="A1620" s="9" t="n"/>
+      <c r="A1620" s="5" t="n"/>
     </row>
     <row r="1621">
-      <c r="A1621" s="9" t="n"/>
+      <c r="A1621" s="5" t="n"/>
     </row>
     <row r="1622">
-      <c r="A1622" s="9" t="n"/>
+      <c r="A1622" s="5" t="n"/>
     </row>
     <row r="1623">
-      <c r="A1623" s="9" t="n"/>
+      <c r="A1623" s="5" t="n"/>
     </row>
     <row r="1624">
-      <c r="A1624" s="9" t="n"/>
+      <c r="A1624" s="5" t="n"/>
     </row>
     <row r="1625">
-      <c r="A1625" s="9" t="n"/>
+      <c r="A1625" s="5" t="n"/>
     </row>
     <row r="1626">
-      <c r="A1626" s="9" t="n"/>
+      <c r="A1626" s="5" t="n"/>
     </row>
     <row r="1627">
-      <c r="A1627" s="9" t="n"/>
+      <c r="A1627" s="5" t="n"/>
     </row>
     <row r="1628">
-      <c r="A1628" s="9" t="n"/>
+      <c r="A1628" s="5" t="n"/>
     </row>
     <row r="1629">
-      <c r="A1629" s="9" t="n"/>
+      <c r="A1629" s="5" t="n"/>
     </row>
     <row r="1630">
-      <c r="A1630" s="9" t="n"/>
+      <c r="A1630" s="5" t="n"/>
     </row>
     <row r="1631">
-      <c r="A1631" s="9" t="n"/>
+      <c r="A1631" s="5" t="n"/>
     </row>
     <row r="1632">
-      <c r="A1632" s="9" t="n"/>
+      <c r="A1632" s="5" t="n"/>
     </row>
     <row r="1633">
-      <c r="A1633" s="9" t="n"/>
+      <c r="A1633" s="5" t="n"/>
     </row>
     <row r="1634">
-      <c r="A1634" s="9" t="n"/>
+      <c r="A1634" s="5" t="n"/>
     </row>
     <row r="1635">
-      <c r="A1635" s="9" t="n"/>
+      <c r="A1635" s="5" t="n"/>
     </row>
     <row r="1636">
-      <c r="A1636" s="9" t="n"/>
+      <c r="A1636" s="5" t="n"/>
     </row>
     <row r="1637">
-      <c r="A1637" s="9" t="n"/>
+      <c r="A1637" s="5" t="n"/>
     </row>
     <row r="1638">
-      <c r="A1638" s="9" t="n"/>
+      <c r="A1638" s="5" t="n"/>
     </row>
     <row r="1639">
-      <c r="A1639" s="9" t="n"/>
+      <c r="A1639" s="5" t="n"/>
     </row>
     <row r="1640">
-      <c r="A1640" s="9" t="n"/>
+      <c r="A1640" s="5" t="n"/>
     </row>
     <row r="1641">
-      <c r="A1641" s="9" t="n"/>
+      <c r="A1641" s="5" t="n"/>
     </row>
     <row r="1642">
-      <c r="A1642" s="9" t="n"/>
+      <c r="A1642" s="5" t="n"/>
     </row>
     <row r="1643">
-      <c r="A1643" s="9" t="n"/>
+      <c r="A1643" s="5" t="n"/>
     </row>
     <row r="1644">
-      <c r="A1644" s="9" t="n"/>
+      <c r="A1644" s="5" t="n"/>
     </row>
     <row r="1645">
-      <c r="A1645" s="9" t="n"/>
+      <c r="A1645" s="5" t="n"/>
     </row>
     <row r="1646">
-      <c r="A1646" s="9" t="n"/>
+      <c r="A1646" s="5" t="n"/>
     </row>
     <row r="1647">
-      <c r="A1647" s="9" t="n"/>
+      <c r="A1647" s="5" t="n"/>
     </row>
     <row r="1648">
-      <c r="A1648" s="9" t="n"/>
+      <c r="A1648" s="5" t="n"/>
     </row>
     <row r="1649">
-      <c r="A1649" s="9" t="n"/>
+      <c r="A1649" s="5" t="n"/>
     </row>
     <row r="1650">
-      <c r="A1650" s="9" t="n"/>
+      <c r="A1650" s="5" t="n"/>
     </row>
     <row r="1651">
-      <c r="A1651" s="9" t="n"/>
+      <c r="A1651" s="5" t="n"/>
     </row>
     <row r="1652">
-      <c r="A1652" s="9" t="n"/>
+      <c r="A1652" s="5" t="n"/>
     </row>
     <row r="1653">
-      <c r="A1653" s="9" t="n"/>
+      <c r="A1653" s="5" t="n"/>
     </row>
     <row r="1654">
-      <c r="A1654" s="9" t="n"/>
+      <c r="A1654" s="5" t="n"/>
     </row>
     <row r="1655">
-      <c r="A1655" s="9" t="n"/>
+      <c r="A1655" s="5" t="n"/>
     </row>
     <row r="1656">
-      <c r="A1656" s="9" t="n"/>
+      <c r="A1656" s="5" t="n"/>
     </row>
     <row r="1657">
-      <c r="A1657" s="9" t="n"/>
+      <c r="A1657" s="5" t="n"/>
     </row>
     <row r="1658">
-      <c r="A1658" s="9" t="n"/>
+      <c r="A1658" s="5" t="n"/>
     </row>
     <row r="1659">
-      <c r="A1659" s="9" t="n"/>
+      <c r="A1659" s="5" t="n"/>
     </row>
     <row r="1660">
-      <c r="A1660" s="9" t="n"/>
+      <c r="A1660" s="5" t="n"/>
     </row>
     <row r="1661">
-      <c r="A1661" s="9" t="n"/>
+      <c r="A1661" s="5" t="n"/>
     </row>
     <row r="1662">
-      <c r="A1662" s="9" t="n"/>
+      <c r="A1662" s="5" t="n"/>
     </row>
     <row r="1663">
-      <c r="A1663" s="9" t="n"/>
+      <c r="A1663" s="5" t="n"/>
     </row>
     <row r="1664">
-      <c r="A1664" s="9" t="n"/>
+      <c r="A1664" s="5" t="n"/>
     </row>
     <row r="1665">
-      <c r="A1665" s="9" t="n"/>
+      <c r="A1665" s="5" t="n"/>
     </row>
     <row r="1666">
-      <c r="A1666" s="9" t="n"/>
+      <c r="A1666" s="5" t="n"/>
     </row>
     <row r="1667">
-      <c r="A1667" s="9" t="n"/>
+      <c r="A1667" s="5" t="n"/>
     </row>
     <row r="1668">
-      <c r="A1668" s="9" t="n"/>
+      <c r="A1668" s="5" t="n"/>
     </row>
     <row r="1669">
-      <c r="A1669" s="9" t="n"/>
+      <c r="A1669" s="5" t="n"/>
     </row>
     <row r="1670">
-      <c r="A1670" s="9" t="n"/>
+      <c r="A1670" s="5" t="n"/>
     </row>
     <row r="1671">
-      <c r="A1671" s="9" t="n"/>
+      <c r="A1671" s="5" t="n"/>
     </row>
     <row r="1672">
-      <c r="A1672" s="9" t="n"/>
+      <c r="A1672" s="5" t="n"/>
     </row>
     <row r="1673">
-      <c r="A1673" s="9" t="n"/>
+      <c r="A1673" s="5" t="n"/>
     </row>
     <row r="1674">
-      <c r="A1674" s="9" t="n"/>
+      <c r="A1674" s="5" t="n"/>
     </row>
     <row r="1675">
-      <c r="A1675" s="9" t="n"/>
+      <c r="A1675" s="5" t="n"/>
     </row>
     <row r="1676">
-      <c r="A1676" s="9" t="n"/>
+      <c r="A1676" s="5" t="n"/>
     </row>
     <row r="1677">
-      <c r="A1677" s="9" t="n"/>
+      <c r="A1677" s="5" t="n"/>
     </row>
     <row r="1678">
-      <c r="A1678" s="9" t="n"/>
+      <c r="A1678" s="5" t="n"/>
     </row>
     <row r="1679">
-      <c r="A1679" s="9" t="n"/>
+      <c r="A1679" s="5" t="n"/>
     </row>
     <row r="1680">
-      <c r="A1680" s="9" t="n"/>
+      <c r="A1680" s="5" t="n"/>
     </row>
     <row r="1681">
-      <c r="A1681" s="9" t="n"/>
+      <c r="A1681" s="5" t="n"/>
     </row>
     <row r="1682">
-      <c r="A1682" s="9" t="n"/>
+      <c r="A1682" s="5" t="n"/>
     </row>
     <row r="1683">
-      <c r="A1683" s="9" t="n"/>
+      <c r="A1683" s="5" t="n"/>
     </row>
     <row r="1684">
-      <c r="A1684" s="9" t="n"/>
+      <c r="A1684" s="5" t="n"/>
     </row>
     <row r="1685">
-      <c r="A1685" s="9" t="n"/>
+      <c r="A1685" s="5" t="n"/>
     </row>
     <row r="1686">
-      <c r="A1686" s="9" t="n"/>
+      <c r="A1686" s="5" t="n"/>
     </row>
     <row r="1687">
-      <c r="A1687" s="9" t="n"/>
+      <c r="A1687" s="5" t="n"/>
     </row>
     <row r="1688">
-      <c r="A1688" s="9" t="n"/>
+      <c r="A1688" s="5" t="n"/>
     </row>
     <row r="1689">
-      <c r="A1689" s="9" t="n"/>
+      <c r="A1689" s="5" t="n"/>
     </row>
     <row r="1690">
-      <c r="A1690" s="9" t="n"/>
+      <c r="A1690" s="5" t="n"/>
     </row>
     <row r="1691">
-      <c r="A1691" s="9" t="n"/>
+      <c r="A1691" s="5" t="n"/>
     </row>
     <row r="1692">
-      <c r="A1692" s="9" t="n"/>
+      <c r="A1692" s="5" t="n"/>
     </row>
     <row r="1693">
-      <c r="A1693" s="9" t="n"/>
+      <c r="A1693" s="5" t="n"/>
     </row>
     <row r="1694">
-      <c r="A1694" s="9" t="n"/>
+      <c r="A1694" s="5" t="n"/>
     </row>
     <row r="1695">
-      <c r="A1695" s="9" t="n"/>
+      <c r="A1695" s="5" t="n"/>
     </row>
     <row r="1696">
-      <c r="A1696" s="9" t="n"/>
+      <c r="A1696" s="5" t="n"/>
     </row>
     <row r="1697">
-      <c r="A1697" s="9" t="n"/>
+      <c r="A1697" s="5" t="n"/>
     </row>
     <row r="1698">
-      <c r="A1698" s="9" t="n"/>
+      <c r="A1698" s="5" t="n"/>
     </row>
     <row r="1699">
-      <c r="A1699" s="9" t="n"/>
+      <c r="A1699" s="5" t="n"/>
     </row>
     <row r="1700">
-      <c r="A1700" s="9" t="n"/>
+      <c r="A1700" s="5" t="n"/>
     </row>
     <row r="1701">
-      <c r="A1701" s="9" t="n"/>
+      <c r="A1701" s="5" t="n"/>
     </row>
     <row r="1702">
-      <c r="A1702" s="9" t="n"/>
+      <c r="A1702" s="5" t="n"/>
     </row>
     <row r="1703">
-      <c r="A1703" s="9" t="n"/>
+      <c r="A1703" s="5" t="n"/>
     </row>
     <row r="1704">
-      <c r="A1704" s="9" t="n"/>
+      <c r="A1704" s="5" t="n"/>
     </row>
     <row r="1705">
-      <c r="A1705" s="9" t="n"/>
+      <c r="A1705" s="5" t="n"/>
     </row>
     <row r="1706">
-      <c r="A1706" s="9" t="n"/>
+      <c r="A1706" s="5" t="n"/>
     </row>
     <row r="1707">
-      <c r="A1707" s="9" t="n"/>
+      <c r="A1707" s="5" t="n"/>
     </row>
     <row r="1708">
-      <c r="A1708" s="9" t="n"/>
+      <c r="A1708" s="5" t="n"/>
     </row>
     <row r="1709">
-      <c r="A1709" s="9" t="n"/>
+      <c r="A1709" s="5" t="n"/>
     </row>
     <row r="1710">
-      <c r="A1710" s="9" t="n"/>
+      <c r="A1710" s="5" t="n"/>
     </row>
     <row r="1711">
-      <c r="A1711" s="9" t="n"/>
+      <c r="A1711" s="5" t="n"/>
     </row>
     <row r="1712">
-      <c r="A1712" s="9" t="n"/>
+      <c r="A1712" s="5" t="n"/>
     </row>
     <row r="1713">
-      <c r="A1713" s="9" t="n"/>
+      <c r="A1713" s="5" t="n"/>
     </row>
     <row r="1714">
-      <c r="A1714" s="9" t="n"/>
+      <c r="A1714" s="5" t="n"/>
     </row>
     <row r="1715">
-      <c r="A1715" s="9" t="n"/>
+      <c r="A1715" s="5" t="n"/>
     </row>
     <row r="1716">
-      <c r="A1716" s="9" t="n"/>
+      <c r="A1716" s="5" t="n"/>
     </row>
     <row r="1717">
-      <c r="A1717" s="9" t="n"/>
+      <c r="A1717" s="5" t="n"/>
     </row>
     <row r="1718">
-      <c r="A1718" s="9" t="n"/>
+      <c r="A1718" s="5" t="n"/>
     </row>
     <row r="1719">
-      <c r="A1719" s="9" t="n"/>
+      <c r="A1719" s="5" t="n"/>
     </row>
     <row r="1720">
-      <c r="A1720" s="9" t="n"/>
+      <c r="A1720" s="5" t="n"/>
     </row>
     <row r="1721">
-      <c r="A1721" s="9" t="n"/>
+      <c r="A1721" s="5" t="n"/>
     </row>
     <row r="1722">
-      <c r="A1722" s="9" t="n"/>
+      <c r="A1722" s="5" t="n"/>
     </row>
     <row r="1723">
-      <c r="A1723" s="9" t="n"/>
+      <c r="A1723" s="5" t="n"/>
     </row>
     <row r="1724">
-      <c r="A1724" s="9" t="n"/>
+      <c r="A1724" s="5" t="n"/>
     </row>
     <row r="1725">
-      <c r="A1725" s="9" t="n"/>
+      <c r="A1725" s="5" t="n"/>
     </row>
     <row r="1726">
-      <c r="A1726" s="9" t="n"/>
+      <c r="A1726" s="5" t="n"/>
     </row>
     <row r="1727">
-      <c r="A1727" s="9" t="n"/>
+      <c r="A1727" s="5" t="n"/>
     </row>
     <row r="1728">
-      <c r="A1728" s="9" t="n"/>
+      <c r="A1728" s="5" t="n"/>
     </row>
     <row r="1729">
-      <c r="A1729" s="9" t="n"/>
+      <c r="A1729" s="5" t="n"/>
     </row>
     <row r="1730">
-      <c r="A1730" s="9" t="n"/>
+      <c r="A1730" s="5" t="n"/>
     </row>
     <row r="1731">
-      <c r="A1731" s="9" t="n"/>
+      <c r="A1731" s="5" t="n"/>
     </row>
     <row r="1732">
-      <c r="A1732" s="9" t="n"/>
+      <c r="A1732" s="5" t="n"/>
     </row>
     <row r="1733">
-      <c r="A1733" s="9" t="n"/>
+      <c r="A1733" s="5" t="n"/>
     </row>
     <row r="1734">
-      <c r="A1734" s="9" t="n"/>
+      <c r="A1734" s="5" t="n"/>
     </row>
     <row r="1735">
-      <c r="A1735" s="9" t="n"/>
+      <c r="A1735" s="5" t="n"/>
     </row>
     <row r="1736">
-      <c r="A1736" s="9" t="n"/>
+      <c r="A1736" s="5" t="n"/>
     </row>
     <row r="1737">
-      <c r="A1737" s="9" t="n"/>
+      <c r="A1737" s="5" t="n"/>
     </row>
     <row r="1738">
-      <c r="A1738" s="9" t="n"/>
+      <c r="A1738" s="5" t="n"/>
     </row>
     <row r="1739">
-      <c r="A1739" s="9" t="n"/>
+      <c r="A1739" s="5" t="n"/>
     </row>
     <row r="1740">
-      <c r="A1740" s="9" t="n"/>
+      <c r="A1740" s="5" t="n"/>
     </row>
     <row r="1741">
-      <c r="A1741" s="9" t="n"/>
+      <c r="A1741" s="5" t="n"/>
     </row>
     <row r="1742">
-      <c r="A1742" s="9" t="n"/>
+      <c r="A1742" s="5" t="n"/>
     </row>
     <row r="1743">
-      <c r="A1743" s="9" t="n"/>
+      <c r="A1743" s="5" t="n"/>
     </row>
     <row r="1744">
-      <c r="A1744" s="9" t="n"/>
+      <c r="A1744" s="5" t="n"/>
     </row>
     <row r="1745">
-      <c r="A1745" s="9" t="n"/>
+      <c r="A1745" s="5" t="n"/>
     </row>
     <row r="1746">
-      <c r="A1746" s="9" t="n"/>
+      <c r="A1746" s="5" t="n"/>
     </row>
     <row r="1747">
-      <c r="A1747" s="9" t="n"/>
+      <c r="A1747" s="5" t="n"/>
     </row>
     <row r="1748">
-      <c r="A1748" s="9" t="n"/>
+      <c r="A1748" s="5" t="n"/>
     </row>
     <row r="1749">
-      <c r="A1749" s="9" t="n"/>
+      <c r="A1749" s="5" t="n"/>
     </row>
     <row r="1750">
-      <c r="A1750" s="9" t="n"/>
+      <c r="A1750" s="5" t="n"/>
     </row>
     <row r="1751">
-      <c r="A1751" s="9" t="n"/>
+      <c r="A1751" s="5" t="n"/>
     </row>
     <row r="1752">
-      <c r="A1752" s="9" t="n"/>
+      <c r="A1752" s="5" t="n"/>
     </row>
     <row r="1753">
-      <c r="A1753" s="9" t="n"/>
+      <c r="A1753" s="5" t="n"/>
     </row>
     <row r="1754">
-      <c r="A1754" s="9" t="n"/>
+      <c r="A1754" s="5" t="n"/>
     </row>
     <row r="1755">
-      <c r="A1755" s="9" t="n"/>
+      <c r="A1755" s="5" t="n"/>
     </row>
     <row r="1756">
-      <c r="A1756" s="9" t="n"/>
+      <c r="A1756" s="5" t="n"/>
     </row>
     <row r="1757">
-      <c r="A1757" s="9" t="n"/>
+      <c r="A1757" s="5" t="n"/>
     </row>
     <row r="1758">
-      <c r="A1758" s="9" t="n"/>
+      <c r="A1758" s="5" t="n"/>
     </row>
     <row r="1759">
-      <c r="A1759" s="9" t="n"/>
+      <c r="A1759" s="5" t="n"/>
     </row>
     <row r="1760">
-      <c r="A1760" s="9" t="n"/>
+      <c r="A1760" s="5" t="n"/>
     </row>
     <row r="1761">
-      <c r="A1761" s="9" t="n"/>
+      <c r="A1761" s="5" t="n"/>
     </row>
     <row r="1762">
-      <c r="A1762" s="9" t="n"/>
+      <c r="A1762" s="5" t="n"/>
     </row>
     <row r="1763">
-      <c r="A1763" s="9" t="n"/>
+      <c r="A1763" s="5" t="n"/>
     </row>
     <row r="1764">
-      <c r="A1764" s="9" t="n"/>
+      <c r="A1764" s="5" t="n"/>
     </row>
     <row r="1765">
-      <c r="A1765" s="9" t="n"/>
+      <c r="A1765" s="5" t="n"/>
     </row>
     <row r="1766">
-      <c r="A1766" s="9" t="n"/>
+      <c r="A1766" s="5" t="n"/>
     </row>
     <row r="1767">
-      <c r="A1767" s="9" t="n"/>
+      <c r="A1767" s="5" t="n"/>
     </row>
     <row r="1768">
-      <c r="A1768" s="9" t="n"/>
+      <c r="A1768" s="5" t="n"/>
     </row>
     <row r="1769">
-      <c r="A1769" s="9" t="n"/>
+      <c r="A1769" s="5" t="n"/>
     </row>
     <row r="1770">
-      <c r="A1770" s="9" t="n"/>
+      <c r="A1770" s="5" t="n"/>
     </row>
     <row r="1771">
-      <c r="A1771" s="9" t="n"/>
+      <c r="A1771" s="5" t="n"/>
     </row>
     <row r="1772">
-      <c r="A1772" s="9" t="n"/>
+      <c r="A1772" s="5" t="n"/>
     </row>
     <row r="1773">
-      <c r="A1773" s="9" t="n"/>
+      <c r="A1773" s="5" t="n"/>
     </row>
     <row r="1774">
-      <c r="A1774" s="9" t="n"/>
+      <c r="A1774" s="5" t="n"/>
     </row>
     <row r="1775">
-      <c r="A1775" s="9" t="n"/>
+      <c r="A1775" s="5" t="n"/>
     </row>
     <row r="1776">
-      <c r="A1776" s="9" t="n"/>
+      <c r="A1776" s="5" t="n"/>
     </row>
     <row r="1777">
-      <c r="A1777" s="9" t="n"/>
+      <c r="A1777" s="5" t="n"/>
     </row>
     <row r="1778">
-      <c r="A1778" s="9" t="n"/>
+      <c r="A1778" s="5" t="n"/>
     </row>
     <row r="1779">
-      <c r="A1779" s="9" t="n"/>
+      <c r="A1779" s="5" t="n"/>
     </row>
     <row r="1780">
-      <c r="A1780" s="9" t="n"/>
+      <c r="A1780" s="5" t="n"/>
     </row>
     <row r="1781">
-      <c r="A1781" s="9" t="n"/>
+      <c r="A1781" s="5" t="n"/>
     </row>
     <row r="1782">
-      <c r="A1782" s="9" t="n"/>
+      <c r="A1782" s="5" t="n"/>
     </row>
     <row r="1783">
-      <c r="A1783" s="9" t="n"/>
+      <c r="A1783" s="5" t="n"/>
     </row>
     <row r="1784">
-      <c r="A1784" s="9" t="n"/>
+      <c r="A1784" s="5" t="n"/>
     </row>
     <row r="1785">
-      <c r="A1785" s="9" t="n"/>
+      <c r="A1785" s="5" t="n"/>
     </row>
     <row r="1786">
-      <c r="A1786" s="9" t="n"/>
+      <c r="A1786" s="5" t="n"/>
     </row>
     <row r="1787">
-      <c r="A1787" s="9" t="n"/>
+      <c r="A1787" s="5" t="n"/>
     </row>
     <row r="1788">
-      <c r="A1788" s="9" t="n"/>
+      <c r="A1788" s="5" t="n"/>
     </row>
     <row r="1789">
-      <c r="A1789" s="9" t="n"/>
+      <c r="A1789" s="5" t="n"/>
     </row>
     <row r="1790">
-      <c r="A1790" s="9" t="n"/>
+      <c r="A1790" s="5" t="n"/>
     </row>
     <row r="1791">
-      <c r="A1791" s="9" t="n"/>
+      <c r="A1791" s="5" t="n"/>
     </row>
     <row r="1792">
-      <c r="A1792" s="9" t="n"/>
+      <c r="A1792" s="5" t="n"/>
     </row>
     <row r="1793">
-      <c r="A1793" s="9" t="n"/>
+      <c r="A1793" s="5" t="n"/>
     </row>
     <row r="1794">
-      <c r="A1794" s="9" t="n"/>
+      <c r="A1794" s="5" t="n"/>
     </row>
     <row r="1795">
-      <c r="A1795" s="9" t="n"/>
+      <c r="A1795" s="5" t="n"/>
     </row>
     <row r="1796">
-      <c r="A1796" s="9" t="n"/>
+      <c r="A1796" s="5" t="n"/>
     </row>
     <row r="1797">
-      <c r="A1797" s="9" t="n"/>
+      <c r="A1797" s="5" t="n"/>
     </row>
     <row r="1798">
-      <c r="A1798" s="9" t="n"/>
+      <c r="A1798" s="5" t="n"/>
     </row>
     <row r="1799">
-      <c r="A1799" s="9" t="n"/>
+      <c r="A1799" s="5" t="n"/>
     </row>
     <row r="1800">
-      <c r="A1800" s="9" t="n"/>
+      <c r="A1800" s="5" t="n"/>
     </row>
     <row r="1801">
-      <c r="A1801" s="9" t="n"/>
+      <c r="A1801" s="5" t="n"/>
     </row>
     <row r="1802">
-      <c r="A1802" s="9" t="n"/>
+      <c r="A1802" s="5" t="n"/>
     </row>
     <row r="1803">
-      <c r="A1803" s="9" t="n"/>
+      <c r="A1803" s="5" t="n"/>
     </row>
     <row r="1804">
-      <c r="A1804" s="9" t="n"/>
+      <c r="A1804" s="5" t="n"/>
     </row>
     <row r="1805">
-      <c r="A1805" s="9" t="n"/>
+      <c r="A1805" s="5" t="n"/>
     </row>
     <row r="1806">
-      <c r="A1806" s="9" t="n"/>
+      <c r="A1806" s="5" t="n"/>
     </row>
     <row r="1807">
-      <c r="A1807" s="9" t="n"/>
+      <c r="A1807" s="5" t="n"/>
     </row>
     <row r="1808">
-      <c r="A1808" s="9" t="n"/>
+      <c r="A1808" s="5" t="n"/>
     </row>
     <row r="1809">
-      <c r="A1809" s="9" t="n"/>
+      <c r="A1809" s="5" t="n"/>
     </row>
     <row r="1810">
-      <c r="A1810" s="9" t="n"/>
+      <c r="A1810" s="5" t="n"/>
     </row>
     <row r="1811">
-      <c r="A1811" s="9" t="n"/>
+      <c r="A1811" s="5" t="n"/>
     </row>
     <row r="1812">
-      <c r="A1812" s="9" t="n"/>
+      <c r="A1812" s="5" t="n"/>
     </row>
     <row r="1813">
-      <c r="A1813" s="9" t="n"/>
+      <c r="A1813" s="5" t="n"/>
     </row>
     <row r="1814">
-      <c r="A1814" s="9" t="n"/>
+      <c r="A1814" s="5" t="n"/>
     </row>
     <row r="1815">
-      <c r="A1815" s="9" t="n"/>
+      <c r="A1815" s="5" t="n"/>
     </row>
     <row r="1816">
-      <c r="A1816" s="9" t="n"/>
+      <c r="A1816" s="5" t="n"/>
     </row>
     <row r="1817">
-      <c r="A1817" s="9" t="n"/>
+      <c r="A1817" s="5" t="n"/>
     </row>
     <row r="1818">
-      <c r="A1818" s="9" t="n"/>
+      <c r="A1818" s="5" t="n"/>
     </row>
     <row r="1819">
-      <c r="A1819" s="9" t="n"/>
+      <c r="A1819" s="5" t="n"/>
     </row>
     <row r="1820">
-      <c r="A1820" s="9" t="n"/>
+      <c r="A1820" s="5" t="n"/>
     </row>
     <row r="1821">
-      <c r="A1821" s="9" t="n"/>
+      <c r="A1821" s="5" t="n"/>
     </row>
     <row r="1822">
-      <c r="A1822" s="9" t="n"/>
+      <c r="A1822" s="5" t="n"/>
     </row>
     <row r="1823">
-      <c r="A1823" s="9" t="n"/>
+      <c r="A1823" s="5" t="n"/>
     </row>
     <row r="1824">
-      <c r="A1824" s="9" t="n"/>
+      <c r="A1824" s="5" t="n"/>
     </row>
     <row r="1825">
-      <c r="A1825" s="9" t="n"/>
+      <c r="A1825" s="5" t="n"/>
     </row>
     <row r="1826">
-      <c r="A1826" s="9" t="n"/>
+      <c r="A1826" s="5" t="n"/>
     </row>
     <row r="1827">
-      <c r="A1827" s="9" t="n"/>
+      <c r="A1827" s="5" t="n"/>
     </row>
     <row r="1828">
-      <c r="A1828" s="9" t="n"/>
+      <c r="A1828" s="5" t="n"/>
     </row>
     <row r="1829">
-      <c r="A1829" s="9" t="n"/>
+      <c r="A1829" s="5" t="n"/>
     </row>
     <row r="1830">
-      <c r="A1830" s="9" t="n"/>
+      <c r="A1830" s="5" t="n"/>
     </row>
     <row r="1831">
-      <c r="A1831" s="9" t="n"/>
+      <c r="A1831" s="5" t="n"/>
     </row>
     <row r="1832">
-      <c r="A1832" s="9" t="n"/>
+      <c r="A1832" s="5" t="n"/>
     </row>
     <row r="1833">
-      <c r="A1833" s="9" t="n"/>
+      <c r="A1833" s="5" t="n"/>
     </row>
     <row r="1834">
-      <c r="A1834" s="9" t="n"/>
+      <c r="A1834" s="5" t="n"/>
     </row>
     <row r="1835">
-      <c r="A1835" s="9" t="n"/>
+      <c r="A1835" s="5" t="n"/>
     </row>
     <row r="1836">
-      <c r="A1836" s="9" t="n"/>
+      <c r="A1836" s="5" t="n"/>
     </row>
     <row r="1837">
-      <c r="A1837" s="9" t="n"/>
+      <c r="A1837" s="5" t="n"/>
     </row>
     <row r="1838">
-      <c r="A1838" s="9" t="n"/>
+      <c r="A1838" s="5" t="n"/>
     </row>
     <row r="1839">
-      <c r="A1839" s="9" t="n"/>
+      <c r="A1839" s="5" t="n"/>
     </row>
     <row r="1840">
-      <c r="A1840" s="9" t="n"/>
+      <c r="A1840" s="5" t="n"/>
     </row>
     <row r="1841">
-      <c r="A1841" s="9" t="n"/>
+      <c r="A1841" s="5" t="n"/>
     </row>
     <row r="1842">
-      <c r="A1842" s="9" t="n"/>
+      <c r="A1842" s="5" t="n"/>
     </row>
     <row r="1843">
-      <c r="A1843" s="9" t="n"/>
+      <c r="A1843" s="5" t="n"/>
     </row>
     <row r="1844">
-      <c r="A1844" s="9" t="n"/>
+      <c r="A1844" s="5" t="n"/>
     </row>
     <row r="1845">
-      <c r="A1845" s="9" t="n"/>
+      <c r="A1845" s="5" t="n"/>
     </row>
     <row r="1846">
-      <c r="A1846" s="9" t="n"/>
+      <c r="A1846" s="5" t="n"/>
     </row>
     <row r="1847">
-      <c r="A1847" s="9" t="n"/>
+      <c r="A1847" s="5" t="n"/>
     </row>
     <row r="1848">
-      <c r="A1848" s="9" t="n"/>
+      <c r="A1848" s="5" t="n"/>
     </row>
     <row r="1849">
-      <c r="A1849" s="9" t="n"/>
+      <c r="A1849" s="5" t="n"/>
     </row>
     <row r="1850">
-      <c r="A1850" s="9" t="n"/>
+      <c r="A1850" s="5" t="n"/>
     </row>
     <row r="1851">
-      <c r="A1851" s="9" t="n"/>
+      <c r="A1851" s="5" t="n"/>
     </row>
     <row r="1852">
-      <c r="A1852" s="9" t="n"/>
+      <c r="A1852" s="5" t="n"/>
     </row>
     <row r="1853">
-      <c r="A1853" s="9" t="n"/>
+      <c r="A1853" s="5" t="n"/>
     </row>
     <row r="1854">
-      <c r="A1854" s="9" t="n"/>
+      <c r="A1854" s="5" t="n"/>
     </row>
     <row r="1855">
-      <c r="A1855" s="9" t="n"/>
+      <c r="A1855" s="5" t="n"/>
     </row>
     <row r="1856">
-      <c r="A1856" s="9" t="n"/>
+      <c r="A1856" s="5" t="n"/>
     </row>
     <row r="1857">
-      <c r="A1857" s="9" t="n"/>
+      <c r="A1857" s="5" t="n"/>
     </row>
     <row r="1858">
-      <c r="A1858" s="9" t="n"/>
+      <c r="A1858" s="5" t="n"/>
     </row>
     <row r="1859">
-      <c r="A1859" s="9" t="n"/>
+      <c r="A1859" s="5" t="n"/>
     </row>
     <row r="1860">
-      <c r="A1860" s="9" t="n"/>
+      <c r="A1860" s="5" t="n"/>
     </row>
     <row r="1861">
-      <c r="A1861" s="9" t="n"/>
+      <c r="A1861" s="5" t="n"/>
     </row>
     <row r="1862">
-      <c r="A1862" s="9" t="n"/>
+      <c r="A1862" s="5" t="n"/>
     </row>
     <row r="1863">
-      <c r="A1863" s="9" t="n"/>
+      <c r="A1863" s="5" t="n"/>
     </row>
     <row r="1864">
-      <c r="A1864" s="9" t="n"/>
+      <c r="A1864" s="5" t="n"/>
     </row>
     <row r="1865">
-      <c r="A1865" s="9" t="n"/>
+      <c r="A1865" s="5" t="n"/>
     </row>
     <row r="1866">
-      <c r="A1866" s="9" t="n"/>
+      <c r="A1866" s="5" t="n"/>
     </row>
     <row r="1867">
-      <c r="A1867" s="9" t="n"/>
+      <c r="A1867" s="5" t="n"/>
     </row>
     <row r="1868">
-      <c r="A1868" s="9" t="n"/>
+      <c r="A1868" s="5" t="n"/>
     </row>
     <row r="1869">
-      <c r="A1869" s="9" t="n"/>
+      <c r="A1869" s="5" t="n"/>
     </row>
     <row r="1870">
-      <c r="A1870" s="9" t="n"/>
+      <c r="A1870" s="5" t="n"/>
     </row>
     <row r="1871">
-      <c r="A1871" s="9" t="n"/>
+      <c r="A1871" s="5" t="n"/>
     </row>
     <row r="1872">
-      <c r="A1872" s="9" t="n"/>
+      <c r="A1872" s="5" t="n"/>
     </row>
     <row r="1873">
-      <c r="A1873" s="9" t="n"/>
+      <c r="A1873" s="5" t="n"/>
     </row>
     <row r="1874">
-      <c r="A1874" s="9" t="n"/>
+      <c r="A1874" s="5" t="n"/>
     </row>
     <row r="1875">
-      <c r="A1875" s="9" t="n"/>
+      <c r="A1875" s="5" t="n"/>
     </row>
     <row r="1876">
-      <c r="A1876" s="9" t="n"/>
+      <c r="A1876" s="5" t="n"/>
     </row>
     <row r="1877">
-      <c r="A1877" s="9" t="n"/>
+      <c r="A1877" s="5" t="n"/>
     </row>
     <row r="1878">
-      <c r="A1878" s="9" t="n"/>
+      <c r="A1878" s="5" t="n"/>
     </row>
     <row r="1879">
-      <c r="A1879" s="9" t="n"/>
+      <c r="A1879" s="5" t="n"/>
     </row>
     <row r="1880">
-      <c r="A1880" s="9" t="n"/>
+      <c r="A1880" s="5" t="n"/>
     </row>
     <row r="1881">
-      <c r="A1881" s="9" t="n"/>
+      <c r="A1881" s="5" t="n"/>
     </row>
     <row r="1882">
-      <c r="A1882" s="9" t="n"/>
+      <c r="A1882" s="5" t="n"/>
     </row>
     <row r="1883">
-      <c r="A1883" s="9" t="n"/>
+      <c r="A1883" s="5" t="n"/>
     </row>
     <row r="1884">
-      <c r="A1884" s="9" t="n"/>
+      <c r="A1884" s="5" t="n"/>
     </row>
     <row r="1885">
-      <c r="A1885" s="9" t="n"/>
+      <c r="A1885" s="5" t="n"/>
     </row>
     <row r="1886">
-      <c r="A1886" s="9" t="n"/>
+      <c r="A1886" s="5" t="n"/>
     </row>
     <row r="1887">
-      <c r="A1887" s="9" t="n"/>
+      <c r="A1887" s="5" t="n"/>
     </row>
     <row r="1888">
-      <c r="A1888" s="9" t="n"/>
+      <c r="A1888" s="5" t="n"/>
     </row>
     <row r="1889">
-      <c r="A1889" s="9" t="n"/>
+      <c r="A1889" s="5" t="n"/>
     </row>
     <row r="1890">
-      <c r="A1890" s="9" t="n"/>
+      <c r="A1890" s="5" t="n"/>
     </row>
     <row r="1891">
-      <c r="A1891" s="9" t="n"/>
+      <c r="A1891" s="5" t="n"/>
     </row>
     <row r="1892">
-      <c r="A1892" s="9" t="n"/>
+      <c r="A1892" s="5" t="n"/>
     </row>
     <row r="1893">
-      <c r="A1893" s="9" t="n"/>
+      <c r="A1893" s="5" t="n"/>
     </row>
     <row r="1894">
-      <c r="A1894" s="9" t="n"/>
+      <c r="A1894" s="5" t="n"/>
     </row>
     <row r="1895">
-      <c r="A1895" s="9" t="n"/>
+      <c r="A1895" s="5" t="n"/>
     </row>
     <row r="1896">
-      <c r="A1896" s="9" t="n"/>
+      <c r="A1896" s="5" t="n"/>
     </row>
     <row r="1897">
-      <c r="A1897" s="9" t="n"/>
+      <c r="A1897" s="5" t="n"/>
     </row>
     <row r="1898">
-      <c r="A1898" s="9" t="n"/>
+      <c r="A1898" s="5" t="n"/>
     </row>
     <row r="1899">
-      <c r="A1899" s="9" t="n"/>
+      <c r="A1899" s="5" t="n"/>
     </row>
     <row r="1900">
-      <c r="A1900" s="9" t="n"/>
+      <c r="A1900" s="5" t="n"/>
     </row>
     <row r="1901">
-      <c r="A1901" s="9" t="n"/>
+      <c r="A1901" s="5" t="n"/>
     </row>
     <row r="1902">
-      <c r="A1902" s="9" t="n"/>
+      <c r="A1902" s="5" t="n"/>
     </row>
     <row r="1903">
-      <c r="A1903" s="9" t="n"/>
+      <c r="A1903" s="5" t="n"/>
     </row>
     <row r="1904">
-      <c r="A1904" s="9" t="n"/>
+      <c r="A1904" s="5" t="n"/>
     </row>
     <row r="1905">
-      <c r="A1905" s="9" t="n"/>
+      <c r="A1905" s="5" t="n"/>
     </row>
     <row r="1906">
-      <c r="A1906" s="9" t="n"/>
+      <c r="A1906" s="5" t="n"/>
     </row>
     <row r="1907">
-      <c r="A1907" s="9" t="n"/>
+      <c r="A1907" s="5" t="n"/>
     </row>
     <row r="1908">
-      <c r="A1908" s="9" t="n"/>
+      <c r="A1908" s="5" t="n"/>
     </row>
     <row r="1909">
-      <c r="A1909" s="9" t="n"/>
+      <c r="A1909" s="5" t="n"/>
     </row>
     <row r="1910">
-      <c r="A1910" s="9" t="n"/>
+      <c r="A1910" s="5" t="n"/>
     </row>
     <row r="1911">
-      <c r="A1911" s="9" t="n"/>
+      <c r="A1911" s="5" t="n"/>
     </row>
     <row r="1912">
-      <c r="A1912" s="9" t="n"/>
+      <c r="A1912" s="5" t="n"/>
     </row>
     <row r="1913">
-      <c r="A1913" s="9" t="n"/>
+      <c r="A1913" s="5" t="n"/>
     </row>
     <row r="1914">
-      <c r="A1914" s="9" t="n"/>
+      <c r="A1914" s="5" t="n"/>
     </row>
     <row r="1915">
-      <c r="A1915" s="9" t="n"/>
+      <c r="A1915" s="5" t="n"/>
     </row>
     <row r="1916">
-      <c r="A1916" s="9" t="n"/>
+      <c r="A1916" s="5" t="n"/>
     </row>
     <row r="1917">
-      <c r="A1917" s="9" t="n"/>
+      <c r="A1917" s="5" t="n"/>
     </row>
     <row r="1918">
-      <c r="A1918" s="9" t="n"/>
+      <c r="A1918" s="5" t="n"/>
     </row>
     <row r="1919">
-      <c r="A1919" s="9" t="n"/>
+      <c r="A1919" s="5" t="n"/>
     </row>
     <row r="1920">
-      <c r="A1920" s="9" t="n"/>
+      <c r="A1920" s="5" t="n"/>
     </row>
     <row r="1921">
-      <c r="A1921" s="9" t="n"/>
+      <c r="A1921" s="5" t="n"/>
     </row>
     <row r="1922">
-      <c r="A1922" s="9" t="n"/>
+      <c r="A1922" s="5" t="n"/>
     </row>
     <row r="1923">
-      <c r="A1923" s="9" t="n"/>
+      <c r="A1923" s="5" t="n"/>
     </row>
     <row r="1924">
-      <c r="A1924" s="9" t="n"/>
+      <c r="A1924" s="5" t="n"/>
     </row>
     <row r="1925">
-      <c r="A1925" s="9" t="n"/>
+      <c r="A1925" s="5" t="n"/>
     </row>
     <row r="1926">
-      <c r="A1926" s="9" t="n"/>
+      <c r="A1926" s="5" t="n"/>
     </row>
     <row r="1927">
-      <c r="A1927" s="9" t="n"/>
+      <c r="A1927" s="5" t="n"/>
     </row>
     <row r="1928">
-      <c r="A1928" s="9" t="n"/>
+      <c r="A1928" s="5" t="n"/>
     </row>
     <row r="1929">
-      <c r="A1929" s="9" t="n"/>
+      <c r="A1929" s="5" t="n"/>
     </row>
     <row r="1930">
-      <c r="A1930" s="9" t="n"/>
+      <c r="A1930" s="5" t="n"/>
     </row>
     <row r="1931">
-      <c r="A1931" s="9" t="n"/>
+      <c r="A1931" s="5" t="n"/>
     </row>
     <row r="1932">
-      <c r="A1932" s="9" t="n"/>
+      <c r="A1932" s="5" t="n"/>
     </row>
     <row r="1933">
-      <c r="A1933" s="9" t="n"/>
+      <c r="A1933" s="5" t="n"/>
     </row>
     <row r="1934">
-      <c r="A1934" s="9" t="n"/>
+      <c r="A1934" s="5" t="n"/>
     </row>
     <row r="1935">
-      <c r="A1935" s="9" t="n"/>
+      <c r="A1935" s="5" t="n"/>
     </row>
     <row r="1936">
-      <c r="A1936" s="9" t="n"/>
+      <c r="A1936" s="5" t="n"/>
     </row>
     <row r="1937">
-      <c r="A1937" s="9" t="n"/>
+      <c r="A1937" s="5" t="n"/>
     </row>
     <row r="1938">
-      <c r="A1938" s="9" t="n"/>
+      <c r="A1938" s="5" t="n"/>
     </row>
     <row r="1939">
-      <c r="A1939" s="9" t="n"/>
+      <c r="A1939" s="5" t="n"/>
     </row>
     <row r="1940">
-      <c r="A1940" s="9" t="n"/>
+      <c r="A1940" s="5" t="n"/>
     </row>
     <row r="1941">
-      <c r="A1941" s="9" t="n"/>
+      <c r="A1941" s="5" t="n"/>
     </row>
     <row r="1942">
-      <c r="A1942" s="9" t="n"/>
+      <c r="A1942" s="5" t="n"/>
     </row>
     <row r="1943">
-      <c r="A1943" s="9" t="n"/>
+      <c r="A1943" s="5" t="n"/>
     </row>
     <row r="1944">
-      <c r="A1944" s="9" t="n"/>
+      <c r="A1944" s="5" t="n"/>
     </row>
     <row r="1945">
-      <c r="A1945" s="9" t="n"/>
+      <c r="A1945" s="5" t="n"/>
     </row>
     <row r="1946">
-      <c r="A1946" s="9" t="n"/>
+      <c r="A1946" s="5" t="n"/>
     </row>
     <row r="1947">
-      <c r="A1947" s="9" t="n"/>
+      <c r="A1947" s="5" t="n"/>
     </row>
     <row r="1948">
-      <c r="A1948" s="9" t="n"/>
+      <c r="A1948" s="5" t="n"/>
     </row>
     <row r="1949">
-      <c r="A1949" s="9" t="n"/>
+      <c r="A1949" s="5" t="n"/>
     </row>
     <row r="1950">
-      <c r="A1950" s="9" t="n"/>
+      <c r="A1950" s="5" t="n"/>
     </row>
     <row r="1951">
-      <c r="A1951" s="9" t="n"/>
+      <c r="A1951" s="5" t="n"/>
     </row>
     <row r="1952">
-      <c r="A1952" s="9" t="n"/>
+      <c r="A1952" s="5" t="n"/>
     </row>
     <row r="1953">
-      <c r="A1953" s="9" t="n"/>
+      <c r="A1953" s="5" t="n"/>
     </row>
     <row r="1954">
-      <c r="A1954" s="9" t="n"/>
+      <c r="A1954" s="5" t="n"/>
     </row>
     <row r="1955">
-      <c r="A1955" s="9" t="n"/>
+      <c r="A1955" s="5" t="n"/>
     </row>
     <row r="1956">
-      <c r="A1956" s="9" t="n"/>
+      <c r="A1956" s="5" t="n"/>
     </row>
     <row r="1957">
-      <c r="A1957" s="9" t="n"/>
+      <c r="A1957" s="5" t="n"/>
     </row>
     <row r="1958">
-      <c r="A1958" s="9" t="n"/>
+      <c r="A1958" s="5" t="n"/>
     </row>
     <row r="1959">
-      <c r="A1959" s="9" t="n"/>
+      <c r="A1959" s="5" t="n"/>
     </row>
     <row r="1960">
-      <c r="A1960" s="9" t="n"/>
+      <c r="A1960" s="5" t="n"/>
     </row>
     <row r="1961">
-      <c r="A1961" s="9" t="n"/>
+      <c r="A1961" s="5" t="n"/>
     </row>
     <row r="1962">
-      <c r="A1962" s="9" t="n"/>
+      <c r="A1962" s="5" t="n"/>
     </row>
     <row r="1963">
-      <c r="A1963" s="9" t="n"/>
+      <c r="A1963" s="5" t="n"/>
     </row>
     <row r="1964">
-      <c r="A1964" s="9" t="n"/>
+      <c r="A1964" s="5" t="n"/>
     </row>
     <row r="1965">
-      <c r="A1965" s="9" t="n"/>
+      <c r="A1965" s="5" t="n"/>
     </row>
     <row r="1966">
-      <c r="A1966" s="9" t="n"/>
+      <c r="A1966" s="5" t="n"/>
     </row>
     <row r="1967">
-      <c r="A1967" s="9" t="n"/>
+      <c r="A1967" s="5" t="n"/>
     </row>
     <row r="1968">
-      <c r="A1968" s="9" t="n"/>
+      <c r="A1968" s="5" t="n"/>
     </row>
     <row r="1969">
-      <c r="A1969" s="9" t="n"/>
+      <c r="A1969" s="5" t="n"/>
     </row>
     <row r="1970">
-      <c r="A1970" s="9" t="n"/>
+      <c r="A1970" s="5" t="n"/>
     </row>
     <row r="1971">
-      <c r="A1971" s="9" t="n"/>
+      <c r="A1971" s="5" t="n"/>
     </row>
     <row r="1972">
-      <c r="A1972" s="9" t="n"/>
+      <c r="A1972" s="5" t="n"/>
     </row>
     <row r="1973">
-      <c r="A1973" s="9" t="n"/>
+      <c r="A1973" s="5" t="n"/>
     </row>
     <row r="1974">
-      <c r="A1974" s="9" t="n"/>
+      <c r="A1974" s="5" t="n"/>
     </row>
     <row r="1975">
-      <c r="A1975" s="9" t="n"/>
+      <c r="A1975" s="5" t="n"/>
     </row>
     <row r="1976">
-      <c r="A1976" s="9" t="n"/>
+      <c r="A1976" s="5" t="n"/>
     </row>
     <row r="1977">
-      <c r="A1977" s="9" t="n"/>
+      <c r="A1977" s="5" t="n"/>
     </row>
     <row r="1978">
-      <c r="A1978" s="9" t="n"/>
+      <c r="A1978" s="5" t="n"/>
     </row>
     <row r="1979">
-      <c r="A1979" s="9" t="n"/>
+      <c r="A1979" s="5" t="n"/>
     </row>
     <row r="1980">
-      <c r="A1980" s="9" t="n"/>
+      <c r="A1980" s="5" t="n"/>
     </row>
     <row r="1981">
-      <c r="A1981" s="9" t="n"/>
+      <c r="A1981" s="5" t="n"/>
     </row>
     <row r="1982">
-      <c r="A1982" s="9" t="n"/>
+      <c r="A1982" s="5" t="n"/>
     </row>
     <row r="1983">
-      <c r="A1983" s="9" t="n"/>
+      <c r="A1983" s="5" t="n"/>
     </row>
     <row r="1984">
-      <c r="A1984" s="9" t="n"/>
+      <c r="A1984" s="5" t="n"/>
     </row>
     <row r="1985">
-      <c r="A1985" s="9" t="n"/>
+      <c r="A1985" s="5" t="n"/>
     </row>
     <row r="1986">
-      <c r="A1986" s="9" t="n"/>
+      <c r="A1986" s="5" t="n"/>
     </row>
     <row r="1987">
-      <c r="A1987" s="9" t="n"/>
+      <c r="A1987" s="5" t="n"/>
     </row>
     <row r="1988">
-      <c r="A1988" s="9" t="n"/>
+      <c r="A1988" s="5" t="n"/>
     </row>
     <row r="1989">
-      <c r="A1989" s="9" t="n"/>
+      <c r="A1989" s="5" t="n"/>
     </row>
     <row r="1990">
-      <c r="A1990" s="9" t="n"/>
+      <c r="A1990" s="5" t="n"/>
     </row>
     <row r="1991">
-      <c r="A1991" s="9" t="n"/>
+      <c r="A1991" s="5" t="n"/>
     </row>
     <row r="1992">
-      <c r="A1992" s="9" t="n"/>
+      <c r="A1992" s="5" t="n"/>
     </row>
     <row r="1993">
-      <c r="A1993" s="9" t="n"/>
+      <c r="A1993" s="5" t="n"/>
     </row>
     <row r="1994">
-      <c r="A1994" s="9" t="n"/>
+      <c r="A1994" s="5" t="n"/>
     </row>
     <row r="1995">
-      <c r="A1995" s="9" t="n"/>
+      <c r="A1995" s="5" t="n"/>
     </row>
     <row r="1996">
-      <c r="A1996" s="9" t="n"/>
+      <c r="A1996" s="5" t="n"/>
     </row>
     <row r="1997">
-      <c r="A1997" s="9" t="n"/>
+      <c r="A1997" s="5" t="n"/>
     </row>
     <row r="1998">
-      <c r="A1998" s="9" t="n"/>
+      <c r="A1998" s="5" t="n"/>
     </row>
     <row r="1999">
-      <c r="A1999" s="9" t="n"/>
+      <c r="A1999" s="5" t="n"/>
     </row>
     <row r="2000">
-      <c r="A2000" s="9" t="n"/>
+      <c r="A2000" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6682,138 +6682,138 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>제품 MASTER 작성안내</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>품목(TM-NO)별 공정 라우팅과 공정별 기준단가를 정의합니다. 불량 배분과 Scrap Cost 계산의 기준입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>작성 방식 (세로형)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>· 한 품목의 공정이 4개면 4행을 씁니다. 각 행 = [품목 × 공정 1개].</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>· 같은 TM-NO의 행에서 품명은 동일하게, 공정순서는 1부터 빠짐없이 이어지게 입력합니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>열 설명</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>· TM-NO : 품목 번호</t>
+          <t>· TM-NO : 품목 번호 — ★ "TM" 접두어 없이 숫자-숫자 형식으로만 입력합니다 (예: 1545-01)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>· 품명 : 품목 이름</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>· 공정순서 : 해당 품목 안에서의 공정 순번 (1, 2, 3, …)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>· 공정명 : 공정명 MASTER에 등록된 이름과 정확히 일치해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>· 기준단가(원) : ★ 해당 공정까지의 누적 단가입니다 (공정이 진행될수록 커짐). 시스템은 이 값을 그대로 곱해 Scrap Cost를 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>※ 단가 단위는 '원'으로 가정했습니다 (집계 화면에서 천원으로 환산 표시). 단위가 다르면 알려주세요.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>· [TM-NO + 공정순서] 중복 금지. 누적 단가가 이전 공정보다 작으면 업로드 시 경고합니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>※ TM-NO 열은 '텍스트 서식'으로 지정되어 있습니다. 1545-01 같은 값은 날짜(1545년 1월)로 자동 변환되기 쉬우므로, 다른 파일에서 붙여넣은 뒤 반드시 확인하세요. 날짜로 변환된 값은 업로드 시 오류로 거부됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>※ 2행부터의 데이터는 '작성 예시'입니다. 실제 데이터로 교체(또는 삭제 후 입력)하여 업로드하세요.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>· 1행(제목 행)은 수정/삭제하지 마세요. 시스템이 열 이름으로 데이터를 인식합니다.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>· 시트 이름(DATA)도 변경하지 마세요.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>※ TM-NO 열은 '텍스트 서식'으로 지정되어 있습니다. 서식을 바꾸거나 다른 파일에서 붙여넣을 때 날짜로 변환되지 않았는지 확인하세요. 날짜로 변환된 값은 업로드 시 오류로 거부됩니다.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
